--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1004,7 +1004,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
@@ -1012,7 +1016,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>93f9967c3ceeb4efe5e6d1c216415b8cd6807a0f8e0fd3d7fdf1903530d27cc8</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1160,7 +1168,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
@@ -1168,7 +1180,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>9c071c4826e0c6bed0f851825c5a32161944e2c0e4b11ef3f0cfc8cf2321a717</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2860,7 +2876,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
@@ -2868,7 +2888,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>36cfe7e7863f9d1460b8dc4a91e8c1baec01e9664a492fb99d918b34bf2b6ea3</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4448,7 +4472,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
@@ -4456,7 +4484,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="N77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06d65258bb5c3c186c7c7db68031023271821689fc4fbd1ea75d865b8fd282c8</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -7770,7 +7802,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:49:47+00:00</t>
+          <t>2026-09-12T11:41:26+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7834,12 +7866,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:49:47+00:00</t>
+          <t>2026-09-12T11:41:26+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:49:47+00:00</t>
+          <t>2026-09-12T11:41:26+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7850,7 +7882,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>bd8c1ce600109c2433e233319fc76d333941de2357bd66d5fc70ecb75ce763a2</t>
+          <t>1dafb16e91fa0cc36d0b9c3704ad9a05b61c930c1e1bd91df670520bb5c4552c</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7934,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:49:47+00:00</t>
+          <t>2026-09-12T11:41:26+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7970,7 +8002,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:49:47+00:00</t>
+          <t>2026-09-12T11:41:26+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8034,7 +8066,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:49:47+00:00</t>
+          <t>2026-09-12T11:41:26+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8368,7 +8400,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="J152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
@@ -8380,7 +8416,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="N152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>ef9fc9b9318e7fb3b77d07dc231a71dfb5a7ba4d87511ec02da4b6dd33909ada</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -8428,7 +8468,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="J153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
@@ -8440,7 +8484,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="N153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>9ffe37a558c138b12b627dad42b2b5031f97c8f9606ff73420c4d90e25a5aa62</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -8488,7 +8536,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="J154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
@@ -8500,7 +8552,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="N154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>74e3b917bfc2953522782bd394b0e392149cdc683ac6a8d3eb223d095317f826</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -8608,7 +8664,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="J156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
@@ -8620,7 +8680,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="N156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>2bb9faef957b5b4e028c37084f7c639a91ae37b499fdbedde32aac91a55d488a</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -8668,7 +8732,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="J157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
@@ -8680,7 +8748,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="N157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>61d26c9a5fc173a201c91f202de53d06297ddf5de8927e930447b1b7b12f0295</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -8728,7 +8800,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="J158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
@@ -8740,7 +8816,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="N158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>a3e05e05353a3351797d1cb622c95e6275066b2d13ceb9b48d17a9f2faac0bfc</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -10412,7 +10492,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="J188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr">
         <is>
@@ -10424,7 +10508,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="N188" s="2" t="inlineStr"/>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>3124fc1887303e571edec4a48ff382f81bc987eee7f99c2c2a097ba5bbc79ba4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N188"/>
@@ -10699,7 +10787,11 @@
           <t>anthelioncap</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -10733,7 +10825,11 @@
           <t>kalshi</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -10767,7 +10863,11 @@
           <t>Talos-Trading</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -10801,7 +10901,11 @@
           <t>voleon</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -10841,7 +10945,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:49:47+00:00</t>
+          <t>2026-09-12T11:41:26+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10883,7 +10987,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:49:47+00:00</t>
+          <t>2026-09-12T11:41:26+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10925,7 +11029,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:49:47+00:00</t>
+          <t>2026-09-12T11:41:26+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10967,7 +11071,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:49:47+00:00</t>
+          <t>2026-09-12T11:41:26+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11009,7 +11113,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:49:47+00:00</t>
+          <t>2026-09-12T11:41:26+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11049,7 +11153,11 @@
           <t>3redpartners</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11083,7 +11191,11 @@
           <t>akunacapital</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11121,7 +11233,11 @@
           <t>aqr</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11155,7 +11271,11 @@
           <t>aquaticcapitalmanagement</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11193,7 +11313,11 @@
           <t>blackedgecapital</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11231,7 +11355,11 @@
           <t>bluecrestcapitalmanagement</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11269,7 +11397,11 @@
           <t>boerboeltrading</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11307,7 +11439,11 @@
           <t>chicagotrading</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11341,7 +11477,11 @@
           <t>drweng</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11375,7 +11515,11 @@
           <t>dvtrading</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11413,7 +11557,11 @@
           <t>engineersgate</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11451,7 +11599,11 @@
           <t>exoduspoint</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11485,7 +11637,11 @@
           <t>fiveringsllc</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11519,7 +11675,11 @@
           <t>flowtraders</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11557,7 +11717,11 @@
           <t>gelbergroup</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11591,7 +11755,11 @@
           <t>genevatrading</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11629,7 +11797,11 @@
           <t>gsacapital</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11663,7 +11835,11 @@
           <t>hyannisportresearch</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11697,7 +11873,11 @@
           <t>imc</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11731,7 +11911,11 @@
           <t>janestreet</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11769,7 +11953,11 @@
           <t>jumpcrypto</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11803,7 +11991,11 @@
           <t>jumptrading</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11841,7 +12033,11 @@
           <t>mako</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11879,7 +12075,11 @@
           <t>mangroup</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11913,7 +12113,11 @@
           <t>mavensecuritiesholdingltd</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11947,7 +12151,11 @@
           <t>oldmissioncapital</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -11981,7 +12189,11 @@
           <t>optiverprivate</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12019,7 +12231,11 @@
           <t>optiverus</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12053,7 +12269,11 @@
           <t>pdtpartners</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12091,7 +12311,11 @@
           <t>point72</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12129,7 +12353,11 @@
           <t>quadraturecapital</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12167,7 +12395,11 @@
           <t>quberesearchandtechnologies</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12205,7 +12437,11 @@
           <t>radixuniversity</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12239,7 +12475,11 @@
           <t>schonfeld</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12273,7 +12513,11 @@
           <t>sevenresearch</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12311,7 +12555,11 @@
           <t>simplextrading</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12349,7 +12597,11 @@
           <t>squarepointcapital</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12387,7 +12639,11 @@
           <t>towerresearchcapital</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12421,7 +12677,11 @@
           <t>transmarketgroup</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12455,7 +12715,11 @@
           <t>vaticlabs</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12489,7 +12753,11 @@
           <t>virtu</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12527,7 +12795,11 @@
           <t>voloridgeinvestmentmanagement</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12561,7 +12833,11 @@
           <t>walleyecapital-external-students</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12599,7 +12875,11 @@
           <t>winton</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12633,7 +12913,11 @@
           <t>worldquant</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12667,7 +12951,11 @@
           <t>belvederetrading</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12701,7 +12989,11 @@
           <t>valkyrietrading</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12894,7 +13186,7 @@
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -12929,7 +13221,11 @@
           <t>https://www.albatrosslabs.io/</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12967,7 +13263,11 @@
           <t>https://www.aqr.com/About-Us/Our-Internship-Program</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13005,7 +13305,11 @@
           <t>https://www.aspectcapital.com/careers/</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13043,7 +13347,11 @@
           <t>https://www.bamfunds.com/careers/internships</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13081,7 +13389,11 @@
           <t>https://www.bfcm.com/careers/</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13119,7 +13431,11 @@
           <t>https://www.blueshift.am/</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13157,7 +13473,11 @@
           <t>https://www.brevanhoward.com/students/</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13195,7 +13515,11 @@
           <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13236,7 +13560,7 @@
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -13271,7 +13595,11 @@
           <t>https://apply.workable.com/api/v1/widget/accounts/capula-investment-management-ltd</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13309,7 +13637,11 @@
           <t>https://careers.cboe.com/us/en</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13350,7 +13682,7 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -13385,7 +13717,11 @@
           <t>https://www.deshaw.com/careers</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13423,7 +13759,11 @@
           <t>https://www.eagleseven.com/</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13461,7 +13801,11 @@
           <t>https://www.eclipsetrading.com/careers/</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13499,7 +13843,11 @@
           <t>https://api.rippling.com/platform/api/ats/v1/board/edgehog-trading/jobs</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13537,7 +13885,11 @@
           <t>https://www.eschatontrading.com/careers</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13575,7 +13927,11 @@
           <t>https://www.gardacp.com/careers/</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13616,7 +13972,7 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -13651,7 +14007,11 @@
           <t>https://www.gresearch.com/careers/</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13689,7 +14049,11 @@
           <t>https://group1.com/careers/</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13727,7 +14091,11 @@
           <t>https://www.gsr.io/careers</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13768,7 +14136,7 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -13803,7 +14171,11 @@
           <t>https://www.huqt.com/</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13841,7 +14213,11 @@
           <t>https://www.headlandstech.com/careers/</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13879,7 +14255,11 @@
           <t>https://hedgewestsf.org/</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13917,7 +14297,11 @@
           <t>https://www.hudsonrivertrading.com/careers/?_departments=internships</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13955,7 +14339,11 @@
           <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13993,7 +14381,11 @@
           <t>https://www.iaqf.org/upcoming-events</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14031,7 +14423,11 @@
           <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14069,7 +14465,11 @@
           <t>https://www.janestreet.com/join-jane-street/programs-and-events/bridge/</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14107,7 +14507,11 @@
           <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14145,7 +14549,11 @@
           <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14183,7 +14591,11 @@
           <t>https://www.janestreet.com/join-jane-street/internships/</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14221,7 +14633,11 @@
           <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14259,7 +14675,11 @@
           <t>https://www.koretrading.com/front-page/careers/</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14297,7 +14717,11 @@
           <t>https://careers.lynxhedge.se/jobs.json</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14335,7 +14759,11 @@
           <t>https://www.marquettepartnersholdingsllc.com/careers</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14376,7 +14804,7 @@
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -14411,7 +14839,11 @@
           <t>https://battlecode.org/</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14449,7 +14881,11 @@
           <t>https://osqf.org/</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14487,7 +14923,11 @@
           <t>https://www.optiver.com/join-us/students/programs/futurefocus/</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14525,7 +14965,11 @@
           <t>https://readytradergo.optiver.com/</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14563,7 +15007,11 @@
           <t>https://optiver.com/working-at-optiver/career-opportunities/?level=student</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14601,7 +15049,11 @@
           <t>https://pokerbots.org/</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14639,7 +15091,11 @@
           <t>https://www.quantbot.com/careers/</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14677,7 +15133,11 @@
           <t>https://www.rentec.com/careers</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14715,7 +15175,11 @@
           <t>https://www.rokoscapital.com/careers</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14753,7 +15217,11 @@
           <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14791,7 +15259,11 @@
           <t>https://www.teza.com/careers/</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14829,7 +15301,11 @@
           <t>https://www.tgsmc.com/join-our-team/</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14870,7 +15346,7 @@
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -14905,7 +15381,11 @@
           <t>https://www.tradebot.com/careers/students</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14943,7 +15423,11 @@
           <t>https://trexquant.com/careers/students</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14984,7 +15468,7 @@
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -15022,7 +15506,7 @@
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -15057,7 +15541,11 @@
           <t>https://vectortrading.com/data/roles.json</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15095,7 +15583,11 @@
           <t>https://www.verition.com/careers</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15133,7 +15625,11 @@
           <t>https://volanttrading.com/</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15171,7 +15667,11 @@
           <t>https://www.voloridge.com/join-our-team</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15209,7 +15709,11 @@
           <t>https://www.wincent.com/careers/</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15247,7 +15751,11 @@
           <t>https://www.wintermute.com/company/careers</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15285,7 +15793,11 @@
           <t>https://careers.wolve.com/postings.json</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15323,7 +15835,11 @@
           <t>https://www.xtxmarkets.com/careers/</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15361,7 +15877,11 @@
           <t>https://careers.sig.com/api/jobs</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15395,7 +15915,11 @@
           <t>https://capgroup.wd1.myworkdayjobs.com/wday/cxs/capgroup/capitalgroupcareers</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15429,7 +15953,11 @@
           <t>https://cibc.wd3.myworkdayjobs.com/wday/cxs/cibc/campus</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15467,7 +15995,11 @@
           <t>https://cmegroup.wd1.myworkdayjobs.com/wday/cxs/cmegroup/cme_careers</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15501,7 +16033,11 @@
           <t>https://dimensional.wd5.myworkdayjobs.com/wday/cxs/dimensional/dfa_careers</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15535,7 +16071,11 @@
           <t>https://draftkings.wd1.myworkdayjobs.com/wday/cxs/draftkings/Campus_Career_Portal</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15569,7 +16109,11 @@
           <t>https://fanniemae.wd1.myworkdayjobs.com/wday/cxs/fanniemae/FannieMaeCareers</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15603,7 +16147,11 @@
           <t>https://freddiemac.wd5.myworkdayjobs.com/wday/cxs/freddiemac/External</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15637,7 +16185,11 @@
           <t>https://spgi.wd5.myworkdayjobs.com/wday/cxs/spgi/Kensho_Careers</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15671,7 +16223,11 @@
           <t>https://lplfinancial.wd1.myworkdayjobs.com/wday/cxs/lplfinancial/university</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15705,7 +16261,11 @@
           <t>https://mastercard.wd1.myworkdayjobs.com/wday/cxs/mastercard/Campus</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr"/>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15739,7 +16299,11 @@
           <t>https://ntrs.wd1.myworkdayjobs.com/wday/cxs/ntrs/northerntrust</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15777,7 +16341,11 @@
           <t>https://peak6group.wd1.myworkdayjobs.com/wday/cxs/peak6group/PEAK6</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15811,7 +16379,11 @@
           <t>https://pimco.wd1.myworkdayjobs.com/wday/cxs/pimco/pimco-careers</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15845,7 +16417,11 @@
           <t>https://rbc.wd3.myworkdayjobs.com/wday/cxs/rbc/RBCEARLYTALENT1</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15879,7 +16455,11 @@
           <t>https://troweprice.wd5.myworkdayjobs.com/wday/cxs/troweprice/TRowePrice</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15913,7 +16493,11 @@
           <t>https://vanguard.wd5.myworkdayjobs.com/wday/cxs/vanguard/vanguard_external</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr"/>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15947,7 +16531,11 @@
           <t>https://wellington.wd5.myworkdayjobs.com/wday/cxs/wellington/Campus</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T11:41:26+00:00</t>
+        </is>
+      </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
           <t>0</t>

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>1dafb16e91fa0cc36d0b9c3704ad9a05b61c930c1e1bd91df670520bb5c4552c</t>
+          <t>6be4c2fe4ea348b30ba97cdea1fd14277424b6eecb2351d325aa84dfffe85c1f</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr"/>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12679,7 +12679,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13186,7 +13186,7 @@
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13265,7 +13265,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -13560,7 +13560,7 @@
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -13597,7 +13597,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -13682,7 +13682,7 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13803,7 +13803,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -13845,7 +13845,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -13972,7 +13972,7 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -14009,7 +14009,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14093,7 +14093,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -14136,7 +14136,7 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14804,7 +14804,7 @@
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14883,7 +14883,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -14967,7 +14967,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15135,7 +15135,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15346,7 +15346,7 @@
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -15425,7 +15425,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15468,7 +15468,7 @@
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -15506,7 +15506,7 @@
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15837,7 +15837,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -15917,7 +15917,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -15997,7 +15997,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16035,7 +16035,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -16111,7 +16111,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16301,7 +16301,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16343,7 +16343,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16381,7 +16381,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16457,7 +16457,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16495,7 +16495,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:26+00:00</t>
+          <t>2026-09-12T12:18:02+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>6be4c2fe4ea348b30ba97cdea1fd14277424b6eecb2351d325aa84dfffe85c1f</t>
+          <t>c8755f7728d076df4bcea9f0b1314d64d98d3d915cfc81710e8c3d4fb72ccdd5</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr"/>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12679,7 +12679,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13186,7 +13186,7 @@
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13265,7 +13265,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -13560,7 +13560,7 @@
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -13597,7 +13597,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -13682,7 +13682,7 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13803,7 +13803,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -13845,7 +13845,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -13972,7 +13972,7 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -14009,7 +14009,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14093,7 +14093,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -14136,7 +14136,7 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14804,7 +14804,7 @@
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14883,7 +14883,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -14967,7 +14967,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15135,7 +15135,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15346,7 +15346,7 @@
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -15425,7 +15425,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15468,7 +15468,7 @@
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -15506,7 +15506,7 @@
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15837,7 +15837,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -15917,7 +15917,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -15997,7 +15997,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16035,7 +16035,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -16111,7 +16111,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16301,7 +16301,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16343,7 +16343,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16381,7 +16381,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16457,7 +16457,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16495,7 +16495,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:18:02+00:00</t>
+          <t>2026-09-12T13:15:28+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Programs'!$A$1:$N$188</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$H$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$H$158</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Applied'!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Discovered'!$A$1:$H$28</definedName>
   </definedNames>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>c8755f7728d076df4bcea9f0b1314d64d98d3d915cfc81710e8c3d4fb72ccdd5</t>
+          <t>60b41166df612d099b6b4e6bbb4e55f1755b95189fada4fa0925bc5843363f74</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr"/>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10882,7 +10882,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>voleon-ashby</t>
+          <t>teza-ashby</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -10898,12 +10898,12 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>voleon</t>
+          <t>teza-technologies</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10913,39 +10913,35 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Voleon. Verified 2026-09-11: 57 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The teza-careers row's note claimed the firm was on no public ATS; it is not true. 9 postings, 0 early-career today.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>luisae</t>
+          <t>voleon-ashby</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>github_readme</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>LuisaE/opportunities</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>LuisaE/opportunities</t>
+          <t>voleon</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10955,39 +10951,35 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Default branch is master, not main.</t>
+          <t>Voleon. Verified 2026-09-11: 57 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>nuft-2027</t>
+          <t>millennium-eightfold</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>github_readme</t>
+          <t>eightfold</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>NUFT 2027 Quant Internships</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>northwesternfintech/2027QuantInternships</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://campusjobs.mlp.com/api/apply/v2/jobs?domain=mlp.com</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10997,14 +10989,14 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47 firms, no class-year tags. Company is the ## heading above each table; watch for new firm sections and new role rows.</t>
+          <t>Added 2026-09-12. The largest hole the source audit found: millennium-students watched a careers page whose note said Millennium was on no public ATS, while this Eightfold board answers our own User-Agent with 59 campus postings (17 US), including '2027 Quantitative Researcher Intern, Austin' and '2027 Applied AI Engineer Intern, New York'. Descriptions are absent from the list payload, so posting bodies are fetched per changed row.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>simplify-2027</t>
+          <t>luisae</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -11014,22 +11006,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>SimplifyJobs Summer 2027 Internships</t>
+          <t>LuisaE/opportunities</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>SimplifyJobs/Summer2027-Internships</t>
+          <t>LuisaE/opportunities</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11039,14 +11031,14 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1169 roles on branch dev. README uses HTML &lt;table&gt;, not markdown. Low signal - no class-year tagging - so filtered to the SWE and quant sections only.</t>
+          <t>Default branch is master, not main.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>underclassmen-cruz</t>
+          <t>nuft-2027</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -11061,17 +11053,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>underclassmen-opportunities (Cruz-Lopez)</t>
+          <t>NUFT 2027 Quant Internships</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
+          <t>northwesternfintech/2027QuantInternships</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11081,14 +11073,14 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Best-maintained underclassmen list. Explicit [OPEN]/[CLOSING SOON] status column and grad windows inline in role titles. Six tables with differing headers.</t>
+          <t>47 firms, no class-year tags. Company is the ## heading above each table; watch for new firm sections and new role rows.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>underclassmen-zapply</t>
+          <t>simplify-2027</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -11098,22 +11090,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>zapplyjobs underclassmen-internships</t>
+          <t>SimplifyJobs Summer 2027 Internships</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>zapplyjobs/underclassmen-internships</t>
+          <t>SimplifyJobs/Summer2027-Internships</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11123,39 +11115,39 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Stale but occasionally updated. Company and role are combined into a single linked Name column.</t>
+          <t>1169 roles on branch dev. README uses HTML &lt;table&gt;, not markdown. Low signal - no class-year tagging - so filtered to the SWE and quant sections only.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>3red-greenhouse</t>
+          <t>underclassmen-cruz</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>github_readme</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3Red Partners</t>
+          <t>underclassmen-opportunities (Cruz-Lopez)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3redpartners</t>
+          <t>Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11165,35 +11157,39 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 8 jobs.</t>
+          <t>Best-maintained underclassmen list. Explicit [OPEN]/[CLOSING SOON] status column and grad windows inline in role titles. Six tables with differing headers.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>akunacapital-greenhouse</t>
+          <t>underclassmen-zapply</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>github_readme</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>zapplyjobs underclassmen-internships</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>akunacapital</t>
+          <t>zapplyjobs/underclassmen-internships</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11203,39 +11199,39 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Akuna Capital. Verified 2026-09-11: 38 postings, 9 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Stale but occasionally updated. Company and role are combined into a single linked Name column.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>aqr-greenhouse</t>
+          <t>zshah-2027</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>github_readme</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>AQR Capital</t>
+          <t>zshah Summer 2027 / Fall 2026 Tech Internships</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>aqr</t>
+          <t>zshah101/Automated-List-Of-Summer-2027-and-Fall-2026-Tech-Internships</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11245,14 +11241,14 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 54 jobs.</t>
+          <t>4,803 ATS endpoints polled every 30 min, 12 connectors, no LLM anywhere. Wide and large-firm-heavy like Simplify, so signal=low, but it carries a stated posting date and a visa/H-1B verdict neither of which we compute.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>aquaticcapitalmanagement-greenhouse</t>
+          <t>3red-greenhouse</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -11262,18 +11258,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3Red Partners</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>aquaticcapitalmanagement</t>
+          <t>3redpartners</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11283,14 +11283,14 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Aquatic Capital. Verified 2026-09-11: 8 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 8 jobs.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>blackedge-greenhouse</t>
+          <t>akunacapital-greenhouse</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -11300,22 +11300,18 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>BlackEdge Capital</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>blackedgecapital</t>
+          <t>akunacapital</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11325,14 +11321,14 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 independently of the agent report: 6 jobs, 2 US student (Quant Developer Intern, Quant Trader Intern - Chicago).</t>
+          <t>Akuna Capital. Verified 2026-09-11: 38 postings, 9 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>bluecrest-greenhouse</t>
+          <t>aqr-greenhouse</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -11342,22 +11338,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>BlueCrest Capital</t>
+          <t>AQR Capital</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>bluecrestcapitalmanagement</t>
+          <t>aqr</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11367,14 +11363,14 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 independently of the agent report: 9 jobs, 0 student today.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 54 jobs.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>boerboel-greenhouse</t>
+          <t>aquaticcapitalmanagement-greenhouse</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -11387,19 +11383,15 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Boerboel Trading</t>
-        </is>
-      </c>
+      <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>boerboeltrading</t>
+          <t>aquaticcapitalmanagement</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11409,14 +11401,14 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 independently of the agent report: 4 jobs, 0 student today.</t>
+          <t>Aquatic Capital. Verified 2026-09-11: 8 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>chicagotrading-greenhouse</t>
+          <t>blackedge-greenhouse</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -11431,17 +11423,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Chicago Trading Company (CTC)</t>
+          <t>BlackEdge Capital</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>chicagotrading</t>
+          <t>blackedgecapital</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11451,14 +11443,14 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 25 jobs.</t>
+          <t>Verified 2026-09-11 independently of the agent report: 6 jobs, 2 US student (Quant Developer Intern, Quant Trader Intern - Chicago).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>drweng-greenhouse</t>
+          <t>bluecrest-greenhouse</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -11471,15 +11463,19 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>BlueCrest Capital</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>drweng</t>
+          <t>bluecrestcapitalmanagement</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11489,14 +11485,14 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>DRW. Verified 2026-09-11: 157 postings, 8 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 independently of the agent report: 9 jobs, 0 student today.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>dvtrading-greenhouse</t>
+          <t>boerboel-greenhouse</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -11509,15 +11505,19 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Boerboel Trading</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>dvtrading</t>
+          <t>boerboeltrading</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11527,14 +11527,14 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>DV Trading. Verified 2026-09-11: 67 postings, 11 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 independently of the agent report: 4 jobs, 0 student today.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>engineersgate-greenhouse</t>
+          <t>capstone-greenhouse</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -11544,22 +11544,18 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Engineers Gate</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>engineersgate</t>
+          <t>capstoneinvestmentadvisors</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,14 +11565,14 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 7 jobs.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The capstone-careers row's note claimed the firm was on no public ATS; it is not true. 12 postings, 0 early-career today.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>exoduspoint-greenhouse</t>
+          <t>chicagotrading-greenhouse</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -11586,22 +11582,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>ExodusPoint Capital</t>
+          <t>Chicago Trading Company (CTC)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>exoduspoint</t>
+          <t>chicagotrading</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11611,14 +11607,14 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 2 jobs.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 25 jobs.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>fiveringsllc-greenhouse</t>
+          <t>drweng-greenhouse</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -11634,12 +11630,12 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>fiveringsllc</t>
+          <t>drweng</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11649,14 +11645,14 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Five Rings. Verified 2026-09-11: 16 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>DRW. Verified 2026-09-11: 157 postings, 8 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>flowtraders-greenhouse</t>
+          <t>dvtrading-greenhouse</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -11672,12 +11668,12 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>flowtraders</t>
+          <t>dvtrading</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11687,14 +11683,14 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Flow Traders. Verified 2026-09-11: 41 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>DV Trading. Verified 2026-09-11: 67 postings, 11 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>gelber-greenhouse</t>
+          <t>eclipse-greenhouse</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -11704,22 +11700,18 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Gelber Group</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>gelbergroup</t>
+          <t>eclipsetrading</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11729,14 +11721,14 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 8 jobs.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The eclipse-careers row's note claimed the firm was on no public ATS; it is not true. 18 postings, 4 early-career ('Graduate Trader | 2027 Intake'). Slug was only visible in a grnhse_app embed script on eclipsetrading.com/all-jobs/.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>genevatrading-greenhouse</t>
+          <t>engineersgate-greenhouse</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -11746,18 +11738,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Engineers Gate</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>genevatrading</t>
+          <t>engineersgate</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11767,14 +11763,14 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Geneva Trading. Verified 2026-09-11: 10 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 7 jobs.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>gsacapital-greenhouse</t>
+          <t>exoduspoint-greenhouse</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -11784,22 +11780,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>GSA Capital</t>
+          <t>ExodusPoint Capital</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>gsacapital</t>
+          <t>exoduspoint</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11809,14 +11805,14 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 independently of the agent report: 9 jobs, 1 US student (Quantitative Researcher - Intern, London/New York). GSA was NOT acquired by Eisler - it converted to a proprietary firm in Nov 2021 and hires actively.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 2 jobs.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>hyannisportresearch-greenhouse</t>
+          <t>fiveringsllc-greenhouse</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -11832,12 +11828,12 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>hyannisportresearch</t>
+          <t>fiveringsllc</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11847,14 +11843,14 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Hyannisport Research. Verified 2026-09-11: 10 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Five Rings. Verified 2026-09-11: 16 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>imc-greenhouse</t>
+          <t>flowtraders-greenhouse</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -11870,12 +11866,12 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>imc</t>
+          <t>flowtraders</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11885,14 +11881,14 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>IMC. Verified 2026-09-11: 170 postings, 7 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Flow Traders. Verified 2026-09-11: 41 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>janestreet-greenhouse</t>
+          <t>gelber-greenhouse</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -11902,18 +11898,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Gelber Group</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>janestreet</t>
+          <t>gelbergroup</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11923,14 +11923,14 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Jane Street. Verified 2026-09-11: 230 postings, 20 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 8 jobs.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>jumpcrypto-greenhouse</t>
+          <t>genevatrading-greenhouse</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -11940,22 +11940,18 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Jump Crypto</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>jumpcrypto</t>
+          <t>genevatrading</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11965,14 +11961,14 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 5 jobs.</t>
+          <t>Geneva Trading. Verified 2026-09-11: 10 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>jumptrading-greenhouse</t>
+          <t>graham-greenhouse</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -11988,12 +11984,12 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>jumptrading</t>
+          <t>grahamcapitalmanagement</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12003,14 +11999,14 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Jump Trading. Verified 2026-09-11: 106 postings, 10 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The graham-careers row's note claimed the firm was on no public ATS; it is not true. 7 postings, 0 early-career today.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>mako-greenhouse</t>
+          <t>gsacapital-greenhouse</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -12020,22 +12016,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Mako Global</t>
+          <t>GSA Capital</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>mako</t>
+          <t>gsacapital</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12045,14 +12041,14 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 independently of the agent report: 8 jobs, 0 US student today (graduate roles are Sydney/London). Watched for when a US role appears.</t>
+          <t>Verified 2026-09-11 independently of the agent report: 9 jobs, 1 US student (Quantitative Researcher - Intern, London/New York). GSA was NOT acquired by Eisler - it converted to a proprietary firm in Nov 2021 and hires actively.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>mangroup-greenhouse</t>
+          <t>gsr-greenhouse</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -12062,22 +12058,18 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Man Group / AHL / Numeric</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>mangroup</t>
+          <t>gsrmarkets</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12087,14 +12079,14 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 53 jobs.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The gsr-careers row's note claimed the firm was on no public ATS; it is not true. 5 postings, 0 early-career today. Advertised on the EU host, but boards-api.eu.greenhouse.io does not resolve and the plain host serves the slug fine.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>mavensecuritiesholdingltd-greenhouse</t>
+          <t>headlands-greenhouse</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -12110,12 +12102,12 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>mavensecuritiesholdingltd</t>
+          <t>headlandstechnologiesllc</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12125,14 +12117,14 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Maven Securities. Verified 2026-09-11: 46 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The headlands-careers row's note claimed the firm was on no public ATS; it is not true. 7 postings, 1 early-career ('Quantitative Researcher - New Grad'). The page_text row stays: headlands-careers does enumerate roles inline.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>oldmissioncapital-greenhouse</t>
+          <t>hrt-greenhouse</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -12148,12 +12140,12 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>oldmissioncapital</t>
+          <t>hrttalentcommunity</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12163,14 +12155,14 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Old Mission. Verified 2026-09-11: 38 postings, 3 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The hrt-careers / hrt-student-opportunities row's note claimed the firm was on no public ATS; it is not true. 3 postings, 2 early-career ('Campus Talent Community', 'FPGA Verification and Developer (Internships and Campus Full-time)'). Both HRT page_text rows claimed no public ATS.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>optiverprivate-greenhouse</t>
+          <t>hyannisportresearch-greenhouse</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -12186,12 +12178,12 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>optiverprivate</t>
+          <t>hyannisportresearch</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12201,14 +12193,14 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Optiver. Verified 2026-09-11: 10 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Hyannisport Research. Verified 2026-09-11: 10 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>optiverus-greenhouse</t>
+          <t>imc-greenhouse</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -12218,22 +12210,18 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Optiver US</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>optiverus</t>
+          <t>imc</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12243,14 +12231,14 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 163 jobs. The `optiver` and `optiverprivate` slugs return 0 and 1; this is the live US board.</t>
+          <t>IMC. Verified 2026-09-11: 170 postings, 7 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>pdtpartners-greenhouse</t>
+          <t>janestreet-greenhouse</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -12266,12 +12254,12 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>pdtpartners</t>
+          <t>janestreet</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12281,14 +12269,14 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>PDT Partners. Verified 2026-09-11: 9 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Jane Street. Verified 2026-09-11: 230 postings, 20 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>point72-greenhouse</t>
+          <t>jumpcrypto-greenhouse</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -12298,22 +12286,22 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Point72 / Cubist</t>
+          <t>Jump Crypto</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>point72</t>
+          <t>jumpcrypto</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12323,14 +12311,14 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 227 jobs.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 5 jobs.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>quadrature-greenhouse</t>
+          <t>jumptrading-greenhouse</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -12340,22 +12328,18 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Quadrature Capital</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>quadraturecapital</t>
+          <t>jumptrading</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12365,14 +12349,14 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 4 jobs.</t>
+          <t>Jump Trading. Verified 2026-09-11: 106 postings, 10 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>qube-greenhouse</t>
+          <t>mako-greenhouse</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -12382,22 +12366,22 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Qube Research &amp; Technologies</t>
+          <t>Mako Global</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>quberesearchandtechnologies</t>
+          <t>mako</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12407,14 +12391,14 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 198 jobs.</t>
+          <t>Verified 2026-09-11 independently of the agent report: 8 jobs, 0 US student today (graduate roles are Sydney/London). Watched for when a US role appears.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>radix-greenhouse</t>
+          <t>mangroup-greenhouse</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -12424,22 +12408,22 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Radix Trading</t>
+          <t>Man Group / AHL / Numeric</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>radixuniversity</t>
+          <t>mangroup</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12449,14 +12433,14 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 independently of the agent report: 8 jobs, 1 US student (Quantitative Technologist, C++ Intern - Chicago). The `radix` and `radixexperienced` slugs are the wrong board and the experienced board respectively.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 53 jobs.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>schonfeld-greenhouse</t>
+          <t>mavensecuritiesholdingltd-greenhouse</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -12472,12 +12456,12 @@
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>schonfeld</t>
+          <t>mavensecuritiesholdingltd</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12487,14 +12471,14 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Schonfeld. Verified 2026-09-11: 71 postings, 13 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Maven Securities. Verified 2026-09-11: 46 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>sevenresearch-greenhouse</t>
+          <t>oldmissioncapital-greenhouse</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -12510,12 +12494,12 @@
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sevenresearch</t>
+          <t>oldmissioncapital</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12525,14 +12509,14 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Seven Research. Verified 2026-09-11: 8 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Old Mission. Verified 2026-09-11: 38 postings, 3 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>simplex-greenhouse</t>
+          <t>optiverprivate-greenhouse</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -12542,22 +12526,18 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Simplex Trading</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>simplextrading</t>
+          <t>optiverprivate</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12567,14 +12547,14 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 5 jobs.</t>
+          <t>Optiver. Verified 2026-09-11: 10 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>squarepoint-greenhouse</t>
+          <t>optiverus-greenhouse</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -12589,17 +12569,17 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Squarepoint Capital</t>
+          <t>Optiver US</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>squarepointcapital</t>
+          <t>optiverus</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12609,14 +12589,14 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 93 jobs.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 163 jobs. The `optiver` and `optiverprivate` slugs return 0 and 1; this is the live US board.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>towerresearch-greenhouse</t>
+          <t>pdtpartners-greenhouse</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -12626,22 +12606,18 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Tower Research Capital</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>towerresearchcapital</t>
+          <t>pdtpartners</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12651,14 +12627,14 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 86 jobs. Richer than the tower-careers page watcher, which is kept as a second signal.</t>
+          <t>PDT Partners. Verified 2026-09-11: 9 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>transmarketgroup-greenhouse</t>
+          <t>point72-greenhouse</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -12668,18 +12644,22 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Point72 / Cubist</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>transmarketgroup</t>
+          <t>point72</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12689,14 +12669,14 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>TransMarket Group. Verified 2026-09-11: 19 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 227 jobs.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>vaticlabs-greenhouse</t>
+          <t>quadrature-greenhouse</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -12706,18 +12686,22 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Quadrature Capital</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>vaticlabs</t>
+          <t>quadraturecapital</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12727,14 +12711,14 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Vatic Labs. Verified 2026-09-11: 9 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 4 jobs.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>virtu-greenhouse</t>
+          <t>quantbot-greenhouse</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -12750,12 +12734,12 @@
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>virtu</t>
+          <t>quantbot-technologies</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12765,14 +12749,14 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Virtu Financial. Verified 2026-09-11: 50 postings, 6 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The quantbot-careers row's note claimed the firm was on no public ATS; it is not true. 7 postings, all 7 early-career: 'Quantitative Researcher Internship - 2027 [NY/London/HK]', 'Data Trading Analyst Summer Internship - 2027'.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>voloridge-greenhouse</t>
+          <t>qube-greenhouse</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -12787,17 +12771,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Voloridge / Ascend Program</t>
+          <t>Qube Research &amp; Technologies</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>voloridgeinvestmentmanagement</t>
+          <t>quberesearchandtechnologies</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12807,14 +12791,14 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 8 jobs, 4 US student rows including ASCEND PROGRAM 2027 - one of the very few programmes whose stated eligibility is 'first and second-year undergraduate students', so it is open to class of 2030 now. Two bugs had to be fixed before this row worked: 'Ascend Program 2027' contains no 'intern' and was only caught once the title screen learned Summer-Analyst/year vocabulary, and its location reads 'Jupiter, Florida' while the rest of the board reads 'Jupiter, FL', so the US filter dropped exactly this posting until it learned spelled-out state names.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 198 jobs.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>walleyecapital-external-students-greenhouse</t>
+          <t>radix-greenhouse</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -12824,18 +12808,22 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Radix Trading</t>
+        </is>
+      </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>walleyecapital-external-students</t>
+          <t>radixuniversity</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12845,14 +12833,14 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Walleye Capital. Verified 2026-09-11: 3 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 independently of the agent report: 8 jobs, 1 US student (Quantitative Technologist, C++ Intern - Chicago). The `radix` and `radixexperienced` slugs are the wrong board and the experienced board respectively.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>winton-greenhouse</t>
+          <t>schonfeld-greenhouse</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -12862,22 +12850,18 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Winton</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>winton</t>
+          <t>schonfeld</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12887,14 +12871,14 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 10 jobs.</t>
+          <t>Schonfeld. Verified 2026-09-11: 71 postings, 13 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>worldquant-greenhouse</t>
+          <t>sevenresearch-greenhouse</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -12910,12 +12894,12 @@
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>worldquant</t>
+          <t>sevenresearch</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12925,35 +12909,39 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>WorldQuant. Verified 2026-09-11: 103 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Seven Research. Verified 2026-09-11: 8 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>belvederetrading-lever</t>
+          <t>simplex-greenhouse</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Simplex Trading</t>
+        </is>
+      </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>belvederetrading</t>
+          <t>simplextrading</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -12963,35 +12951,39 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Belvedere Trading. Verified 2026-09-11: 14 postings, 3 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 5 jobs.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>valkyrietrading-lever</t>
+          <t>squarepoint-greenhouse</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Squarepoint Capital</t>
+        </is>
+      </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>valkyrietrading</t>
+          <t>squarepointcapital</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13001,19 +12993,19 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Valkyrie Trading. Verified 2026-09-11: 6 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 93 jobs.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>citadel-students</t>
+          <t>towerresearch-greenhouse</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13023,15 +13015,19 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Citadel students</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>https://www.citadel.com/careers/students/</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr"/>
+          <t>Tower Research Capital</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>towerresearchcapital</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13039,37 +13035,37 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>method=manual on purpose. Re-tested 2026-09-11: 403 Forbidden to state.USER_AGENT, HTTP 200 to a spoofed browser User-Agent. The block is deliberate and UA-based, so the only way to automate this page is to lie about who we are - declined. Surfaces as a monthly calendar reminder instead. An earlier note claiming 6,763 chars of text was measured with a browser-presenting fetcher, not with this tool's client.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 86 jobs. Richer than the tower-careers page watcher, which is kept as a second signal.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>citadelsecurities-careers</t>
+          <t>transmarketgroup-greenhouse</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Citadel Securities</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>https://www.citadelsecurities.com/careers</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr"/>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>transmarketgroup</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13077,19 +13073,19 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>method=manual on purpose. Sampled 10x on 2026-09-11: HTTP 200 in 5 of 10 fetches, 403 Cloudflare in the other 5, all with state.USER_AGENT. An earlier note here claimed the page was readable at 10,638 chars - that was a single lucky sample, the same error made on citadel.com the same day. An INTERMITTENT block is worse than a hard one: the source would report a failure on roughly half of all runs and escalate into ACT NOW after three, so it must not be automated. Re-sample repeatedly, never once, before moving any Citadel row off manual.</t>
+          <t>TransMarket Group. Verified 2026-09-11: 19 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>kaggle-competitions</t>
+          <t>tudor-greenhouse</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -13097,17 +13093,17 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Kaggle Competitions (all active)</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>https://www.kaggle.com/api/v1/competitions/list</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>tudorgroup</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13115,37 +13111,37 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>MANUAL. Kaggle competitions are always-open and rolling, so a daily diff is noise rather than news; calendar_reminders.ALWAYS already covers them. Dropped from Phase 2 deliberately.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The tudor-careers row's note claimed the firm was on no public ATS; it is not true. 4 postings, 0 early-career today.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>thedeckgame</t>
+          <t>vaticlabs-greenhouse</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>The Deck Game</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>https://thedeckgame.com/</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr"/>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>vaticlabs</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13153,77 +13149,73 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>MANUAL. Verified: JS shell yielding ~28 characters; sitemap has only two URLs. Not worth a Playwright run - there is nothing to diff.</t>
+          <t>Vatic Labs. Verified 2026-09-11: 9 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>akuna-academy</t>
+          <t>verition-greenhouse</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Akuna Academy</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>https://akunacapital.com/careers</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr"/>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>veritiongroupllc</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Carries Akuna Academy. Verified 2026-09-11: 1,304 chars.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The verition-careers row's note claimed the firm was on no public ATS; it is not true. 32 postings, 3 early-career ('2027 Investment/Technology/Platform Internship (US)'). Slug was only visible in a grnhse_app embed script on verition.com/open-positions.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>albatross-labs</t>
+          <t>virtu-greenhouse</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Albatross Labs</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>https://www.albatrosslabs.io/</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>virtu</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13233,19 +13225,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 2,390 chars, ratio 0.0055 - above the 0.0015 floor but the thinnest ratio on the watchlist. Advertises Software/Quant Developer at internship level.</t>
+          <t>Virtu Financial. Verified 2026-09-11: 50 postings, 6 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>aqr-internship-program</t>
+          <t>voloridge-greenhouse</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -13255,17 +13247,17 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>AQR internship programme</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aqr.com/About-Us/Our-Internship-Program</t>
+          <t>Voloridge / Ascend Program</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>voloridgeinvestmentmanagement</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13275,39 +13267,35 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Programme page kept alongside the Greenhouse board because it states eligibility, which the board rows do not. Verified 2026-09-11: 8,992 chars.</t>
+          <t>Verified 2026-09-11: 8 jobs, 4 US student rows including ASCEND PROGRAM 2027 - one of the very few programmes whose stated eligibility is 'first and second-year undergraduate students', so it is open to class of 2030 now. Two bugs had to be fixed before this row worked: 'Ascend Program 2027' contains no 'intern' and was only caught once the title screen learned Summer-Analyst/year vocabulary, and its location reads 'Jupiter, Florida' while the rest of the board reads 'Jupiter, FL', so the US filter dropped exactly this posting until it learned spelled-out state names.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>aspect-careers</t>
+          <t>walleyecapital-external-students-greenhouse</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Aspect Capital</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aspectcapital.com/careers/</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>walleyecapital-external-students</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13317,39 +13305,39 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 8,724 chars of text.</t>
+          <t>Walleye Capital. Verified 2026-09-11: 3 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>bam-internships</t>
+          <t>winton-greenhouse</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Balyasny (BAM)</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>https://www.bamfunds.com/careers/internships</t>
+          <t>Winton</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>winton</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13359,19 +13347,19 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 3,394 chars. Programme page only: BAM's Salesforce ATS is a 60-character shell, so individual reqs are not reachable.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 10 jobs.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>bluefin-careers</t>
+          <t>worldquant-greenhouse</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -13379,19 +13367,15 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Bluefin Companies</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>https://www.bfcm.com/careers/</t>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>worldquant</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13401,19 +13385,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 740 chars, close to the 500 floor. Renamed from Bluefin Trading; applications by email.</t>
+          <t>WorldQuant. Verified 2026-09-11: 103 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>blueshift-careers</t>
+          <t>xtxmarkets-greenhouse</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -13421,19 +13405,15 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Blueshift Asset Management</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>https://www.blueshift.am/</t>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>xtxmarketstechnologies</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13443,39 +13423,35 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 5,636 chars. Quantitative Analyst (MS/PhD) only. Note blueshift.com is marketing SaaS.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The xtx-careers row's note claimed the firm was on no public ATS; it is not true. 10 postings, 1 early-career ('AI Research Internship - XTY Labs').</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>brevanhoward-students</t>
+          <t>belvederetrading-lever</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Brevan Howard students</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>https://www.brevanhoward.com/students/</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>belvederetrading</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -13485,39 +13461,35 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 2,375 chars of text.</t>
+          <t>Belvedere Trading. Verified 2026-09-11: 14 postings, 3 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>bridgewater-students</t>
+          <t>valkyrietrading-lever</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Bridgewater students</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>valkyrietrading</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -13527,57 +13499,57 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Students page. bridgewater.com/careers yields less (2,326). Verified 2026-09-11: 4,624 chars.</t>
+          <t>Valkyrie Trading. Verified 2026-09-11: 6 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>capstone-careers</t>
+          <t>citadel-students</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Capstone Investment Advisors</t>
+          <t>Citadel students</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>https://www.capstoneco.com/careers</t>
+          <t>https://www.citadel.com/careers/students/</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 2,890 chars of text.</t>
+          <t>method=manual on purpose. Re-tested 2026-09-11: 403 Forbidden to state.USER_AGENT, HTTP 200 to a spoofed browser User-Agent. The block is deliberate and UA-based, so the only way to automate this page is to lie about who we are - declined. Surfaces as a monthly calendar reminder instead. An earlier note claiming 6,763 chars of text was measured with a browser-presenting fetcher, not with this tool's client.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>capula-workable</t>
+          <t>citadelsecurities-careers</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -13587,19 +13559,15 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Capula Investment Management</t>
+          <t>Citadel Securities</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>https://apply.workable.com/api/v1/widget/accounts/capula-investment-management-ltd</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12T13:15:28+00:00</t>
-        </is>
-      </c>
+          <t>https://www.citadelsecurities.com/careers</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13607,41 +13575,37 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: Workable JSON widget, 8,015 chars, ratio 0.997. Carries '2027 Trading and Research Summer Internship' and 'Technology Graduate Analyst'. Read as page_text because the tracker has no Workable parser; the feed is deterministic so a text diff is stable.</t>
+          <t>method=manual on purpose. Sampled 10x on 2026-09-11: HTTP 200 in 5 of 10 fetches, 403 Cloudflare in the other 5, all with state.USER_AGENT. An earlier note here claimed the page was readable at 10,638 chars - that was a single lucky sample, the same error made on citadel.com the same day. An INTERMITTENT block is worse than a hard one: the source would report a failure on roughly half of all runs and escalate into ACT NOW after three, so it must not be automated. Re-sample repeatedly, never once, before moving any Citadel row off manual.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>cboe-careers</t>
+          <t>kaggle-competitions</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>Kaggle Competitions (all active)</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>https://careers.cboe.com/us/en</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12T13:15:28+00:00</t>
-        </is>
-      </c>
+          <t>https://www.kaggle.com/api/v1/competitions/list</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13649,52 +13613,52 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 4,717 chars of text.</t>
+          <t>MANUAL. Kaggle competitions are always-open and rolling, so a daily diff is noise rather than news; calendar_reminders.ALWAYS already covers them. Dropped from Phase 2 deliberately.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>crabel-careers</t>
+          <t>thedeckgame</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Crabel Capital</t>
+          <t>The Deck Game</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>https://crabel.com/careers/</t>
+          <t>https://thedeckgame.com/</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 5,540 chars of text.</t>
+          <t>MANUAL. Verified: JS shell yielding ~28 characters; sitemap has only two URLs. Not worth a Playwright run - there is nothing to diff.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>deshaw-careers</t>
+          <t>akuna-academy</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -13704,39 +13668,35 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>D. E. Shaw</t>
+          <t>Akuna Academy</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>https://www.deshaw.com/careers</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12T13:15:28+00:00</t>
-        </is>
-      </c>
+          <t>https://akunacapital.com/careers</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 36,840 chars of text. deshaw.com/careers/students renders nothing (0 chars); /careers is the readable one.</t>
+          <t>Carries Akuna Academy. Verified 2026-09-11: 1,304 chars.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>eagleseven-careers</t>
+          <t>albatross-labs</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -13746,22 +13706,22 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Eagle Seven</t>
+          <t>Albatross Labs</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>https://www.eagleseven.com/</t>
+          <t>https://www.albatrosslabs.io/</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13771,14 +13731,14 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 15,784 chars. 'Junior Trader' is the most junior role today.</t>
+          <t>Verified 2026-09-11: 2,390 chars, ratio 0.0055 - above the 0.0015 floor but the thinnest ratio on the watchlist. Advertises Software/Quant Developer at internship level.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>eclipse-careers</t>
+          <t>aqr-internship-program</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -13788,22 +13748,22 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Eclipse Trading</t>
+          <t>AQR internship programme</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>https://www.eclipsetrading.com/careers/</t>
+          <t>https://www.aqr.com/About-Us/Our-Internship-Program</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -13813,14 +13773,14 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 2,270 chars of text.</t>
+          <t>BROKEN 2026-09-12 and not re-pointable: /About-Us/Our-Internship-Program now 302s to aqr.com/404, and /Careers plus /careers/internships both redirect to the homepage while /Insights/Careers and /About-Us/Careers 404. careers.aqr.com is a JS shell (0 chars of text). It had been reporting success off the 404 page's own prose (4,683 chars at ratio 0.0929) since some point after 2026-09-11, when it last verified at 8,992 chars. The redirect check now fails it loudly. ELIGIBILITY RESEARCH AT RISK: this row existed because the programme page stated eligibility that the board rows do not -- that text is gone and needs re-verifying by hand. Coverage of the postings themselves is not lost: aqr-greenhouse carries 54 postings including 12+ '2027 ... Summer Analyst' roles.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>edgehog-rippling</t>
+          <t>aspect-careers</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -13835,17 +13795,17 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Edgehog Trading</t>
+          <t>Aspect Capital</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>https://api.rippling.com/platform/api/ats/v1/board/edgehog-trading/jobs</t>
+          <t>https://www.aspectcapital.com/careers/</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13855,14 +13815,14 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: Rippling ATS JSON, 14 jobs, 3,171 chars, ratio 0.79. Graduate Quant Trader, Graduate SWE, Junior FPGA Developer.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 8,724 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>eschaton-careers</t>
+          <t>bam-internships</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -13872,22 +13832,22 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Eschaton Trading</t>
+          <t>Balyasny (BAM)</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>https://www.eschatontrading.com/careers</t>
+          <t>https://www.bamfunds.com/careers/internships</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -13897,14 +13857,14 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 2,184 chars of text.</t>
+          <t>Verified 2026-09-11: 3,394 chars. Programme page only: BAM's Salesforce ATS is a 60-character shell, so individual reqs are not reachable.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>garda-careers</t>
+          <t>bluefin-careers</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -13914,22 +13874,22 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Garda Capital Partners</t>
+          <t>Bluefin Companies</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>https://www.gardacp.com/careers/</t>
+          <t>https://www.bfcm.com/careers/</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -13939,14 +13899,14 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 5,287 chars. Six internships live, including SWE Intern (NY) and Trading Analyst Intern across Credit/Mortgages/Rates.</t>
+          <t>Verified 2026-09-11: 740 chars, close to the 500 floor. Renamed from Bluefin Trading; applications by email.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>graham-careers</t>
+          <t>blueshift-careers</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -13956,35 +13916,39 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Graham Capital</t>
+          <t>Blueshift Asset Management</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>https://www.grahamcapital.com/careers/</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr"/>
+          <t>https://www.blueshift.am/</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 18,019 chars of text.</t>
+          <t>Verified 2026-09-11: 5,636 chars. Quantitative Analyst (MS/PhD) only. Note blueshift.com is marketing SaaS.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>gresearch-careers</t>
+          <t>brevanhoward-students</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -13994,22 +13958,22 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>G-Research</t>
+          <t>Brevan Howard students</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>https://www.gresearch.com/careers/</t>
+          <t>https://www.brevanhoward.com/students/</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14019,14 +13983,14 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 1,801 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 2,375 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>group1-careers</t>
+          <t>bridgewater-students</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -14036,22 +14000,22 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Group One Trading</t>
+          <t>Bridgewater students</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>https://group1.com/careers/</t>
+          <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14061,14 +14025,14 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 3,990 chars. Trading Analyst Intern and Software Developer Intern. Also advertises a STANFORD CAREER FAIR on 6 Oct 2026 - see calendar_reminders.</t>
+          <t>Students page. bridgewater.com/careers yields less (2,326). Verified 2026-09-11: 4,624 chars.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>gsr-careers</t>
+          <t>capstone-careers</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -14078,39 +14042,35 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>GSR Markets</t>
+          <t>Capstone Investment Advisors</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>https://www.gsr.io/careers</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12T13:15:28+00:00</t>
-        </is>
-      </c>
+          <t>https://www.capstoneco.com/careers</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 5,216 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 2,890 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- capstone-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>gts-careers</t>
+          <t>capula-workable</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -14125,30 +14085,34 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>GTS</t>
+          <t>Capula Investment Management</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>https://gtsx.com/careers/</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr"/>
+          <t>https://apply.workable.com/api/v1/widget/accounts/capula-investment-management-ltd</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 18,734 chars of text.</t>
+          <t>Verified 2026-09-11: Workable JSON widget, 8,015 chars, ratio 0.997. Carries '2027 Trading and Research Summer Internship' and 'Technology Graduate Analyst'. Read as page_text because the tracker has no Workable parser; the feed is deterministic so a text diff is stable.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>harvard-undergraduate-trading</t>
+          <t>cboe-careers</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -14158,22 +14122,22 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Harvard Undergraduate Trading Competition</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>https://www.huqt.com/</t>
+          <t>https://careers.cboe.com/us/en</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14183,14 +14147,14 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 1654 chars of text over plain HTTP, no robots.txt. Use huqt.com - the article's harvarduqt.com/competition redirects to a 404.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 4,717 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>headlands-careers</t>
+          <t>crabel-careers</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -14200,39 +14164,35 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Headlands Technologies</t>
+          <t>Crabel Capital</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>https://www.headlandstech.com/careers/</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12T13:15:28+00:00</t>
-        </is>
-      </c>
+          <t>https://crabel.com/careers/</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 28,067 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 5,540 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>hedgewest-sf-meetup-series</t>
+          <t>deshaw-careers</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -14247,17 +14207,17 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>HedgeWest SF Meetup Series</t>
+          <t>D. E. Shaw</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>https://hedgewestsf.org/</t>
+          <t>https://www.deshaw.com/careers</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14267,14 +14227,14 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 837 chars of text over plain HTTP.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 36,840 chars of text. deshaw.com/careers/students renders nothing (0 chars); /careers is the readable one.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>hrt-careers</t>
+          <t>eagleseven-careers</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -14284,22 +14244,22 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Hudson River Trading</t>
+          <t>Eagle Seven</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>https://www.hudsonrivertrading.com/careers/?_departments=internships</t>
+          <t>https://www.eagleseven.com/</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14309,14 +14269,14 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>HRT is on no public ATS. Verified 2026-09-11: 5,598 chars of text.</t>
+          <t>Verified 2026-09-11: 15,784 chars. 'Junior Trader' is the most junior role today. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- eagleseven-workable watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>hrt-student-opportunities</t>
+          <t>eagleseven-workable</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -14326,22 +14286,18 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>HRT Inside HRT</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
+          <t>https://apply.workable.com/api/v1/widget/accounts/eagle-seven</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14351,14 +14307,14 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Programme page. Carries Inside HRT, a three-day programme for FIRST and second-year students - the eligibility band this owner is actually in. Verified 2026-09-11: 13,510 chars.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The eagleseven-careers row's note claimed the firm was on no public ATS; it is not true. 5 postings. Watched as page_text on the Workable widget JSON, the same shape as the existing capula-workable row, because there is no workable method.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>iaqf-academic-paper-competition</t>
+          <t>eclipse-careers</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -14368,22 +14324,22 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>IAQF Academic Paper Competition</t>
+          <t>Eclipse Trading</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>https://www.iaqf.org/upcoming-events</t>
+          <t>https://www.eclipsetrading.com/careers/</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14393,14 +14349,14 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 8194 chars of text over plain HTTP.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 2,270 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- eclipse-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>imc-launchpad-us</t>
+          <t>edgehog-rippling</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -14410,22 +14366,22 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>IMC Launchpad (US)</t>
+          <t>Edgehog Trading</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
+          <t>https://api.rippling.com/platform/api/ats/v1/board/edgehog-trading/jobs</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14435,14 +14391,14 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 2450 chars of text over plain HTTP.</t>
+          <t>Verified 2026-09-11: Rippling ATS JSON, 14 jobs, 3,171 chars, ratio 0.79. Graduate Quant Trader, Graduate SWE, Junior FPGA Developer.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>janestreet-bridge</t>
+          <t>eschaton-careers</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -14452,22 +14408,22 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Jane Street Bridge</t>
+          <t>Eschaton Trading</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/bridge/</t>
+          <t>https://www.eschatontrading.com/careers</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14477,14 +14433,14 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Programme page for first- and second-years. Verified 2026-09-11: 4,111 chars.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 2,184 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>janestreet-fttp</t>
+          <t>garda-careers</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -14499,17 +14455,17 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Jane Street FTTP</t>
+          <t>Garda Capital Partners</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
+          <t>https://www.gardacp.com/careers/</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14519,14 +14475,14 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Programme page, not the board. Jane Street's Greenhouse board has no FTTP listing at all, and this page carries the apply button. Rolling review. Verified 2026-09-11: 3,393 chars.</t>
+          <t>Verified 2026-09-11: 5,287 chars. Six internships live, including SWE Intern (NY) and Trading Analyst Intern across Credit/Mortgages/Rates.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>janestreet-insight</t>
+          <t>graham-careers</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -14536,39 +14492,35 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Jane Street INSIGHT</t>
+          <t>Graham Capital</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12T13:15:28+00:00</t>
-        </is>
-      </c>
+          <t>https://www.grahamcapital.com/careers/</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Programme page for INSIGHT, Jane Street's first-year programme. Verified 2026-09-11: 4,780 chars.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 18,019 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- graham-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>janestreet-internships</t>
+          <t>gresearch-careers</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -14583,17 +14535,17 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Jane Street internships</t>
+          <t>G-Research</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/internships/</t>
+          <t>https://www.gresearch.com/careers/</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14603,14 +14555,14 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 5,956 chars.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 1,801 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>janestreet-programs</t>
+          <t>group1-careers</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -14625,17 +14577,17 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Jane Street programs and events</t>
+          <t>Group One Trading</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://group1.com/careers/</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14645,14 +14597,14 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Index of every Jane Street programme; catches a new one appearing. Verified 2026-09-11: 5,997 chars.</t>
+          <t>Verified 2026-09-11: 3,990 chars. Trading Analyst Intern and Software Developer Intern. Also advertises a STANFORD CAREER FAIR on 6 Oct 2026 - see calendar_reminders.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>kore-careers</t>
+          <t>gsr-careers</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -14662,22 +14614,22 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Kore Trading</t>
+          <t>GSR Markets</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>https://www.koretrading.com/front-page/careers/</t>
+          <t>https://www.gsr.io/careers</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14687,14 +14639,14 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 1,485 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 5,216 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- gsr-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>lynx-teamtailor</t>
+          <t>gts-careers</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -14704,39 +14656,35 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Lynx Asset Management</t>
+          <t>GTS</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>https://careers.lynxhedge.se/jobs.json</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12T13:15:28+00:00</t>
-        </is>
-      </c>
+          <t>https://gtsx.com/careers/</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: Teamtailor JSON feed, 17,592 chars, ratio 0.993. Tags a Hackathon 2026 row as [Student Opportunity].</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 18,734 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>marquette-careers</t>
+          <t>harvard-undergraduate-trading</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -14746,22 +14694,22 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Marquette Partners</t>
+          <t>Harvard Undergraduate Trading Competition</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>https://www.marquettepartnersholdingsllc.com/careers</t>
+          <t>https://www.huqt.com/</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14771,14 +14719,14 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 4,406 chars. Experienced only today.</t>
+          <t>Probed 2026-09-06: 200, 1654 chars of text over plain HTTP, no robots.txt. Use huqt.com - the article's harvarduqt.com/competition redirects to a 404.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>millennium-students</t>
+          <t>headlands-careers</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -14793,30 +14741,34 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Millennium students</t>
+          <t>Headlands Technologies</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>https://www.mlp.com/careers/students/</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr"/>
+          <t>https://www.headlandstech.com/careers/</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Millennium is on no public ATS; this students page is the only automatable surface. Verified 2026-09-11: 7,366 chars.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 28,067 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- headlands-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>mit-battlecode-2027</t>
+          <t>hedgewest-sf-meetup-series</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -14831,17 +14783,17 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>MIT Battlecode 2027</t>
+          <t>HedgeWest SF Meetup Series</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>https://battlecode.org/</t>
+          <t>https://hedgewestsf.org/</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14851,14 +14803,14 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Probed: HTTP 200, 1,627 chars of visible text over plain HTTP, no robots.txt. Home page carries the live season banner ('Battlecode 2026 ended on January 31st, 2026!'), so a text diff should catch the 2027 announcement.</t>
+          <t>Probed 2026-09-06: 200, 837 chars of text over plain HTTP.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>open-source-quantitative-finance</t>
+          <t>hrt-careers</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -14873,17 +14825,17 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Open Source Quantitative Finance Conference</t>
+          <t>Hudson River Trading</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>https://osqf.org/</t>
+          <t>https://www.hudsonrivertrading.com/careers/?_departments=internships</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -14893,14 +14845,14 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 1966 chars of text over plain HTTP.</t>
+          <t>HRT is on no public ATS. Verified 2026-09-11: 5,598 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- hrt-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>optiver-futurefocus</t>
+          <t>hrt-student-opportunities</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -14915,17 +14867,17 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Optiver FutureFocus</t>
+          <t>HRT Inside HRT</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>https://www.optiver.com/join-us/students/programs/futurefocus/</t>
+          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -14935,14 +14887,14 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Programme page for FutureFocus, Optiver's five-day discovery programme, which the page states is for FIRST and second-year students. Renamed and re-pointed 2026-09-11: the old id and URL (optiver-futurefocus-chicago-2026, /recruitment-events/futurefocus-chicago) baked in a city and a year, and the old URL now 301s here. Verified 2026-09-11: 4,591 chars. Note the page states no graduation-year window, only 'first and second-year', so eligibility cannot be confirmed from it the way Susquehanna's postings can - read the application itself before trusting the label.</t>
+          <t>Programme page. Carries Inside HRT, a three-day programme for FIRST and second-year students - the eligibility band this owner is actually in. Verified 2026-09-11: 13,510 chars. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- hrt-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>optiver-ready-trader</t>
+          <t>iaqf-academic-paper-competition</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -14957,17 +14909,17 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Optiver Ready Trader Go</t>
+          <t>IAQF Academic Paper Competition</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>https://readytradergo.optiver.com/</t>
+          <t>https://www.iaqf.org/upcoming-events</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -14977,14 +14929,14 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>PHASE 3. Verified: 200, ~1KB of text over plain HTTP, no JS needed.</t>
+          <t>Probed 2026-09-06: 200, 8194 chars of text over plain HTTP.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>optiver-students</t>
+          <t>imc-launchpad-us</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -14999,17 +14951,17 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Optiver student opportunities</t>
+          <t>IMC Launchpad (US)</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/?level=student</t>
+          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15019,14 +14971,14 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 2,349 chars. Optiver's Greenhouse board (optiverprivate) is small, so the student page is the better signal.</t>
+          <t>Probed 2026-09-06: 200, 2450 chars of text over plain HTTP.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>pokerbots</t>
+          <t>janestreet-bridge</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -15041,17 +14993,17 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>MIT Pokerbots</t>
+          <t>Jane Street Bridge</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>https://pokerbots.org/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/bridge/</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15061,14 +15013,14 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>PHASE 3. Verified: 200, ~6.2KB of text over plain HTTP, no JS needed. Needs a selector - the page retains announcement banners from 2023-2026 in the markup.</t>
+          <t>Programme page for first- and second-years. Verified 2026-09-11: 4,111 chars.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>quantbot-careers</t>
+          <t>janestreet-fttp</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -15078,22 +15030,22 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Quantbot Technologies</t>
+          <t>Jane Street FTTP</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>https://www.quantbot.com/careers/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15103,14 +15055,14 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 751 chars of text.</t>
+          <t>Programme page, not the board. Jane Street's Greenhouse board has no FTTP listing at all, and this page carries the apply button. Rolling review. Verified 2026-09-11: 3,393 chars.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>rentec-careers</t>
+          <t>janestreet-insight</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -15125,17 +15077,17 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Renaissance Technologies</t>
+          <t>Jane Street INSIGHT</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>https://www.rentec.com/careers</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15145,14 +15097,14 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 1,380 chars of text.</t>
+          <t>Programme page for INSIGHT, Jane Street's first-year programme. Verified 2026-09-11: 4,780 chars.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>rokos-careers</t>
+          <t>janestreet-internships</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -15162,22 +15114,22 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Rokos Capital</t>
+          <t>Jane Street internships</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>https://www.rokoscapital.com/careers</t>
+          <t>https://www.janestreet.com/join-jane-street/internships/</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15187,14 +15139,14 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 620 chars of text. Close to the 500-char floor; a redesign will trip the shrink guard rather than go quiet.</t>
+          <t>Verified 2026-09-11: 5,956 chars.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>stevens-high-frequency-trading</t>
+          <t>janestreet-programs</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -15209,17 +15161,17 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Stevens High Frequency Trading Competition 2026</t>
+          <t>Jane Street programs and events</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15229,14 +15181,14 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 10400 chars of text over plain HTTP, robots.txt allows. Cleanly pollable.</t>
+          <t>Index of every Jane Street programme; catches a new one appearing. Verified 2026-09-11: 5,997 chars.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>teza-careers</t>
+          <t>kore-careers</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -15251,17 +15203,17 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>Kore Trading</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>https://www.teza.com/careers/</t>
+          <t>https://www.koretrading.com/front-page/careers/</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15271,14 +15223,14 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 8,134 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 1,485 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>tgs-join-our-team</t>
+          <t>lynx-teamtailor</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -15288,22 +15240,22 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>TGS Management</t>
+          <t>Lynx Asset Management</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>https://www.tgsmc.com/join-our-team/</t>
+          <t>https://careers.lynxhedge.se/jobs.json</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15313,14 +15265,14 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 1,977 chars. The Lever slug `tgsmc` resolves but returns an empty list, so the page is the only non-alerting surface.</t>
+          <t>Verified 2026-09-11: Teamtailor JSON feed, 17,592 chars, ratio 0.993. Tags a Hackathon 2026 row as [Student Opportunity].</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>tower-careers</t>
+          <t>marquette-careers</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -15330,35 +15282,39 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Tower Research Capital</t>
+          <t>Marquette Partners</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr"/>
+          <t>https://www.marquettepartnersholdingsllc.com/careers</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Tower is on no public ATS. Verified 2026-09-11: 1,233 chars of text.</t>
+          <t>Verified 2026-09-11: 4,406 chars. Experienced only today.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>tradebot-students</t>
+          <t>millennium-students</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -15368,39 +15324,35 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Tradebot Systems</t>
+          <t>Millennium students</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>https://www.tradebot.com/careers/students</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12T13:15:28+00:00</t>
-        </is>
-      </c>
+          <t>https://www.mlp.com/careers/students/</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 1,253 chars of text.</t>
+          <t>Millennium is on no public ATS; this students page is the only automatable surface. Verified 2026-09-11: 7,366 chars. CORRECTED 2026-09-12: the "no public ATS" claim above is false -- millennium-eightfold watches campusjobs.mlp.com, which serves 59 campus postings (17 US). This page_text row is kept in case the page carries programme detail the board rows do not state.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>trexquant-students</t>
+          <t>mit-battlecode-2027</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -15410,22 +15362,22 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Trexquant</t>
+          <t>MIT Battlecode 2027</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>https://trexquant.com/careers/students</t>
+          <t>https://battlecode.org/</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15435,14 +15387,14 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 891 chars of text.</t>
+          <t>Probed: HTTP 200, 1,627 chars of visible text over plain HTTP, no robots.txt. Home page carries the live season banner ('Battlecode 2026 ended on January 31st, 2026!'), so a text diff should catch the 2027 announcement.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>tudor-careers</t>
+          <t>open-source-quantitative-finance</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -15452,35 +15404,39 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Tudor Investment</t>
+          <t>Open Source Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>https://www.tudor.com/careers/</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr"/>
+          <t>https://osqf.org/</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 3,597 chars of text.</t>
+          <t>Probed 2026-09-06: 200, 1966 chars of text over plain HTTP.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>twosigma-campus</t>
+          <t>optiver-futurefocus</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -15495,30 +15451,34 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Two Sigma</t>
+          <t>Optiver FutureFocus</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/careers/students/</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr"/>
+          <t>https://www.optiver.com/join-us/students/programs/futurefocus/</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Two Sigma is on no public ATS. Verified 2026-09-11: 8,840 chars of text.</t>
+          <t>Programme page for FutureFocus, Optiver's five-day discovery programme, which the page states is for FIRST and second-year students. Renamed and re-pointed 2026-09-11: the old id and URL (optiver-futurefocus-chicago-2026, /recruitment-events/futurefocus-chicago) baked in a city and a year, and the old URL now 301s here. Verified 2026-09-11: 4,591 chars. Note the page states no graduation-year window, only 'first and second-year', so eligibility cannot be confirmed from it the way Susquehanna's postings can - read the application itself before trusting the label.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>vector-roles</t>
+          <t>optiver-ready-trader</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -15528,22 +15488,22 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Vector Trading (Chicago)</t>
+          <t>Optiver Ready Trader Go</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>https://vectortrading.com/data/roles.json</t>
+          <t>https://readytradergo.optiver.com/</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15553,14 +15513,14 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: The firm's own roles.json, 5 roles, 11,367 chars. 0 student today. Note vectortrading.io and Ashby `vector` are different companies entirely.</t>
+          <t>PHASE 3. Verified: 200, ~1KB of text over plain HTTP, no JS needed.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>verition-careers</t>
+          <t>optiver-students</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -15570,22 +15530,22 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Verition Fund Management</t>
+          <t>Optiver student opportunities</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>https://www.verition.com/careers</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/?level=student</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15595,14 +15555,14 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 11,469 chars of text.</t>
+          <t>Verified 2026-09-11: 2,349 chars. Optiver's Greenhouse board (optiverprivate) is small, so the student page is the better signal.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>volant-careers</t>
+          <t>pokerbots</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -15612,22 +15572,22 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Volant Trading</t>
+          <t>MIT Pokerbots</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>https://volanttrading.com/</t>
+          <t>https://pokerbots.org/</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15637,14 +15597,14 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 2,245 chars. Entry-level roles are Hong Kong only today.</t>
+          <t>PHASE 3. Verified: 200, ~6.2KB of text over plain HTTP, no JS needed. Needs a selector - the page retains announcement banners from 2023-2026 in the markup.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>voloridge-join-our-team</t>
+          <t>quantbot-careers</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -15654,22 +15614,22 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Voloridge Ascend Program</t>
+          <t>Quantbot Technologies</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>https://www.voloridge.com/join-our-team</t>
+          <t>https://www.quantbot.com/careers/</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15679,14 +15639,14 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 9,393 chars. Kept alongside the board because it carries the Ascend eligibility text and cohort size (20 places); board rows carry the posting only.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 751 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- quantbot-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>wincent-careers</t>
+          <t>rentec-careers</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -15696,22 +15656,22 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Wincent</t>
+          <t>Renaissance Technologies</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>https://www.wincent.com/careers/</t>
+          <t>https://www.rentec.com/careers</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15721,14 +15681,14 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 11,076 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 1,380 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>wintermute-careers</t>
+          <t>rokos-careers</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -15738,22 +15698,22 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Wintermute</t>
+          <t>Rokos Capital</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>https://www.wintermute.com/company/careers</t>
+          <t>https://www.rokoscapital.com/careers</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15763,14 +15723,14 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 14,346 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 620 chars of text. Close to the 500-char floor; a redesign will trip the shrink guard rather than go quiet.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>wolverine-careers</t>
+          <t>stevens-high-frequency-trading</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -15780,22 +15740,22 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Wolverine Trading</t>
+          <t>Stevens High Frequency Trading Competition 2026</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>https://careers.wolve.com/postings.json</t>
+          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15805,14 +15765,14 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: Pinpoint ATS JSON, 21 postings, 147,741 chars, ratio 0.99. Re-pointed from wolve.com/careers, which is 1,178 chars with zero student hits, and careers.wolve.com, which is a 317-char shell. Caveat: the feed embeds full HTML descriptions, so a reworded description will diff as changed text - if that turns noisy, write a small Pinpoint parser that keeps descriptions out of the snapshot the way the ATS methods do.</t>
+          <t>Probed 2026-09-06: 200, 10400 chars of text over plain HTTP, robots.txt allows. Cleanly pollable.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>xtx-careers</t>
+          <t>teza-careers</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -15822,22 +15782,22 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>XTX Markets</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>https://www.xtxmarkets.com/careers/</t>
+          <t>https://www.teza.com/careers/</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15847,39 +15807,39 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>XTX is on no public ATS. Verified 2026-09-11: 13,750 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 8,134 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- teza-ashby watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>sig-phenom</t>
+          <t>tgs-join-our-team</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>phenom</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Susquehanna (SIG)</t>
+          <t>TGS Management</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/api/jobs</t>
+          <t>https://www.tgsmc.com/join-our-team/</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -15889,73 +15849,77 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Phenom/iCIMS JSON API. Replaces the sig-careers manual row, which was correct about the page (402KB of HTML yields 221 chars) and wrong about the firm: this endpoint answers state.USER_AGENT with 263 postings. Verified 2026-09-11: 52 US student rows across Interns + Co-ops, New Graduates and Student Discovery Program. The five US Discovery Programs are gated to winter 2028 / spring 2029 graduates, i.e. sophomores for a four-year US degree, so they are correctly ruled out for class of 2030 until the autumn 2027 cycle.</t>
+          <t>Verified 2026-09-11: 1,977 chars. The Lever slug `tgsmc` resolves but returns an empty list, so the page is the only non-alerting surface.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>capitalgroup-workday</t>
+          <t>tower-careers</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Tower Research Capital</t>
+        </is>
+      </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>https://capgroup.wd1.myworkdayjobs.com/wday/cxs/capgroup/capitalgroupcareers</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12T13:15:28+00:00</t>
-        </is>
-      </c>
+          <t>https://www.tower-research.com/open-positions/</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Capital Group. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 1 US student rows.</t>
+          <t>Tower is on no public ATS. Verified 2026-09-11: 1,233 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>cibc-workday</t>
+          <t>tradebot-students</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Tradebot Systems</t>
+        </is>
+      </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>https://cibc.wd3.myworkdayjobs.com/wday/cxs/cibc/campus</t>
+          <t>https://www.tradebot.com/careers/students</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -15965,19 +15929,19 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>CIBC. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 44 postings on the board, 6 US student rows.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 1,253 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>cme-workday</t>
+          <t>trexquant-students</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -15987,17 +15951,17 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Trexquant</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>https://cmegroup.wd1.myworkdayjobs.com/wday/cxs/cmegroup/cme_careers</t>
+          <t>https://trexquant.com/careers/students</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16007,95 +15971,95 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 33 postings, 0 student today. Use the CXS API only - www.cmegroup.com times out for our User-Agent.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 891 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>dimensional-workday</t>
+          <t>tudor-careers</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Tudor Investment</t>
+        </is>
+      </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>https://dimensional.wd5.myworkdayjobs.com/wday/cxs/dimensional/dfa_careers</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12T13:15:28+00:00</t>
-        </is>
-      </c>
+          <t>https://www.tudor.com/careers/</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 72 postings on the board, 7 US student rows.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 3,597 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- tudor-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>draftkings-workday</t>
+          <t>twosigma-campus</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Two Sigma</t>
+        </is>
+      </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>https://draftkings.wd1.myworkdayjobs.com/wday/cxs/draftkings/Campus_Career_Portal</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12T13:15:28+00:00</t>
-        </is>
-      </c>
+          <t>https://www.twosigma.com/careers/internships/</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>DraftKings. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 7 postings on the board, 6 US student rows.</t>
+          <t>Re-pointed 2026-09-12: the old /careers/students/ url 301'd to the generic /careers/ page and had been reporting success from it. The internships page is the real replacement (9,509 chars, 29 'intern' mentions). No public vendor ATS -- careers.twosigma.com is a custom board with no Greenhouse/Lever/Ashby fingerprint.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>fanniemae-workday</t>
+          <t>vector-roles</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -16103,15 +16067,19 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr"/>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Vector Trading (Chicago)</t>
+        </is>
+      </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>https://fanniemae.wd1.myworkdayjobs.com/wday/cxs/fanniemae/FannieMaeCareers</t>
+          <t>https://vectortrading.com/data/roles.json</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16121,35 +16089,39 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Fannie Mae. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 61 postings on the board, 6 US student rows.</t>
+          <t>Verified 2026-09-11: The firm's own roles.json, 5 roles, 11,367 chars. 0 student today. Note vectortrading.io and Ashby `vector` are different companies entirely.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>freddiemac-workday</t>
+          <t>verition-careers</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Verition Fund Management</t>
+        </is>
+      </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>https://freddiemac.wd5.myworkdayjobs.com/wday/cxs/freddiemac/External</t>
+          <t>https://www.verition.com/careers</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16159,19 +16131,19 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Freddie Mac. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 103 postings on the board, 13 US student rows.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 11,469 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- verition-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>kensho-workday</t>
+          <t>volant-careers</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -16179,15 +16151,19 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr"/>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Volant Trading</t>
+        </is>
+      </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>https://spgi.wd5.myworkdayjobs.com/wday/cxs/spgi/Kensho_Careers</t>
+          <t>https://volanttrading.com/</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16197,35 +16173,39 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Kensho (S&amp;P Global). Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 9 postings on the board, 0 US student rows.</t>
+          <t>Verified 2026-09-11: 2,245 chars. Entry-level roles are Hong Kong only today.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>lpl-workday</t>
+          <t>voloridge-join-our-team</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Voloridge Ascend Program</t>
+        </is>
+      </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>https://lplfinancial.wd1.myworkdayjobs.com/wday/cxs/lplfinancial/university</t>
+          <t>https://www.voloridge.com/join-our-team</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16235,35 +16215,39 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>LPL Financial. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 36 postings on the board, 16 US student rows.</t>
+          <t>Verified 2026-09-11: 9,393 chars. Kept alongside the board because it carries the Ascend eligibility text and cohort size (20 places); board rows carry the posting only.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>mastercard-workday</t>
+          <t>wincent-careers</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Wincent</t>
+        </is>
+      </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/wday/cxs/mastercard/Campus</t>
+          <t>https://www.wincent.com/careers/</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16273,35 +16257,39 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Mastercard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 52 postings on the board, 1 US student rows.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 11,076 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>northerntrust-workday</t>
+          <t>wintermute-careers</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Wintermute</t>
+        </is>
+      </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>https://ntrs.wd1.myworkdayjobs.com/wday/cxs/ntrs/northerntrust</t>
+          <t>https://www.wintermute.com/company/careers</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16311,39 +16299,39 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Northern Trust. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 665 postings on the board, 20 US student rows.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 14,346 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>peak6-workday</t>
+          <t>wolverine-careers</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>PEAK6</t>
+          <t>Wolverine Trading</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>https://peak6group.wd1.myworkdayjobs.com/wday/cxs/peak6group/PEAK6</t>
+          <t>https://careers.wolve.com/postings.json</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16353,35 +16341,39 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 14 postings, 3 US student rows (Trading Bootcamp Micro-Internship Summer 2027, Trading Internship for Women+ Summer 2027, Trading Associate 2027). Re-pointed from peak6.com/careers, which returns 3,100 chars of marketing copy with no job data and no outbound job links - a row that could only ever look healthy and quiet.</t>
+          <t>Verified 2026-09-11: Pinpoint ATS JSON, 21 postings, 147,741 chars, ratio 0.99. Re-pointed from wolve.com/careers, which is 1,178 chars with zero student hits, and careers.wolve.com, which is a 317-char shell. Caveat: the feed embeds full HTML descriptions, so a reworded description will diff as changed text - if that turns noisy, write a small Pinpoint parser that keeps descriptions out of the snapshot the way the ATS methods do.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>pimco-workday</t>
+          <t>xtx-careers</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>XTX Markets</t>
+        </is>
+      </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>https://pimco.wd1.myworkdayjobs.com/wday/cxs/pimco/pimco-careers</t>
+          <t>https://www.xtxmarkets.com/careers/</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16391,35 +16383,39 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>PIMCO. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 195 postings on the board, 7 US student rows.</t>
+          <t>XTX is on no public ATS. Verified 2026-09-11: 13,750 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- xtxmarkets-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>rbc-workday</t>
+          <t>sig-phenom</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>phenom</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Susquehanna (SIG)</t>
+        </is>
+      </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>https://rbc.wd3.myworkdayjobs.com/wday/cxs/rbc/RBCEARLYTALENT1</t>
+          <t>https://careers.sig.com/api/jobs</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16429,14 +16425,14 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>RBC Early Talent. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 3 US student rows.</t>
+          <t>Phenom/iCIMS JSON API. Replaces the sig-careers manual row, which was correct about the page (402KB of HTML yields 221 chars) and wrong about the firm: this endpoint answers state.USER_AGENT with 263 postings. Verified 2026-09-11: 52 US student rows across Interns + Co-ops, New Graduates and Student Discovery Program. The five US Discovery Programs are gated to winter 2028 / spring 2029 graduates, i.e. sophomores for a four-year US degree, so they are correctly ruled out for class of 2030 until the autumn 2027 cycle.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>troweprice-workday</t>
+          <t>capitalgroup-workday</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -16452,12 +16448,12 @@
       <c r="D142" s="2" t="inlineStr"/>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>https://troweprice.wd5.myworkdayjobs.com/wday/cxs/troweprice/TRowePrice</t>
+          <t>https://capgroup.wd1.myworkdayjobs.com/wday/cxs/capgroup/capitalgroupcareers</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16467,14 +16463,14 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>T. Rowe Price. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 136 postings on the board, 8 US student rows.</t>
+          <t>Capital Group. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 1 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>vanguard-workday</t>
+          <t>cibc-workday</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -16490,12 +16486,12 @@
       <c r="D143" s="2" t="inlineStr"/>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>https://vanguard.wd5.myworkdayjobs.com/wday/cxs/vanguard/vanguard_external</t>
+          <t>https://cibc.wd3.myworkdayjobs.com/wday/cxs/cibc/campus</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:15:28+00:00</t>
+          <t>2026-09-13T12:47:15+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16505,138 +16501,680 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Vanguard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 441 postings on the board, 18 US student rows.</t>
+          <t>CIBC. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 44 postings on the board, 6 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>cme-workday</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>CME Group</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>https://cmegroup.wd1.myworkdayjobs.com/wday/cxs/cmegroup/cme_careers</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-11: 33 postings, 0 student today. Use the CXS API only - www.cmegroup.com times out for our User-Agent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>dimensional-workday</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr"/>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>https://dimensional.wd5.myworkdayjobs.com/wday/cxs/dimensional/dfa_careers</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>Dimensional Fund Advisors. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 72 postings on the board, 7 US student rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>draftkings-workday</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>https://draftkings.wd1.myworkdayjobs.com/wday/cxs/draftkings/Campus_Career_Portal</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>DraftKings. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 7 postings on the board, 6 US student rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>fanniemae-workday</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>https://fanniemae.wd1.myworkdayjobs.com/wday/cxs/fanniemae/FannieMaeCareers</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>Fannie Mae. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 61 postings on the board, 6 US student rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>freddiemac-workday</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr"/>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>https://freddiemac.wd5.myworkdayjobs.com/wday/cxs/freddiemac/External</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Freddie Mac. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 103 postings on the board, 13 US student rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>kensho-workday</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr"/>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>https://spgi.wd5.myworkdayjobs.com/wday/cxs/spgi/Kensho_Careers</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>Kensho (S&amp;P Global). Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 9 postings on the board, 0 US student rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>lpl-workday</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr"/>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>https://lplfinancial.wd1.myworkdayjobs.com/wday/cxs/lplfinancial/university</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>LPL Financial. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 36 postings on the board, 16 US student rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>mastercard-workday</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr"/>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>https://mastercard.wd1.myworkdayjobs.com/wday/cxs/mastercard/Campus</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>Mastercard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 52 postings on the board, 1 US student rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>northerntrust-workday</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr"/>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>https://ntrs.wd1.myworkdayjobs.com/wday/cxs/ntrs/northerntrust</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Northern Trust. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 665 postings on the board, 20 US student rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>peak6-workday</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>PEAK6</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>https://peak6group.wd1.myworkdayjobs.com/wday/cxs/peak6group/PEAK6</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-11: 14 postings, 3 US student rows (Trading Bootcamp Micro-Internship Summer 2027, Trading Internship for Women+ Summer 2027, Trading Associate 2027). Re-pointed from peak6.com/careers, which returns 3,100 chars of marketing copy with no job data and no outbound job links - a row that could only ever look healthy and quiet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>pimco-workday</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr"/>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>https://pimco.wd1.myworkdayjobs.com/wday/cxs/pimco/pimco-careers</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>PIMCO. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 195 postings on the board, 7 US student rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>rbc-workday</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr"/>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>https://rbc.wd3.myworkdayjobs.com/wday/cxs/rbc/RBCEARLYTALENT1</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>RBC Early Talent. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 3 US student rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>troweprice-workday</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr"/>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>https://troweprice.wd5.myworkdayjobs.com/wday/cxs/troweprice/TRowePrice</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>T. Rowe Price. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 136 postings on the board, 8 US student rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>vanguard-workday</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr"/>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>https://vanguard.wd5.myworkdayjobs.com/wday/cxs/vanguard/vanguard_external</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>Vanguard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 441 postings on the board, 18 US student rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
           <t>wellington-workday</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>workday</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr"/>
-      <c r="E144" s="3" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr"/>
+      <c r="E158" s="3" t="inlineStr">
         <is>
           <t>https://wellington.wd5.myworkdayjobs.com/wday/cxs/wellington/Campus</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12T13:15:28+00:00</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:47:15+00:00</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>Wellington Management. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 10 postings on the board, 4 US student rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H144"/>
+  <autoFilter ref="A1:H158"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId89"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr"/>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13025,7 +13025,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13295,7 +13295,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -13805,7 +13805,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -13889,7 +13889,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14015,7 +14015,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14545,7 +14545,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -14919,7 +14919,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15003,7 +15003,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15045,7 +15045,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15297,7 +15297,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15419,7 +15419,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15545,7 +15545,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15671,7 +15671,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15713,7 +15713,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15755,7 +15755,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16121,7 +16121,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16205,7 +16205,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16289,7 +16289,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16415,7 +16415,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16453,7 +16453,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16609,7 +16609,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -16647,7 +16647,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16685,7 +16685,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16723,7 +16723,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -16761,7 +16761,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -16842,7 +16842,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -16879,7 +16879,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -17031,7 +17031,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -17069,7 +17069,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:27:13+00:00</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>60b41166df612d099b6b4e6bbb4e55f1755b95189fada4fa0925bc5843363f74</t>
+          <t>914754581aace9fd7a7cff7bfb787ac0e7f52f18e0194b6a8d837531643e0b9d</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr"/>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13025,7 +13025,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13295,7 +13295,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -13805,7 +13805,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -13889,7 +13889,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14015,7 +14015,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14545,7 +14545,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -14919,7 +14919,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15003,7 +15003,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15045,7 +15045,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15297,7 +15297,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15419,7 +15419,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15545,7 +15545,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15671,7 +15671,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15713,7 +15713,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15755,7 +15755,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16121,7 +16121,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16205,7 +16205,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16289,7 +16289,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16415,7 +16415,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16453,7 +16453,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16609,7 +16609,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -16647,7 +16647,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16685,7 +16685,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16723,7 +16723,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -16761,7 +16761,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -16837,12 +16837,12 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -16879,7 +16879,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -17031,7 +17031,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -17069,7 +17069,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:27:13+00:00</t>
+          <t>2026-09-13T13:59:47+00:00</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Programs'!$A$1:$N$188</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$H$158</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Applied'!$A$1:$C$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Discovered'!$A$1:$H$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Discovered'!$A$1:$H$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>914754581aace9fd7a7cff7bfb787ac0e7f52f18e0194b6a8d837531643e0b9d</t>
+          <t>9f94bdf7c297d22169d8a6e0e0413c94ff4a6cd02a1b6464a87b49ba2b6c9bb9</t>
         </is>
       </c>
     </row>
@@ -7934,12 +7934,12 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T12:11:00+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr"/>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>de71475901207962ca947d6f8f4202f2de5be54ec3c1592fc60d8211806d9b25</t>
+          <t>7aae100d64822870cb3d2a28d1948dd7d89af148e680e1b5c8f15aee2305042c</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8734,10 +8734,14 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
-        </is>
-      </c>
-      <c r="K157" s="2" t="inlineStr"/>
+          <t>2026-09-14T15:23:08+00:00</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14T15:23:08+00:00</t>
+        </is>
+      </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
           <t>2026-09-06</t>
@@ -8750,7 +8754,7 @@
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>61d26c9a5fc173a201c91f202de53d06297ddf5de8927e930447b1b7b12f0295</t>
+          <t>354e8229c45e114d1b9a08f856918cb1d9faba977a578b3417b1c84b5f02ef8d</t>
         </is>
       </c>
     </row>
@@ -8802,7 +8806,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10494,7 +10498,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10789,7 +10793,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10827,7 +10831,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10865,7 +10869,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10903,7 +10907,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10941,7 +10945,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10979,7 +10983,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11021,7 +11025,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11063,7 +11067,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11105,7 +11109,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11147,7 +11151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11189,7 +11193,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11231,7 +11235,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11273,7 +11277,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11311,7 +11315,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11353,7 +11357,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11391,7 +11395,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11433,7 +11437,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11475,7 +11479,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11517,7 +11521,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11555,7 +11559,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11597,7 +11601,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11635,7 +11639,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11673,7 +11677,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11711,7 +11715,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11753,7 +11757,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11795,7 +11799,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11833,7 +11837,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11871,7 +11875,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11913,7 +11917,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11951,7 +11955,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11989,7 +11993,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12031,7 +12035,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12069,7 +12073,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12107,7 +12111,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12145,7 +12149,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12183,7 +12187,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12221,7 +12225,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12259,7 +12263,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12301,7 +12305,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12339,7 +12343,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12381,7 +12385,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12423,7 +12427,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12461,7 +12465,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12499,7 +12503,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12537,7 +12541,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12579,7 +12583,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12617,7 +12621,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12659,7 +12663,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12701,7 +12705,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12739,7 +12743,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12781,7 +12785,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12823,7 +12827,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12861,7 +12865,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12899,7 +12903,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12941,7 +12945,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -12983,7 +12987,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13025,7 +13029,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13063,7 +13067,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13101,7 +13105,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13139,7 +13143,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13177,7 +13181,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13215,7 +13219,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13257,7 +13261,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13295,7 +13299,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13337,7 +13341,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13375,7 +13379,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13413,7 +13417,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13451,7 +13455,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -13489,7 +13493,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -13684,7 +13688,7 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -13721,7 +13725,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13763,12 +13767,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:47:15+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -13805,7 +13809,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13847,7 +13851,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -13889,7 +13893,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -13931,7 +13935,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -13973,7 +13977,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14015,7 +14019,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14058,7 +14062,7 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -14095,7 +14099,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14137,7 +14141,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14180,7 +14184,7 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -14217,7 +14221,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14259,7 +14263,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14297,7 +14301,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14339,7 +14343,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14381,7 +14385,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14423,7 +14427,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14465,7 +14469,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14508,7 +14512,7 @@
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -14545,7 +14549,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14587,7 +14591,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14629,7 +14633,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14672,7 +14676,7 @@
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -14709,7 +14713,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14751,7 +14755,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14793,7 +14797,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14835,7 +14839,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -14877,7 +14881,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -14919,7 +14923,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -14961,7 +14965,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15003,7 +15007,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15045,7 +15049,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15087,7 +15091,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15129,7 +15133,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15171,7 +15175,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15213,7 +15217,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15255,7 +15259,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15297,7 +15301,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15340,7 +15344,7 @@
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -15377,7 +15381,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15419,7 +15423,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15461,7 +15465,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15503,7 +15507,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15545,7 +15549,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15587,7 +15591,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15629,7 +15633,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15671,7 +15675,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15713,7 +15717,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15755,7 +15759,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15797,7 +15801,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15839,7 +15843,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -15882,7 +15886,7 @@
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -15919,7 +15923,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -15961,7 +15965,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16004,7 +16008,7 @@
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -16042,7 +16046,7 @@
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -16079,7 +16083,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16121,7 +16125,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16163,7 +16167,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16205,7 +16209,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16247,7 +16251,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16289,7 +16293,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16331,7 +16335,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16373,7 +16377,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16415,7 +16419,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16453,7 +16457,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16491,7 +16495,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16533,7 +16537,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16571,7 +16575,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16609,7 +16613,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -16647,7 +16651,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16685,7 +16689,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16723,7 +16727,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -16761,7 +16765,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -16799,7 +16803,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -16837,7 +16841,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -16879,7 +16883,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -16917,7 +16921,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -16955,7 +16959,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -16993,7 +16997,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -17031,7 +17035,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -17069,7 +17073,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:59:47+00:00</t>
+          <t>2026-09-14T15:23:08+00:00</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -17223,7 +17227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17281,962 +17285,966 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Allston Trading</t>
+          <t>appian</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>allston-trading</t>
+          <t>greenhouse:appian</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>https://allstontrading.com</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/appian/jobs?content=true</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>DNS resolves, ports 443 and 80 closed. Acquired by DV Trading Dec 2021; DV's board is already watched as dvtrading-greenhouse.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 172 postings, 10 US student rows</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>AlphaGrep Securities</t>
+          <t>bti36021</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>alphagrep</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>alphagrepsecurities (greenhouse)</t>
+          <t>greenhouse:bti36021</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>https://boards-api.greenhouse.io/v1/boards/bti36021/jobs?content=true</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>16 jobs including a 2027 Campus Program, but every location is India/China/Singapore - zero US rows now or historically.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 12 postings, 1 US student rows</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>AlphaSimplex</t>
+          <t>chicagotradingcampus</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>alphasimplex</t>
+          <t>greenhouse:chicagotradingcampus</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>https://www.alphasimplex.com/</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/chicagotradingcampus/jobs?content=true</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Acquired by Virtus (closed Apr 2023). The Workday board that answers is all-Virtus sales/advisory, not quant.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 8 postings, 4 US student rows</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Arb Trading Group</t>
+          <t>compeerfinancial</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>arb-trading-group</t>
+          <t>greenhouse:compeerfinancial</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>https://arb-tg.com/</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/compeerfinancial/jobs?content=true</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,775-char Webflow site, every careers path 404. arbtrading.com is a catch-all serving the same page for all 22 paths - a trap that would look healthy.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 67 postings, 0 US student rows</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Citadel (hedge fund)</t>
+          <t>cssmerge</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>citadel</t>
+          <t>greenhouse:cssmerge</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>https://www.citadel.com/careers/students/</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/cssmerge/jobs?content=true</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>403 Cloudflare intermittently (1 of 3 fetches over 12 samples); homepage always 403. An intermittent block is worse than a hard one - it would fire spurious source failures. method=manual is correct.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 245 postings, 2 US student rows</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Consolidated Trading</t>
+          <t>ctccampusboard</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>consolidated-trading</t>
+          <t>greenhouse:ctccampusboard</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>http://consolidatedtrading.com/</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/ctccampusboard/jobs?content=true</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,086 chars with no careers content, all careers paths 404, HTTPS handshake fails.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 6 postings, 4 US student rows</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Cutler Group</t>
+          <t>devtechnology</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>cutler-group</t>
+          <t>greenhouse:devtechnology</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>https://cutlerllc.com/</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/devtechnology/jobs?content=true</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224 chars, under the floor; WP REST shows two pages total. NOTE cutlergroup.com is a Canadian bathroom-vanity manufacturer - wrong company.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 26 postings, 5 US student rows</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Dark Forest Technologies</t>
+          <t>eulerity</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>dark-forest-tech</t>
+          <t>greenhouse:eulerity</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>https://darkforesttech.com/</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/eulerity/jobs?content=true</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>231 chars, under the floor. A single GitHub Pages placeholder; recruiting@darkforesttech.com only.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 17 postings, 6 US student rows</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Eisler Capital</t>
+          <t>gallup</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>eisler-capital</t>
+          <t>greenhouse:gallup</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>https://eislercapital.com</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/gallup/jobs?content=true</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>DEFUNCT: no A record; www CNAMEs to a torn-down CloudFront distribution. Flagship wound down 31 Dec 2025.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 54 postings, 5 US student rows</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Emergent Trading</t>
+          <t>gardacp</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>emergent-trading</t>
+          <t>greenhouse:gardacp</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>https://www.emergenttrading.com/join</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/gardacp/jobs?content=true</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Ember.js shell: /join is the real careers route and returns 0 chars. App and vendor bundles grepped, no ATS and no fetch target.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 14 postings, 4 US student rows</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Freestone Grove Partners</t>
+          <t>generalmatter</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>freestone-grove</t>
+          <t>greenhouse:generalmatter</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.gem.com/freestone-grove-partners</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/generalmatter/jobs?content=true</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Gem JS shell, 32 chars. Board verified real but empty: the GraphQL POST returns jobPostings: []. Worth re-probing later.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 132 postings, 24 US student rows</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs Emerging Leaders Series</t>
+          <t>hpiq</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>goldman-emerging-leaders</t>
+          <t>greenhouse:hpiq</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships/americas/emerging-leaders-series</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/hpiq/jobs?content=true</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>403 Akamai. higher.gs.com/roles returns 200 but 29 chars (JS shell). Programme is live for 2026 but only reachable at edition-specific Avature URLs that expire.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 32 postings, 7 US student rows</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Kinetic Trading Partners</t>
+          <t>hudl</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>kinetic-trading-partners</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+          <t>greenhouse:hudl</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>https://boards-api.greenhouse.io/v1/boards/hudl/jobs?content=true</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Zero LinkedIn results, absent from every quant directory checked. The name collides with Kinetic Partners Management LP, Kinetix Trading Solutions and retail prop-firm affiliate sites.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 31 postings, 3 US student rows</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Laurion Capital</t>
+          <t>idmeuniversityrecruiting</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>laurion-capital</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>laurioncapitalmanagement (greenhouse)</t>
+          <t>greenhouse:idmeuniversityrecruiting</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>https://boards-api.greenhouse.io/v1/boards/idmeuniversityrecruiting/jobs?content=true</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Slug resolves but the board has 0 postings. A permanently empty board can only ever look healthy-and-quiet, so it is not added - same call as optiver/marshallwace in Phase 2.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 7 postings, 7 US student rows</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Nico Trading</t>
+          <t>k2spacecorporation</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>nico-trading</t>
+          <t>greenhouse:k2spacecorporation</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>https://nicotrading.com</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/k2spacecorporation/jobs?content=true</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114-byte GoDaddy parking redirect, 0 chars. Firm operating but web-dark.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 219 postings, 9 US student rows</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Numerai</t>
+          <t>klaviyocampus</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>numerai</t>
+          <t>greenhouse:klaviyocampus</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>https://numer.ai/careers</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/klaviyocampus/jobs?content=true</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>404. No first-party careers page; Wellfound 403s us and Built In serves nav boilerplate with zero titles.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 3 postings, 2 US student rows</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Quantitative Investment Management</t>
+          <t>nisc</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>qim</t>
+          <t>greenhouse:nisc</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>https://quantitative.com/</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/nisc/jobs?content=true</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Every path 404 while robots.txt returns 200 - the site is genuinely unpublished, not blocking us. Firm is still an active RIA.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 39 postings, 8 US student rows</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Quantbox Research</t>
+          <t>pacificfusion</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>quantbox-research</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>quantboxresearchpte (greenhouse)</t>
+          <t>greenhouse:pacificfusion</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>https://boards-api.greenhouse.io/v1/boards/pacificfusion/jobs?content=true</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7 jobs, junior roles are Amsterdam/Singapore only.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 37 postings, 5 US student rows</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Quantlab Financial</t>
+          <t>testnisc</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>quantlab</t>
+          <t>greenhouse:testnisc</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>https://www.quantlab.com/careers</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/testnisc/jobs?content=true</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>403 S3 AccessDenied, 26 chars. Its Jobvite board returns 200 with 237 chars (empty, under the 500 floor) and redirects back into the block.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 37 postings, 9 US student rows</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>QVR Advisors</t>
+          <t>tgsmc</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>qvr-advisors</t>
+          <t>lever:tgsmc</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>https://qvradvisors.com</t>
+          <t>https://api.lever.co/v0/postings/tgsmc?mode=json</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>DEFUNCT: homepage rewritten to past tense ('was formerly a boutique SEC-registered investment advisor'). Closing after ~30% losses Jan-Apr 2026.</t>
+          <t>found in the HTML of tgs-join-our-team, which is watched as page_text; not in sources.csv; API returns 0 postings, 0 US student rows</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Rosetta Analytics</t>
+          <t>Chieler/Summer-2027-SWE-Internships</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>repo</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>rosetta-analytics</t>
+          <t>repo:chieler/summer-2027-swe-internships</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>https://rosetta-analytics.com/</t>
+          <t>https://github.com/Chieler/Summer-2027-SWE-Internships</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>DEFUNCT: 114 bytes, 0 chars, JS redirect to a parking lander. Closed March 2025.</t>
+          <t>26 stars, pushed 2026-09-13; matched "Summer 2027 Internships"</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Sensato Investors</t>
+          <t>sndsh404/summer-2027-internships</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>repo</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>sensato-investors</t>
+          <t>repo:sndsh404/summer-2027-internships</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>https://sensatoinvestors.com</t>
+          <t>https://github.com/sndsh404/summer-2027-internships</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>HTTPS TLS internal error; over http, 27KB of HTML yields 44 chars. No careers link anywhere.</t>
+          <t>934 stars, pushed 2026-08-03; matched "Summer 2027 Internships"</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Spot Trading</t>
+          <t>vanshb03/Summer2027-Internships</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>repo</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>spot-trading</t>
+          <t>repo:vanshb03/summer2027-internships</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>https://spottradingllc.com</t>
+          <t>https://github.com/vanshb03/Summer2027-Internships</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>DEFUNCT: 'Coming Soon' placeholder, 40 chars. Firm closed 28 Feb 2018.</t>
+          <t>9045 stars, pushed 2026-08-23; matched "Summer 2027 Internships"</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -18248,7 +18256,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Summerside Capital</t>
+          <t>Allston Trading</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -18258,13 +18266,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>summerside-capital</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
+          <t>allston-trading</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>https://allstontrading.com</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>No A record on five domain variants. No trading firm of this name appears to exist.</t>
+          <t>DNS resolves, ports 443 and 80 closed. Acquired by DV Trading Dec 2021; DV's board is already watched as dvtrading-greenhouse.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -18286,7 +18298,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Tyler Capital</t>
+          <t>AlphaGrep Securities</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -18296,17 +18308,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>tyler-capital</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>https://www.tylercapital.co.uk/</t>
+          <t>alphagrep</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>alphagrepsecurities (greenhouse)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Watchable (2,093 chars) but states explicitly: 'we don't run an internship or graduate recruitment program'. UK-only. Not worth a row.</t>
+          <t>16 jobs including a 2027 Campus Program, but every location is India/China/Singapore - zero US rows now or historically.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -18328,7 +18340,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>WH Trading</t>
+          <t>AlphaSimplex</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -18338,17 +18350,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>wh-trading</t>
+          <t>alphasimplex</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>https://whtrading.com/life-at-wh-trading/</t>
+          <t>https://www.alphasimplex.com/</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Page is 2,320 chars but lists no roles; /careers and /jobs 404. Hiring via opportunities@whtrading.com only.</t>
+          <t>Acquired by Virtus (closed Apr 2023). The Workday board that answers is all-Virtus sales/advisory, not quant.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -18370,65 +18382,1046 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
+          <t>Arb Trading Group</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>arb-trading-group</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>https://arb-tg.com/</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>4,775-char Webflow site, every careers path 404. arbtrading.com is a catch-all serving the same page for all 22 paths - a trap that would look healthy.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Citadel (hedge fund)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>citadel</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.citadel.com/careers/students/</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>403 Cloudflare intermittently (1 of 3 fetches over 12 samples); homepage always 403. An intermittent block is worse than a hard one - it would fire spurious source failures. method=manual is correct.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated Trading</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>consolidated-trading</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>http://consolidatedtrading.com/</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1,086 chars with no careers content, all careers paths 404, HTTPS handshake fails.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Cutler Group</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>cutler-group</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>https://cutlerllc.com/</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>224 chars, under the floor; WP REST shows two pages total. NOTE cutlergroup.com is a Canadian bathroom-vanity manufacturer - wrong company.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Dark Forest Technologies</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>dark-forest-tech</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>https://darkforesttech.com/</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>231 chars, under the floor. A single GitHub Pages placeholder; recruiting@darkforesttech.com only.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Eisler Capital</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>eisler-capital</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>https://eislercapital.com</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>DEFUNCT: no A record; www CNAMEs to a torn-down CloudFront distribution. Flagship wound down 31 Dec 2025.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Emergent Trading</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>emergent-trading</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.emergenttrading.com/join</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Ember.js shell: /join is the real careers route and returns 0 chars. App and vendor bundles grepped, no ATS and no fetch target.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Freestone Grove Partners</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>freestone-grove</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.gem.com/freestone-grove-partners</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Gem JS shell, 32 chars. Board verified real but empty: the GraphQL POST returns jobPostings: []. Worth re-probing later.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Goldman Sachs Emerging Leaders Series</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>goldman-emerging-leaders</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships/americas/emerging-leaders-series</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>403 Akamai. higher.gs.com/roles returns 200 but 29 chars (JS shell). Programme is live for 2026 but only reachable at edition-specific Avature URLs that expire.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Kinetic Trading Partners</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>kinetic-trading-partners</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Zero LinkedIn results, absent from every quant directory checked. The name collides with Kinetic Partners Management LP, Kinetix Trading Solutions and retail prop-firm affiliate sites.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Laurion Capital</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>laurion-capital</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>laurioncapitalmanagement (greenhouse)</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Slug resolves but the board has 0 postings. A permanently empty board can only ever look healthy-and-quiet, so it is not added - same call as optiver/marshallwace in Phase 2.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Nico Trading</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>nico-trading</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>https://nicotrading.com</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>114-byte GoDaddy parking redirect, 0 chars. Firm operating but web-dark.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Numerai</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>numerai</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>https://numer.ai/careers</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>404. No first-party careers page; Wellfound 403s us and Built In serves nav boilerplate with zero titles.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Quantitative Investment Management</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>qim</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>https://quantitative.com/</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Every path 404 while robots.txt returns 200 - the site is genuinely unpublished, not blocking us. Firm is still an active RIA.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Quantbox Research</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>quantbox-research</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>quantboxresearchpte (greenhouse)</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>7 jobs, junior roles are Amsterdam/Singapore only.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Quantlab Financial</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>quantlab</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.quantlab.com/careers</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>403 S3 AccessDenied, 26 chars. Its Jobvite board returns 200 with 237 chars (empty, under the 500 floor) and redirects back into the block.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>QVR Advisors</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>qvr-advisors</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>https://qvradvisors.com</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>DEFUNCT: homepage rewritten to past tense ('was formerly a boutique SEC-registered investment advisor'). Closing after ~30% losses Jan-Apr 2026.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Rosetta Analytics</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>rosetta-analytics</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>https://rosetta-analytics.com/</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>DEFUNCT: 114 bytes, 0 chars, JS redirect to a parking lander. Closed March 2025.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Sensato Investors</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>sensato-investors</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>https://sensatoinvestors.com</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>HTTPS TLS internal error; over http, 27KB of HTML yields 44 chars. No careers link anywhere.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Spot Trading</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>spot-trading</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>https://spottradingllc.com</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>DEFUNCT: 'Coming Soon' placeholder, 40 chars. Firm closed 28 Feb 2018.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Summerside Capital</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>summerside-capital</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>No A record on five domain variants. No trading firm of this name appears to exist.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Tyler Capital</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>tyler-capital</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tylercapital.co.uk/</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Watchable (2,093 chars) but states explicitly: 'we don't run an internship or graduate recruitment program'. UK-only. Not worth a row.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>WH Trading</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>wh-trading</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>https://whtrading.com/life-at-wh-trading/</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Page is 2,320 chars but lists no roles; /careers and /jobs 404. Hiring via opportunities@whtrading.com only.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>XR Trading</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>firm</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>xr-trading</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>https://www.xrtrading.com/</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Paylocity React shell: board returns 670 chars, all of it 'unsupported browser' boilerplate, zero titles. Bundle grepped - no JSON endpoint exists.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H28"/>
+  <autoFilter ref="A1:H51"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>9f94bdf7c297d22169d8a6e0e0413c94ff4a6cd02a1b6464a87b49ba2b6c9bb9</t>
+          <t>d51d9f66f8476698fa50ad70f823fea06ed1bb0169c8665a5f2a1f4315a30a2d</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8729,17 +8729,17 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>open</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="L157" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>354e8229c45e114d1b9a08f856918cb1d9faba977a578b3417b1c84b5f02ef8d</t>
+          <t>60a880796c08ba895b63ab55bdaee867faf3afedf8135ba2a56f16e08682874a</t>
         </is>
       </c>
     </row>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12385,7 +12385,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12503,7 +12503,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12583,7 +12583,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -13493,7 +13493,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14019,7 +14019,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14469,7 +14469,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14797,7 +14797,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -14965,7 +14965,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15259,7 +15259,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15381,7 +15381,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15549,7 +15549,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15633,7 +15633,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15675,7 +15675,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15759,7 +15759,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16209,7 +16209,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16457,7 +16457,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16495,7 +16495,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16537,7 +16537,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16575,7 +16575,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16613,7 +16613,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -16883,7 +16883,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -16921,7 +16921,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -16959,7 +16959,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -16997,7 +16997,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -17073,7 +17073,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-14T16:06:55+00:00</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>d51d9f66f8476698fa50ad70f823fea06ed1bb0169c8665a5f2a1f4315a30a2d</t>
+          <t>cacbfe1bfa8c253bb724a3ee875c67a9087abb488e1c1d42c24c6c1e016bc977</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8002,12 +8002,12 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T16:42:35+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="L145" s="2" t="inlineStr"/>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>770702cb19ea8d996aed49851c54d2d3a4bc930f4c445257f7e6626ae1b193e8</t>
+          <t>1f1887cdb2115241c55873db773039a5495f8440af9d0148b518fe01ffa1fc4f</t>
         </is>
       </c>
     </row>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12385,7 +12385,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12503,7 +12503,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12583,7 +12583,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -13493,7 +13493,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -13688,7 +13688,7 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14019,7 +14019,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14062,7 +14062,7 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14184,7 +14184,7 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14469,7 +14469,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14512,7 +14512,7 @@
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14676,7 +14676,7 @@
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14797,7 +14797,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -14965,7 +14965,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15259,7 +15259,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15344,7 +15344,7 @@
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -15381,7 +15381,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15549,7 +15549,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15633,7 +15633,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15675,7 +15675,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15759,7 +15759,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -15886,7 +15886,7 @@
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16008,7 +16008,7 @@
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -16046,7 +16046,7 @@
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16209,7 +16209,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16457,7 +16457,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16495,7 +16495,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16537,7 +16537,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16575,7 +16575,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16613,7 +16613,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -16883,7 +16883,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -16921,7 +16921,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -16959,7 +16959,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -16997,7 +16997,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -17073,7 +17073,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-15T20:43:53+00:00</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -17285,7 +17285,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -17327,7 +17327,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -17369,12 +17369,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>chicagotradingcampus</t>
+          <t>compeerfinancial</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:chicagotradingcampus</t>
+          <t>greenhouse:compeerfinancial</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/chicagotradingcampus/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/compeerfinancial/jobs?content=true</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 8 postings, 4 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 67 postings, 0 US student rows</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -17411,12 +17411,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>compeerfinancial</t>
+          <t>cssmerge</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -17426,17 +17426,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:compeerfinancial</t>
+          <t>greenhouse:cssmerge</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/compeerfinancial/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/cssmerge/jobs?content=true</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 67 postings, 0 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 245 postings, 2 US student rows</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -17453,12 +17453,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>cssmerge</t>
+          <t>devtechnology</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -17468,17 +17468,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:cssmerge</t>
+          <t>greenhouse:devtechnology</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/cssmerge/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/devtechnology/jobs?content=true</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 245 postings, 2 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 26 postings, 5 US student rows</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -17495,12 +17495,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ctccampusboard</t>
+          <t>eulerity</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -17510,17 +17510,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:ctccampusboard</t>
+          <t>greenhouse:eulerity</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/ctccampusboard/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/eulerity/jobs?content=true</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 6 postings, 4 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 17 postings, 6 US student rows</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -17537,12 +17537,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>devtechnology</t>
+          <t>gallup</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -17552,17 +17552,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:devtechnology</t>
+          <t>greenhouse:gallup</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/devtechnology/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/gallup/jobs?content=true</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 26 postings, 5 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 54 postings, 5 US student rows</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -17579,12 +17579,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>eulerity</t>
+          <t>generalmatter</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -17594,17 +17594,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:eulerity</t>
+          <t>greenhouse:generalmatter</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/eulerity/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/generalmatter/jobs?content=true</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 17 postings, 6 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 132 postings, 24 US student rows</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -17621,12 +17621,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>gallup</t>
+          <t>hpiq</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -17636,17 +17636,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:gallup</t>
+          <t>greenhouse:hpiq</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/gallup/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/hpiq/jobs?content=true</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 54 postings, 5 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 32 postings, 7 US student rows</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -17663,12 +17663,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>gardacp</t>
+          <t>hudl</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -17678,17 +17678,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:gardacp</t>
+          <t>greenhouse:hudl</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/gardacp/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/hudl/jobs?content=true</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 14 postings, 4 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 31 postings, 3 US student rows</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -17705,12 +17705,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>generalmatter</t>
+          <t>idmeuniversityrecruiting</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -17720,17 +17720,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:generalmatter</t>
+          <t>greenhouse:idmeuniversityrecruiting</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/generalmatter/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/idmeuniversityrecruiting/jobs?content=true</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 132 postings, 24 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 7 postings, 7 US student rows</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -17747,12 +17747,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>hpiq</t>
+          <t>k2spacecorporation</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -17762,17 +17762,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:hpiq</t>
+          <t>greenhouse:k2spacecorporation</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/hpiq/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/k2spacecorporation/jobs?content=true</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 32 postings, 7 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 219 postings, 9 US student rows</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -17789,12 +17789,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>hudl</t>
+          <t>klaviyocampus</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -17804,17 +17804,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:hudl</t>
+          <t>greenhouse:klaviyocampus</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/hudl/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/klaviyocampus/jobs?content=true</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 31 postings, 3 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 3 postings, 2 US student rows</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -17831,12 +17831,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>idmeuniversityrecruiting</t>
+          <t>nisc</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -17846,17 +17846,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:idmeuniversityrecruiting</t>
+          <t>greenhouse:nisc</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/idmeuniversityrecruiting/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/nisc/jobs?content=true</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 7 postings, 7 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 39 postings, 8 US student rows</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -17873,12 +17873,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>k2spacecorporation</t>
+          <t>pacificfusion</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -17888,17 +17888,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:k2spacecorporation</t>
+          <t>greenhouse:pacificfusion</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/k2spacecorporation/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/pacificfusion/jobs?content=true</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 219 postings, 9 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 37 postings, 5 US student rows</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -17915,12 +17915,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>klaviyocampus</t>
+          <t>testnisc</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -17930,17 +17930,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:klaviyocampus</t>
+          <t>greenhouse:testnisc</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/klaviyocampus/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/testnisc/jobs?content=true</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 3 postings, 2 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 37 postings, 9 US student rows</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -17957,32 +17957,32 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>nisc</t>
+          <t>Chieler/Summer-2027-SWE-Internships</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>repo</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:nisc</t>
+          <t>repo:chieler/summer-2027-swe-internships</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/nisc/jobs?content=true</t>
+          <t>https://github.com/Chieler/Summer-2027-SWE-Internships</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 39 postings, 8 US student rows</t>
+          <t>26 stars, pushed 2026-09-13; matched "Summer 2027 Internships"</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -17999,32 +17999,32 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>pacificfusion</t>
+          <t>sndsh404/summer-2027-internships</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>repo</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:pacificfusion</t>
+          <t>repo:sndsh404/summer-2027-internships</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/pacificfusion/jobs?content=true</t>
+          <t>https://github.com/sndsh404/summer-2027-internships</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 37 postings, 5 US student rows</t>
+          <t>934 stars, pushed 2026-08-03; matched "Summer 2027 Internships"</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -18046,7 +18046,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>testnisc</t>
+          <t>chicagotradingcampus</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -18056,17 +18056,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:testnisc</t>
+          <t>greenhouse:chicagotradingcampus</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/testnisc/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/chicagotradingcampus/jobs?content=true</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 37 postings, 9 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 8 postings, 4 US student rows</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -18088,27 +18088,27 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>tgsmc</t>
+          <t>ctccampusboard</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>lever:tgsmc</t>
+          <t>greenhouse:ctccampusboard</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>https://api.lever.co/v0/postings/tgsmc?mode=json</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/ctccampusboard/jobs?content=true</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>found in the HTML of tgs-join-our-team, which is watched as page_text; not in sources.csv; API returns 0 postings, 0 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 6 postings, 4 US student rows</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -18130,27 +18130,27 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Chieler/Summer-2027-SWE-Internships</t>
+          <t>gardacp</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>repo</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>repo:chieler/summer-2027-swe-internships</t>
+          <t>greenhouse:gardacp</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Chieler/Summer-2027-SWE-Internships</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/gardacp/jobs?content=true</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26 stars, pushed 2026-09-13; matched "Summer 2027 Internships"</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 14 postings, 4 US student rows</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -18172,27 +18172,27 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>sndsh404/summer-2027-internships</t>
+          <t>tgsmc</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>repo</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>repo:sndsh404/summer-2027-internships</t>
+          <t>lever:tgsmc</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sndsh404/summer-2027-internships</t>
+          <t>https://api.lever.co/v0/postings/tgsmc?mode=json</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>934 stars, pushed 2026-08-03; matched "Summer 2027 Internships"</t>
+          <t>found in the HTML of tgs-join-our-team, which is watched as page_text; not in sources.csv; API returns 0 postings, 0 US student rows</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12385,7 +12385,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12503,7 +12503,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12583,7 +12583,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -13493,7 +13493,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14019,7 +14019,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14469,7 +14469,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14797,7 +14797,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -14965,7 +14965,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15259,7 +15259,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15381,7 +15381,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15549,7 +15549,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15633,7 +15633,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15675,7 +15675,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15759,7 +15759,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16209,7 +16209,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16457,7 +16457,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16495,7 +16495,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16537,7 +16537,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16575,7 +16575,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16613,7 +16613,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -16883,7 +16883,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -16921,7 +16921,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -16959,7 +16959,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -16997,7 +16997,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -17073,7 +17073,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T20:43:53+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>cacbfe1bfa8c253bb724a3ee875c67a9087abb488e1c1d42c24c6c1e016bc977</t>
+          <t>1c646d305b4c280a09f1fdcebc43895d8416592b0361b8f5e27f07ae39a0f064</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12385,7 +12385,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12503,7 +12503,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12583,7 +12583,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -13493,7 +13493,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13767,12 +13767,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14019,7 +14019,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14469,7 +14469,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14797,7 +14797,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -14965,7 +14965,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15259,7 +15259,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15381,7 +15381,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15549,7 +15549,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15633,7 +15633,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15675,7 +15675,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15759,7 +15759,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -15970,7 +15970,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16209,7 +16209,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16457,7 +16457,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16495,7 +16495,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16537,7 +16537,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16575,7 +16575,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16613,7 +16613,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -16883,7 +16883,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -16921,7 +16921,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -16959,7 +16959,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -16997,7 +16997,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -17073,7 +17073,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Programs'!$A$1:$N$188</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$H$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$H$149</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Applied'!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Discovered'!$A$1:$H$51</definedName>
   </definedNames>
@@ -2982,7 +2982,11 @@
           <t>Write market-making bots against an open exchange.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>akunacapital-greenhouse</t>
+        </is>
+      </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -3086,7 +3090,11 @@
           <t>Options crash course: risk management, game theory, decision making.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>akunacapital-greenhouse</t>
+        </is>
+      </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -10714,7 +10722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H158"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -11538,7 +11546,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>capstone-greenhouse</t>
+          <t>chicagotrading-greenhouse</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -11548,13 +11556,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Chicago Trading Company (CTC)</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>capstoneinvestmentadvisors</t>
+          <t>chicagotrading</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -11569,14 +11581,14 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The capstone-careers row's note claimed the firm was on no public ATS; it is not true. 12 postings, 0 early-career today.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 25 jobs.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>chicagotrading-greenhouse</t>
+          <t>drweng-greenhouse</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -11586,17 +11598,13 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Chicago Trading Company (CTC)</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>chicagotrading</t>
+          <t>drweng</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11611,14 +11619,14 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 25 jobs.</t>
+          <t>DRW. Verified 2026-09-11: 157 postings, 8 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>drweng-greenhouse</t>
+          <t>dvtrading-greenhouse</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -11634,7 +11642,7 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>drweng</t>
+          <t>dvtrading</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -11649,14 +11657,14 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>DRW. Verified 2026-09-11: 157 postings, 8 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>DV Trading. Verified 2026-09-11: 67 postings, 11 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>dvtrading-greenhouse</t>
+          <t>eclipse-greenhouse</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -11672,7 +11680,7 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>dvtrading</t>
+          <t>eclipsetrading</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -11687,14 +11695,14 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>DV Trading. Verified 2026-09-11: 67 postings, 11 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The eclipse-careers row's note claimed the firm was on no public ATS; it is not true. 18 postings, 4 early-career ('Graduate Trader | 2027 Intake'). Slug was only visible in a grnhse_app embed script on eclipsetrading.com/all-jobs/.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>eclipse-greenhouse</t>
+          <t>engineersgate-greenhouse</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -11704,13 +11712,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Engineers Gate</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>eclipsetrading</t>
+          <t>engineersgate</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -11725,14 +11737,14 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The eclipse-careers row's note claimed the firm was on no public ATS; it is not true. 18 postings, 4 early-career ('Graduate Trader | 2027 Intake'). Slug was only visible in a grnhse_app embed script on eclipsetrading.com/all-jobs/.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 7 jobs.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>engineersgate-greenhouse</t>
+          <t>exoduspoint-greenhouse</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -11747,12 +11759,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Engineers Gate</t>
+          <t>ExodusPoint Capital</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>engineersgate</t>
+          <t>exoduspoint</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -11767,14 +11779,14 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 7 jobs.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 2 jobs.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>exoduspoint-greenhouse</t>
+          <t>fiveringsllc-greenhouse</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -11784,17 +11796,13 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>ExodusPoint Capital</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>exoduspoint</t>
+          <t>fiveringsllc</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11809,14 +11817,14 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 2 jobs.</t>
+          <t>Five Rings. Verified 2026-09-11: 16 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>fiveringsllc-greenhouse</t>
+          <t>flowtraders-greenhouse</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -11832,7 +11840,7 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>fiveringsllc</t>
+          <t>flowtraders</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -11847,14 +11855,14 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Five Rings. Verified 2026-09-11: 16 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Flow Traders. Verified 2026-09-11: 41 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>flowtraders-greenhouse</t>
+          <t>gelber-greenhouse</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -11864,13 +11872,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Gelber Group</t>
+        </is>
+      </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>flowtraders</t>
+          <t>gelbergroup</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -11885,14 +11897,14 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Flow Traders. Verified 2026-09-11: 41 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 8 jobs.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>gelber-greenhouse</t>
+          <t>genevatrading-greenhouse</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -11902,17 +11914,13 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Gelber Group</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>gelbergroup</t>
+          <t>genevatrading</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -11927,14 +11935,14 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 8 jobs.</t>
+          <t>Geneva Trading. Verified 2026-09-11: 10 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>genevatrading-greenhouse</t>
+          <t>gsacapital-greenhouse</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -11944,13 +11952,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>GSA Capital</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>genevatrading</t>
+          <t>gsacapital</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -11965,14 +11977,14 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Geneva Trading. Verified 2026-09-11: 10 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 independently of the agent report: 9 jobs, 1 US student (Quantitative Researcher - Intern, London/New York). GSA was NOT acquired by Eisler - it converted to a proprietary firm in Nov 2021 and hires actively.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>graham-greenhouse</t>
+          <t>gsr-greenhouse</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -11988,7 +12000,7 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>grahamcapitalmanagement</t>
+          <t>gsrmarkets</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -12003,14 +12015,14 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The graham-careers row's note claimed the firm was on no public ATS; it is not true. 7 postings, 0 early-career today.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The gsr-careers row's note claimed the firm was on no public ATS; it is not true. 5 postings, 0 early-career today. Advertised on the EU host, but boards-api.eu.greenhouse.io does not resolve and the plain host serves the slug fine.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>gsacapital-greenhouse</t>
+          <t>headlands-greenhouse</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -12020,17 +12032,13 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>GSA Capital</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>gsacapital</t>
+          <t>headlandstechnologiesllc</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -12045,14 +12053,14 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 independently of the agent report: 9 jobs, 1 US student (Quantitative Researcher - Intern, London/New York). GSA was NOT acquired by Eisler - it converted to a proprietary firm in Nov 2021 and hires actively.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The headlands-careers row's note claimed the firm was on no public ATS; it is not true. 7 postings, 1 early-career ('Quantitative Researcher - New Grad'). The page_text row stays: headlands-careers does enumerate roles inline.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>gsr-greenhouse</t>
+          <t>hrt-greenhouse</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -12068,7 +12076,7 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>gsrmarkets</t>
+          <t>hrttalentcommunity</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -12083,14 +12091,14 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The gsr-careers row's note claimed the firm was on no public ATS; it is not true. 5 postings, 0 early-career today. Advertised on the EU host, but boards-api.eu.greenhouse.io does not resolve and the plain host serves the slug fine.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The hrt-careers / hrt-student-opportunities row's note claimed the firm was on no public ATS; it is not true. 3 postings, 2 early-career ('Campus Talent Community', 'FPGA Verification and Developer (Internships and Campus Full-time)'). Both HRT page_text rows claimed no public ATS.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>headlands-greenhouse</t>
+          <t>hyannisportresearch-greenhouse</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -12106,7 +12114,7 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>headlandstechnologiesllc</t>
+          <t>hyannisportresearch</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -12121,14 +12129,14 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The headlands-careers row's note claimed the firm was on no public ATS; it is not true. 7 postings, 1 early-career ('Quantitative Researcher - New Grad'). The page_text row stays: headlands-careers does enumerate roles inline.</t>
+          <t>Hyannisport Research. Verified 2026-09-11: 10 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>hrt-greenhouse</t>
+          <t>imc-greenhouse</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -12144,7 +12152,7 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>hrttalentcommunity</t>
+          <t>imc</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -12159,14 +12167,14 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The hrt-careers / hrt-student-opportunities row's note claimed the firm was on no public ATS; it is not true. 3 postings, 2 early-career ('Campus Talent Community', 'FPGA Verification and Developer (Internships and Campus Full-time)'). Both HRT page_text rows claimed no public ATS.</t>
+          <t>IMC. Verified 2026-09-11: 170 postings, 7 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>hyannisportresearch-greenhouse</t>
+          <t>janestreet-greenhouse</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -12182,7 +12190,7 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>hyannisportresearch</t>
+          <t>janestreet</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -12197,14 +12205,14 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Hyannisport Research. Verified 2026-09-11: 10 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Jane Street. Verified 2026-09-11: 230 postings, 20 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>imc-greenhouse</t>
+          <t>jumpcrypto-greenhouse</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -12214,13 +12222,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Jump Crypto</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>imc</t>
+          <t>jumpcrypto</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -12235,14 +12247,14 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>IMC. Verified 2026-09-11: 170 postings, 7 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 5 jobs.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>janestreet-greenhouse</t>
+          <t>jumptrading-greenhouse</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -12258,7 +12270,7 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>janestreet</t>
+          <t>jumptrading</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -12273,14 +12285,14 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Jane Street. Verified 2026-09-11: 230 postings, 20 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Jump Trading. Verified 2026-09-11: 106 postings, 10 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>jumpcrypto-greenhouse</t>
+          <t>mako-greenhouse</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -12290,17 +12302,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Jump Crypto</t>
+          <t>Mako Global</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>jumpcrypto</t>
+          <t>mako</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -12315,14 +12327,14 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 5 jobs.</t>
+          <t>Verified 2026-09-11 independently of the agent report: 8 jobs, 0 US student today (graduate roles are Sydney/London). Watched for when a US role appears.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>jumptrading-greenhouse</t>
+          <t>mangroup-greenhouse</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -12332,13 +12344,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Man Group / AHL / Numeric</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>jumptrading</t>
+          <t>mangroup</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -12353,14 +12369,14 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Jump Trading. Verified 2026-09-11: 106 postings, 10 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 53 jobs.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>mako-greenhouse</t>
+          <t>mavensecuritiesholdingltd-greenhouse</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -12373,14 +12389,10 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Mako Global</t>
-        </is>
-      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>mako</t>
+          <t>mavensecuritiesholdingltd</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -12395,14 +12407,14 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 independently of the agent report: 8 jobs, 0 US student today (graduate roles are Sydney/London). Watched for when a US role appears.</t>
+          <t>Maven Securities. Verified 2026-09-11: 46 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>mangroup-greenhouse</t>
+          <t>oldmissioncapital-greenhouse</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -12412,17 +12424,13 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Man Group / AHL / Numeric</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>mangroup</t>
+          <t>oldmissioncapital</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -12437,14 +12445,14 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 53 jobs.</t>
+          <t>Old Mission. Verified 2026-09-11: 38 postings, 3 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>mavensecuritiesholdingltd-greenhouse</t>
+          <t>optiverprivate-greenhouse</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -12460,7 +12468,7 @@
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>mavensecuritiesholdingltd</t>
+          <t>optiverprivate</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -12475,14 +12483,14 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Maven Securities. Verified 2026-09-11: 46 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Optiver. Verified 2026-09-11: 10 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>oldmissioncapital-greenhouse</t>
+          <t>optiverus-greenhouse</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -12492,13 +12500,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Optiver US</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>oldmissioncapital</t>
+          <t>optiverus</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -12513,14 +12525,14 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Old Mission. Verified 2026-09-11: 38 postings, 3 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 163 jobs. The `optiver` and `optiverprivate` slugs return 0 and 1; this is the live US board.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>optiverprivate-greenhouse</t>
+          <t>pdtpartners-greenhouse</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -12536,7 +12548,7 @@
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>optiverprivate</t>
+          <t>pdtpartners</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -12551,14 +12563,14 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Optiver. Verified 2026-09-11: 10 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>PDT Partners. Verified 2026-09-11: 9 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>optiverus-greenhouse</t>
+          <t>point72-greenhouse</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -12573,12 +12585,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Optiver US</t>
+          <t>Point72 / Cubist</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>optiverus</t>
+          <t>point72</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -12593,14 +12605,14 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 163 jobs. The `optiver` and `optiverprivate` slugs return 0 and 1; this is the live US board.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 227 jobs.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>pdtpartners-greenhouse</t>
+          <t>quadrature-greenhouse</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -12610,13 +12622,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Quadrature Capital</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>pdtpartners</t>
+          <t>quadraturecapital</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -12631,14 +12647,14 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>PDT Partners. Verified 2026-09-11: 9 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 4 jobs.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>point72-greenhouse</t>
+          <t>quantbot-greenhouse</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -12648,17 +12664,13 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Point72 / Cubist</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>point72</t>
+          <t>quantbot-technologies</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -12673,14 +12685,14 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 227 jobs.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The quantbot-careers row's note claimed the firm was on no public ATS; it is not true. 7 postings, all 7 early-career: 'Quantitative Researcher Internship - 2027 [NY/London/HK]', 'Data Trading Analyst Summer Internship - 2027'.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>quadrature-greenhouse</t>
+          <t>qube-greenhouse</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -12695,12 +12707,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Quadrature Capital</t>
+          <t>Qube Research &amp; Technologies</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>quadraturecapital</t>
+          <t>quberesearchandtechnologies</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -12715,14 +12727,14 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 4 jobs.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 198 jobs.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>quantbot-greenhouse</t>
+          <t>radix-greenhouse</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -12732,13 +12744,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Radix Trading</t>
+        </is>
+      </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>quantbot-technologies</t>
+          <t>radixuniversity</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -12753,14 +12769,14 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The quantbot-careers row's note claimed the firm was on no public ATS; it is not true. 7 postings, all 7 early-career: 'Quantitative Researcher Internship - 2027 [NY/London/HK]', 'Data Trading Analyst Summer Internship - 2027'.</t>
+          <t>Verified 2026-09-11 independently of the agent report: 8 jobs, 1 US student (Quantitative Technologist, C++ Intern - Chicago). The `radix` and `radixexperienced` slugs are the wrong board and the experienced board respectively.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>qube-greenhouse</t>
+          <t>schonfeld-greenhouse</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -12770,17 +12786,13 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Qube Research &amp; Technologies</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>quberesearchandtechnologies</t>
+          <t>schonfeld</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -12795,14 +12807,14 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 198 jobs.</t>
+          <t>Schonfeld. Verified 2026-09-11: 71 postings, 13 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>radix-greenhouse</t>
+          <t>sevenresearch-greenhouse</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -12812,17 +12824,13 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Radix Trading</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>radixuniversity</t>
+          <t>sevenresearch</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -12837,14 +12845,14 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 independently of the agent report: 8 jobs, 1 US student (Quantitative Technologist, C++ Intern - Chicago). The `radix` and `radixexperienced` slugs are the wrong board and the experienced board respectively.</t>
+          <t>Seven Research. Verified 2026-09-11: 8 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>schonfeld-greenhouse</t>
+          <t>simplex-greenhouse</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -12854,13 +12862,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Simplex Trading</t>
+        </is>
+      </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>schonfeld</t>
+          <t>simplextrading</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -12875,14 +12887,14 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Schonfeld. Verified 2026-09-11: 71 postings, 13 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 5 jobs.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>sevenresearch-greenhouse</t>
+          <t>squarepoint-greenhouse</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -12892,13 +12904,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Squarepoint Capital</t>
+        </is>
+      </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>sevenresearch</t>
+          <t>squarepointcapital</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -12913,14 +12929,14 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Seven Research. Verified 2026-09-11: 8 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 93 jobs.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>simplex-greenhouse</t>
+          <t>towerresearch-greenhouse</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -12930,17 +12946,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Simplex Trading</t>
+          <t>Tower Research Capital</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>simplextrading</t>
+          <t>towerresearchcapital</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -12955,14 +12971,14 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 5 jobs.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 86 jobs. Richer than the tower-careers page watcher, which is kept as a second signal.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>squarepoint-greenhouse</t>
+          <t>transmarketgroup-greenhouse</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -12972,17 +12988,13 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Squarepoint Capital</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>squarepointcapital</t>
+          <t>transmarketgroup</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12997,14 +13009,14 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 93 jobs.</t>
+          <t>TransMarket Group. Verified 2026-09-11: 19 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>towerresearch-greenhouse</t>
+          <t>tudor-greenhouse</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -13014,17 +13026,13 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Tower Research Capital</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>towerresearchcapital</t>
+          <t>tudorgroup</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -13039,14 +13047,14 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 86 jobs. Richer than the tower-careers page watcher, which is kept as a second signal.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The tudor-careers row's note claimed the firm was on no public ATS; it is not true. 4 postings, 0 early-career today.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>transmarketgroup-greenhouse</t>
+          <t>vaticlabs-greenhouse</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -13062,7 +13070,7 @@
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>transmarketgroup</t>
+          <t>vaticlabs</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -13077,14 +13085,14 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>TransMarket Group. Verified 2026-09-11: 19 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Vatic Labs. Verified 2026-09-11: 9 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>tudor-greenhouse</t>
+          <t>verition-greenhouse</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -13100,7 +13108,7 @@
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>tudorgroup</t>
+          <t>veritiongroupllc</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -13115,14 +13123,14 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The tudor-careers row's note claimed the firm was on no public ATS; it is not true. 4 postings, 0 early-career today.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The verition-careers row's note claimed the firm was on no public ATS; it is not true. 32 postings, 3 early-career ('2027 Investment/Technology/Platform Internship (US)'). Slug was only visible in a grnhse_app embed script on verition.com/open-positions.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>vaticlabs-greenhouse</t>
+          <t>virtu-greenhouse</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -13138,7 +13146,7 @@
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>vaticlabs</t>
+          <t>virtu</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -13153,14 +13161,14 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Vatic Labs. Verified 2026-09-11: 9 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Virtu Financial. Verified 2026-09-11: 50 postings, 6 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>verition-greenhouse</t>
+          <t>voloridge-greenhouse</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -13170,13 +13178,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Voloridge / Ascend Program</t>
+        </is>
+      </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>veritiongroupllc</t>
+          <t>voloridgeinvestmentmanagement</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -13191,14 +13203,14 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The verition-careers row's note claimed the firm was on no public ATS; it is not true. 32 postings, 3 early-career ('2027 Investment/Technology/Platform Internship (US)'). Slug was only visible in a grnhse_app embed script on verition.com/open-positions.</t>
+          <t>Verified 2026-09-11: 8 jobs, 4 US student rows including ASCEND PROGRAM 2027 - one of the very few programmes whose stated eligibility is 'first and second-year undergraduate students', so it is open to class of 2030 now. Two bugs had to be fixed before this row worked: 'Ascend Program 2027' contains no 'intern' and was only caught once the title screen learned Summer-Analyst/year vocabulary, and its location reads 'Jupiter, Florida' while the rest of the board reads 'Jupiter, FL', so the US filter dropped exactly this posting until it learned spelled-out state names.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>virtu-greenhouse</t>
+          <t>walleyecapital-external-students-greenhouse</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -13214,7 +13226,7 @@
       <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>virtu</t>
+          <t>walleyecapital-external-students</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -13229,14 +13241,14 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Virtu Financial. Verified 2026-09-11: 50 postings, 6 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Walleye Capital. Verified 2026-09-11: 3 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>voloridge-greenhouse</t>
+          <t>winton-greenhouse</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -13246,17 +13258,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Voloridge / Ascend Program</t>
+          <t>Winton</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>voloridgeinvestmentmanagement</t>
+          <t>winton</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -13271,14 +13283,14 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 8 jobs, 4 US student rows including ASCEND PROGRAM 2027 - one of the very few programmes whose stated eligibility is 'first and second-year undergraduate students', so it is open to class of 2030 now. Two bugs had to be fixed before this row worked: 'Ascend Program 2027' contains no 'intern' and was only caught once the title screen learned Summer-Analyst/year vocabulary, and its location reads 'Jupiter, Florida' while the rest of the board reads 'Jupiter, FL', so the US filter dropped exactly this posting until it learned spelled-out state names.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 10 jobs.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>walleyecapital-external-students-greenhouse</t>
+          <t>worldquant-greenhouse</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -13294,7 +13306,7 @@
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>walleyecapital-external-students</t>
+          <t>worldquant</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -13309,14 +13321,14 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Walleye Capital. Verified 2026-09-11: 3 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>WorldQuant. Verified 2026-09-11: 103 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>winton-greenhouse</t>
+          <t>xtxmarkets-greenhouse</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -13326,17 +13338,13 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Winton</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>winton</t>
+          <t>xtxmarketstechnologies</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -13351,19 +13359,19 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 10 jobs.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The xtx-careers row's note claimed the firm was on no public ATS; it is not true. 10 postings, 1 early-career ('AI Research Internship - XTY Labs').</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>worldquant-greenhouse</t>
+          <t>belvederetrading-lever</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -13374,7 +13382,7 @@
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>worldquant</t>
+          <t>belvederetrading</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -13389,19 +13397,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>WorldQuant. Verified 2026-09-11: 103 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Belvedere Trading. Verified 2026-09-11: 14 postings, 3 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>xtxmarkets-greenhouse</t>
+          <t>valkyrietrading-lever</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -13412,7 +13420,7 @@
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>xtxmarketstechnologies</t>
+          <t>valkyrietrading</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -13427,37 +13435,37 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The xtx-careers row's note claimed the firm was on no public ATS; it is not true. 10 postings, 1 early-career ('AI Research Internship - XTY Labs').</t>
+          <t>Valkyrie Trading. Verified 2026-09-11: 6 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>belvederetrading-lever</t>
+          <t>citadel-students</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>belvederetrading</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T12:40:49+00:00</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Citadel students</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.citadel.com/careers/students/</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13465,37 +13473,37 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Belvedere Trading. Verified 2026-09-11: 14 postings, 3 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>method=manual on purpose. Re-tested 2026-09-11: 403 Forbidden to state.USER_AGENT, HTTP 200 to a spoofed browser User-Agent. The block is deliberate and UA-based, so the only way to automate this page is to lie about who we are - declined. Surfaces as a monthly calendar reminder instead. An earlier note claiming 6,763 chars of text was measured with a browser-presenting fetcher, not with this tool's client.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>valkyrietrading-lever</t>
+          <t>citadelsecurities-careers</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>valkyrietrading</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T12:40:49+00:00</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Citadel Securities</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>https://www.citadelsecurities.com/careers</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13503,14 +13511,14 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Valkyrie Trading. Verified 2026-09-11: 6 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>method=manual on purpose. Sampled 10x on 2026-09-11: HTTP 200 in 5 of 10 fetches, 403 Cloudflare in the other 5, all with state.USER_AGENT. An earlier note here claimed the page was readable at 10,638 chars - that was a single lucky sample, the same error made on citadel.com the same day. An INTERMITTENT block is worse than a hard one: the source would report a failure on roughly half of all runs and escalate into ACT NOW after three, so it must not be automated. Re-sample repeatedly, never once, before moving any Citadel row off manual.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>citadel-students</t>
+          <t>kaggle-competitions</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -13520,17 +13528,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Citadel students</t>
+          <t>Kaggle Competitions (all active)</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>https://www.citadel.com/careers/students/</t>
+          <t>https://www.kaggle.com/api/v1/competitions/list</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
@@ -13541,14 +13549,14 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>method=manual on purpose. Re-tested 2026-09-11: 403 Forbidden to state.USER_AGENT, HTTP 200 to a spoofed browser User-Agent. The block is deliberate and UA-based, so the only way to automate this page is to lie about who we are - declined. Surfaces as a monthly calendar reminder instead. An earlier note claiming 6,763 chars of text was measured with a browser-presenting fetcher, not with this tool's client.</t>
+          <t>MANUAL. Kaggle competitions are always-open and rolling, so a daily diff is noise rather than news; calendar_reminders.ALWAYS already covers them. Dropped from Phase 2 deliberately.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>citadelsecurities-careers</t>
+          <t>thedeckgame</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -13563,12 +13571,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Citadel Securities</t>
+          <t>The Deck Game</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers</t>
+          <t>https://thedeckgame.com/</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -13579,37 +13587,41 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>method=manual on purpose. Sampled 10x on 2026-09-11: HTTP 200 in 5 of 10 fetches, 403 Cloudflare in the other 5, all with state.USER_AGENT. An earlier note here claimed the page was readable at 10,638 chars - that was a single lucky sample, the same error made on citadel.com the same day. An INTERMITTENT block is worse than a hard one: the source would report a failure on roughly half of all runs and escalate into ACT NOW after three, so it must not be automated. Re-sample repeatedly, never once, before moving any Citadel row off manual.</t>
+          <t>MANUAL. Verified: JS shell yielding ~28 characters; sitemap has only two URLs. Not worth a Playwright run - there is nothing to diff.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>kaggle-competitions</t>
+          <t>albatross-labs</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Kaggle Competitions (all active)</t>
+          <t>Albatross Labs</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/api/v1/competitions/list</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr"/>
+          <t>https://www.albatrosslabs.io/</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T12:40:49+00:00</t>
+        </is>
+      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13617,19 +13629,19 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>MANUAL. Kaggle competitions are always-open and rolling, so a daily diff is noise rather than news; calendar_reminders.ALWAYS already covers them. Dropped from Phase 2 deliberately.</t>
+          <t>Verified 2026-09-11: 2,390 chars, ratio 0.0055 - above the 0.0015 floor but the thinnest ratio on the watchlist. Advertises Software/Quant Developer at internship level.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>thedeckgame</t>
+          <t>aqr-internship-program</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -13639,15 +13651,19 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>The Deck Game</t>
+          <t>AQR internship programme</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>https://thedeckgame.com/</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr"/>
+          <t>https://www.aqr.com/About-Us/Our-Internship-Program</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T12:40:49+00:00</t>
+        </is>
+      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -13655,14 +13671,14 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>MANUAL. Verified: JS shell yielding ~28 characters; sitemap has only two URLs. Not worth a Playwright run - there is nothing to diff.</t>
+          <t>BROKEN 2026-09-12 and not re-pointable: /About-Us/Our-Internship-Program now 302s to aqr.com/404, and /Careers plus /careers/internships both redirect to the homepage while /Insights/Careers and /About-Us/Careers 404. careers.aqr.com is a JS shell (0 chars of text). It had been reporting success off the 404 page's own prose (4,683 chars at ratio 0.0929) since some point after 2026-09-11, when it last verified at 8,992 chars. The redirect check now fails it loudly. ELIGIBILITY RESEARCH AT RISK: this row existed because the programme page stated eligibility that the board rows do not -- that text is gone and needs re-verifying by hand. Coverage of the postings themselves is not lost: aqr-greenhouse carries 54 postings including 12+ '2027 ... Summer Analyst' roles.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>akuna-academy</t>
+          <t>aspect-careers</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -13677,30 +13693,34 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Akuna Academy</t>
+          <t>Aspect Capital</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>https://akunacapital.com/careers</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr"/>
+          <t>https://www.aspectcapital.com/careers/</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T12:40:49+00:00</t>
+        </is>
+      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Carries Akuna Academy. Verified 2026-09-11: 1,304 chars.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 8,724 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>albatross-labs</t>
+          <t>bam-internships</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -13710,17 +13730,17 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Albatross Labs</t>
+          <t>Balyasny (BAM)</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>https://www.albatrosslabs.io/</t>
+          <t>https://www.bamfunds.com/careers/internships</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -13735,14 +13755,14 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 2,390 chars, ratio 0.0055 - above the 0.0015 floor but the thinnest ratio on the watchlist. Advertises Software/Quant Developer at internship level.</t>
+          <t>Verified 2026-09-11: 3,394 chars. Programme page only: BAM's Salesforce ATS is a 60-character shell, so individual reqs are not reachable.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>aqr-internship-program</t>
+          <t>bluefin-careers</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -13752,17 +13772,17 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>AQR internship programme</t>
+          <t>Bluefin Companies</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>https://www.aqr.com/About-Us/Our-Internship-Program</t>
+          <t>https://www.bfcm.com/careers/</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -13777,14 +13797,14 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>BROKEN 2026-09-12 and not re-pointable: /About-Us/Our-Internship-Program now 302s to aqr.com/404, and /Careers plus /careers/internships both redirect to the homepage while /Insights/Careers and /About-Us/Careers 404. careers.aqr.com is a JS shell (0 chars of text). It had been reporting success off the 404 page's own prose (4,683 chars at ratio 0.0929) since some point after 2026-09-11, when it last verified at 8,992 chars. The redirect check now fails it loudly. ELIGIBILITY RESEARCH AT RISK: this row existed because the programme page stated eligibility that the board rows do not -- that text is gone and needs re-verifying by hand. Coverage of the postings themselves is not lost: aqr-greenhouse carries 54 postings including 12+ '2027 ... Summer Analyst' roles.</t>
+          <t>Verified 2026-09-11: 740 chars, close to the 500 floor. Renamed from Bluefin Trading; applications by email.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>aspect-careers</t>
+          <t>blueshift-careers</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -13794,17 +13814,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Aspect Capital</t>
+          <t>Blueshift Asset Management</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>https://www.aspectcapital.com/careers/</t>
+          <t>https://www.blueshift.am/</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13819,14 +13839,14 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 8,724 chars of text.</t>
+          <t>Verified 2026-09-11: 5,636 chars. Quantitative Analyst (MS/PhD) only. Note blueshift.com is marketing SaaS.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>bam-internships</t>
+          <t>brevanhoward-students</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -13836,17 +13856,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Balyasny (BAM)</t>
+          <t>Brevan Howard students</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>https://www.bamfunds.com/careers/internships</t>
+          <t>https://www.brevanhoward.com/students/</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -13861,14 +13881,14 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 3,394 chars. Programme page only: BAM's Salesforce ATS is a 60-character shell, so individual reqs are not reachable.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 2,375 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>bluefin-careers</t>
+          <t>bridgewater-students</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -13878,17 +13898,17 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Bluefin Companies</t>
+          <t>Bridgewater students</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>https://www.bfcm.com/careers/</t>
+          <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -13903,14 +13923,14 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 740 chars, close to the 500 floor. Renamed from Bluefin Trading; applications by email.</t>
+          <t>Students page. bridgewater.com/careers yields less (2,326). Verified 2026-09-11: 4,624 chars.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>blueshift-careers</t>
+          <t>capula-workable</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -13920,17 +13940,17 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Blueshift Asset Management</t>
+          <t>Capula Investment Management</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>https://www.blueshift.am/</t>
+          <t>https://apply.workable.com/api/v1/widget/accounts/capula-investment-management-ltd</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -13945,14 +13965,14 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 5,636 chars. Quantitative Analyst (MS/PhD) only. Note blueshift.com is marketing SaaS.</t>
+          <t>Verified 2026-09-11: Workable JSON widget, 8,015 chars, ratio 0.997. Carries '2027 Trading and Research Summer Internship' and 'Technology Graduate Analyst'. Read as page_text because the tracker has no Workable parser; the feed is deterministic so a text diff is stable.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>brevanhoward-students</t>
+          <t>cboe-careers</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -13967,12 +13987,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Brevan Howard students</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>https://www.brevanhoward.com/students/</t>
+          <t>https://careers.cboe.com/us/en</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -13987,14 +14007,14 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 2,375 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 4,717 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>bridgewater-students</t>
+          <t>deshaw-careers</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -14004,17 +14024,17 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Bridgewater students</t>
+          <t>D. E. Shaw</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
+          <t>https://www.deshaw.com/careers</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -14029,14 +14049,14 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Students page. bridgewater.com/careers yields less (2,326). Verified 2026-09-11: 4,624 chars.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 36,840 chars of text. deshaw.com/careers/students renders nothing (0 chars); /careers is the readable one.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>capstone-careers</t>
+          <t>eagleseven-careers</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -14046,35 +14066,39 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Capstone Investment Advisors</t>
+          <t>Eagle Seven</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>https://www.capstoneco.com/careers</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr"/>
+          <t>https://www.eagleseven.com/</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T12:40:49+00:00</t>
+        </is>
+      </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 2,890 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- capstone-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Verified 2026-09-11: 15,784 chars. 'Junior Trader' is the most junior role today. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- eagleseven-workable watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>capula-workable</t>
+          <t>eagleseven-workable</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -14084,17 +14108,13 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Capula Investment Management</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>https://apply.workable.com/api/v1/widget/accounts/capula-investment-management-ltd</t>
+          <t>https://apply.workable.com/api/v1/widget/accounts/eagle-seven</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -14109,14 +14129,14 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: Workable JSON widget, 8,015 chars, ratio 0.997. Carries '2027 Trading and Research Summer Internship' and 'Technology Graduate Analyst'. Read as page_text because the tracker has no Workable parser; the feed is deterministic so a text diff is stable.</t>
+          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The eagleseven-careers row's note claimed the firm was on no public ATS; it is not true. 5 postings. Watched as page_text on the Workable widget JSON, the same shape as the existing capula-workable row, because there is no workable method.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>cboe-careers</t>
+          <t>eclipse-careers</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -14126,17 +14146,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>Eclipse Trading</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>https://careers.cboe.com/us/en</t>
+          <t>https://www.eclipsetrading.com/careers/</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -14151,14 +14171,14 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 4,717 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 2,270 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- eclipse-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>crabel-careers</t>
+          <t>edgehog-rippling</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -14173,30 +14193,34 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Crabel Capital</t>
+          <t>Edgehog Trading</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>https://crabel.com/careers/</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr"/>
+          <t>https://api.rippling.com/platform/api/ats/v1/board/edgehog-trading/jobs</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T12:40:49+00:00</t>
+        </is>
+      </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 5,540 chars of text.</t>
+          <t>Verified 2026-09-11: Rippling ATS JSON, 14 jobs, 3,171 chars, ratio 0.79. Graduate Quant Trader, Graduate SWE, Junior FPGA Developer.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>deshaw-careers</t>
+          <t>eschaton-careers</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -14206,17 +14230,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>D. E. Shaw</t>
+          <t>Eschaton Trading</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>https://www.deshaw.com/careers</t>
+          <t>https://www.eschatontrading.com/careers</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -14231,14 +14255,14 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 36,840 chars of text. deshaw.com/careers/students renders nothing (0 chars); /careers is the readable one.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 2,184 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>eagleseven-careers</t>
+          <t>garda-careers</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -14248,17 +14272,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Eagle Seven</t>
+          <t>Garda Capital Partners</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>https://www.eagleseven.com/</t>
+          <t>https://www.gardacp.com/careers/</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -14273,14 +14297,14 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 15,784 chars. 'Junior Trader' is the most junior role today. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- eagleseven-workable watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Verified 2026-09-11: 5,287 chars. Six internships live, including SWE Intern (NY) and Trading Analyst Intern across Credit/Mortgages/Rates.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>eagleseven-workable</t>
+          <t>gresearch-careers</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -14290,13 +14314,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>G-Research</t>
+        </is>
+      </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>https://apply.workable.com/api/v1/widget/accounts/eagle-seven</t>
+          <t>https://www.gresearch.com/careers/</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -14311,14 +14339,14 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The eagleseven-careers row's note claimed the firm was on no public ATS; it is not true. 5 postings. Watched as page_text on the Workable widget JSON, the same shape as the existing capula-workable row, because there is no workable method.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 1,801 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>eclipse-careers</t>
+          <t>group1-careers</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -14328,17 +14356,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Eclipse Trading</t>
+          <t>Group One Trading</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>https://www.eclipsetrading.com/careers/</t>
+          <t>https://group1.com/careers/</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -14353,14 +14381,14 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 2,270 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- eclipse-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Verified 2026-09-11: 3,990 chars. Trading Analyst Intern and Software Developer Intern. Also advertises a STANFORD CAREER FAIR on 6 Oct 2026 - see calendar_reminders.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>edgehog-rippling</t>
+          <t>gsr-careers</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -14370,17 +14398,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Edgehog Trading</t>
+          <t>GSR Markets</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>https://api.rippling.com/platform/api/ats/v1/board/edgehog-trading/jobs</t>
+          <t>https://www.gsr.io/careers</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -14395,14 +14423,14 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: Rippling ATS JSON, 14 jobs, 3,171 chars, ratio 0.79. Graduate Quant Trader, Graduate SWE, Junior FPGA Developer.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 5,216 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- gsr-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>eschaton-careers</t>
+          <t>gts-careers</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -14412,24 +14440,20 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Eschaton Trading</t>
+          <t>GTS</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>https://www.eschatontrading.com/careers</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T12:40:49+00:00</t>
-        </is>
-      </c>
+          <t>https://careers-gtsx.icims.com/jobs/search?ss=1&amp;in_iframe=1</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14437,14 +14461,14 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 2,184 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 18,734 chars of text. Correction 2026-09-16: "no public ATS" was false. GTS is on iCIMS at careers-gtsx.icims.com, linked from the careers page as a button; the project does not fingerprint iCIMS, so the discovery probe never saw it. Re-pointed at the board itself, which is vendor-hosted (CNAME wildcard.cloud.icims.tools) and so outside the WAF that was returning 403 to the Actions runner on gtsx.com. The in_iframe=1 parameter is load-bearing: without it the response is the WordPress wrapper, 2,877 chars at ratio 0.017. With it, 10,156 chars at 0.241, including "Quantitative Trader - 2027 Graduates".</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>garda-careers</t>
+          <t>harvard-undergraduate-trading</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -14459,12 +14483,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Garda Capital Partners</t>
+          <t>Harvard Undergraduate Trading Competition</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>https://www.gardacp.com/careers/</t>
+          <t>https://www.huqt.com/</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -14479,14 +14503,14 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 5,287 chars. Six internships live, including SWE Intern (NY) and Trading Analyst Intern across Credit/Mortgages/Rates.</t>
+          <t>Probed 2026-09-06: 200, 1654 chars of text over plain HTTP, no robots.txt. Use huqt.com - the article's harvarduqt.com/competition redirects to a 404.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>graham-careers</t>
+          <t>headlands-careers</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -14496,35 +14520,39 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Graham Capital</t>
+          <t>Headlands Technologies</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>https://www.grahamcapital.com/careers/</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr"/>
+          <t>https://www.headlandstech.com/careers/</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T12:40:49+00:00</t>
+        </is>
+      </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 18,019 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- graham-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 28,067 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- headlands-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>gresearch-careers</t>
+          <t>hedgewest-sf-meetup-series</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -14539,12 +14567,12 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>G-Research</t>
+          <t>HedgeWest SF Meetup Series</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>https://www.gresearch.com/careers/</t>
+          <t>https://hedgewestsf.org/</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -14559,14 +14587,14 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 1,801 chars of text.</t>
+          <t>Probed 2026-09-06: 200, 837 chars of text over plain HTTP.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>group1-careers</t>
+          <t>hrt-careers</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -14581,12 +14609,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Group One Trading</t>
+          <t>Hudson River Trading</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>https://group1.com/careers/</t>
+          <t>https://www.hudsonrivertrading.com/careers/?_departments=internships</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -14601,14 +14629,14 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 3,990 chars. Trading Analyst Intern and Software Developer Intern. Also advertises a STANFORD CAREER FAIR on 6 Oct 2026 - see calendar_reminders.</t>
+          <t>HRT is on no public ATS. Verified 2026-09-11: 5,598 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- hrt-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>gsr-careers</t>
+          <t>hrt-student-opportunities</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -14618,17 +14646,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>GSR Markets</t>
+          <t>HRT Inside HRT</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>https://www.gsr.io/careers</t>
+          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -14643,14 +14671,14 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 5,216 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- gsr-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Programme page. Carries Inside HRT, a three-day programme for FIRST and second-year students - the eligibility band this owner is actually in. Verified 2026-09-11: 13,510 chars. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- hrt-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>gts-careers</t>
+          <t>iaqf-academic-paper-competition</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -14665,30 +14693,34 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>GTS</t>
+          <t>IAQF Academic Paper Competition</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>https://gtsx.com/careers/</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr"/>
+          <t>https://www.iaqf.org/upcoming-events</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T12:40:49+00:00</t>
+        </is>
+      </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 18,734 chars of text.</t>
+          <t>Probed 2026-09-06: 200, 8194 chars of text over plain HTTP.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>harvard-undergraduate-trading</t>
+          <t>imc-launchpad-us</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -14703,12 +14735,12 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Harvard Undergraduate Trading Competition</t>
+          <t>IMC Launchpad (US)</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>https://www.huqt.com/</t>
+          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -14723,14 +14755,14 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 1654 chars of text over plain HTTP, no robots.txt. Use huqt.com - the article's harvarduqt.com/competition redirects to a 404.</t>
+          <t>Probed 2026-09-06: 200, 2450 chars of text over plain HTTP.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>headlands-careers</t>
+          <t>janestreet-bridge</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -14745,12 +14777,12 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Headlands Technologies</t>
+          <t>Jane Street Bridge</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>https://www.headlandstech.com/careers/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/bridge/</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -14765,14 +14797,14 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 28,067 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- headlands-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Programme page for first- and second-years. Verified 2026-09-11: 4,111 chars.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>hedgewest-sf-meetup-series</t>
+          <t>janestreet-fttp</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -14787,12 +14819,12 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>HedgeWest SF Meetup Series</t>
+          <t>Jane Street FTTP</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>https://hedgewestsf.org/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -14807,14 +14839,14 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 837 chars of text over plain HTTP.</t>
+          <t>Programme page, not the board. Jane Street's Greenhouse board has no FTTP listing at all, and this page carries the apply button. Rolling review. Verified 2026-09-11: 3,393 chars.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>hrt-careers</t>
+          <t>janestreet-insight</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -14829,12 +14861,12 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Hudson River Trading</t>
+          <t>Jane Street INSIGHT</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>https://www.hudsonrivertrading.com/careers/?_departments=internships</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -14849,14 +14881,14 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>HRT is on no public ATS. Verified 2026-09-11: 5,598 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- hrt-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Programme page for INSIGHT, Jane Street's first-year programme. Verified 2026-09-11: 4,780 chars.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>hrt-student-opportunities</t>
+          <t>janestreet-internships</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -14871,12 +14903,12 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>HRT Inside HRT</t>
+          <t>Jane Street internships</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
+          <t>https://www.janestreet.com/join-jane-street/internships/</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -14891,14 +14923,14 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Programme page. Carries Inside HRT, a three-day programme for FIRST and second-year students - the eligibility band this owner is actually in. Verified 2026-09-11: 13,510 chars. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- hrt-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Verified 2026-09-11: 5,956 chars.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>iaqf-academic-paper-competition</t>
+          <t>janestreet-programs</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -14913,12 +14945,12 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>IAQF Academic Paper Competition</t>
+          <t>Jane Street programs and events</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>https://www.iaqf.org/upcoming-events</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -14933,14 +14965,14 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 8194 chars of text over plain HTTP.</t>
+          <t>Index of every Jane Street programme; catches a new one appearing. Verified 2026-09-11: 5,997 chars.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>imc-launchpad-us</t>
+          <t>kore-careers</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -14950,17 +14982,17 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>IMC Launchpad (US)</t>
+          <t>Kore Trading</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
+          <t>https://www.koretrading.com/front-page/careers/</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -14975,14 +15007,14 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 2450 chars of text over plain HTTP.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 1,485 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>janestreet-bridge</t>
+          <t>lynx-teamtailor</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -14992,17 +15024,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Jane Street Bridge</t>
+          <t>Lynx Asset Management</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/bridge/</t>
+          <t>https://careers.lynxhedge.se/jobs.json</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -15017,14 +15049,14 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Programme page for first- and second-years. Verified 2026-09-11: 4,111 chars.</t>
+          <t>Verified 2026-09-11: Teamtailor JSON feed, 17,592 chars, ratio 0.993. Tags a Hackathon 2026 row as [Student Opportunity].</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>janestreet-fttp</t>
+          <t>marquette-careers</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -15034,17 +15066,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Jane Street FTTP</t>
+          <t>Marquette Partners</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
+          <t>https://www.marquettepartnersholdingsllc.com/careers</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -15059,14 +15091,14 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Programme page, not the board. Jane Street's Greenhouse board has no FTTP listing at all, and this page carries the apply button. Rolling review. Verified 2026-09-11: 3,393 chars.</t>
+          <t>Verified 2026-09-11: 4,406 chars. Experienced only today.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>janestreet-insight</t>
+          <t>mit-battlecode-2027</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -15081,12 +15113,12 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Jane Street INSIGHT</t>
+          <t>MIT Battlecode 2027</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
+          <t>https://battlecode.org/</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -15101,14 +15133,14 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Programme page for INSIGHT, Jane Street's first-year programme. Verified 2026-09-11: 4,780 chars.</t>
+          <t>Probed: HTTP 200, 1,627 chars of visible text over plain HTTP, no robots.txt. Home page carries the live season banner ('Battlecode 2026 ended on January 31st, 2026!'), so a text diff should catch the 2027 announcement.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>janestreet-internships</t>
+          <t>open-source-quantitative-finance</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -15123,12 +15155,12 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Jane Street internships</t>
+          <t>Open Source Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/internships/</t>
+          <t>https://osqf.org/</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -15143,14 +15175,14 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 5,956 chars.</t>
+          <t>Probed 2026-09-06: 200, 1966 chars of text over plain HTTP.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>janestreet-programs</t>
+          <t>optiver-futurefocus</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -15165,12 +15197,12 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Jane Street programs and events</t>
+          <t>Optiver FutureFocus</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://www.optiver.com/join-us/students/programs/futurefocus/</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -15185,14 +15217,14 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Index of every Jane Street programme; catches a new one appearing. Verified 2026-09-11: 5,997 chars.</t>
+          <t>Programme page for FutureFocus, Optiver's five-day discovery programme, which the page states is for FIRST and second-year students. Renamed and re-pointed 2026-09-11: the old id and URL (optiver-futurefocus-chicago-2026, /recruitment-events/futurefocus-chicago) baked in a city and a year, and the old URL now 301s here. Verified 2026-09-11: 4,591 chars. Note the page states no graduation-year window, only 'first and second-year', so eligibility cannot be confirmed from it the way Susquehanna's postings can - read the application itself before trusting the label.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>kore-careers</t>
+          <t>optiver-ready-trader</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -15202,17 +15234,17 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Kore Trading</t>
+          <t>Optiver Ready Trader Go</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>https://www.koretrading.com/front-page/careers/</t>
+          <t>https://readytradergo.optiver.com/</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -15227,14 +15259,14 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 1,485 chars of text.</t>
+          <t>PHASE 3. Verified: 200, ~1KB of text over plain HTTP, no JS needed.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>lynx-teamtailor</t>
+          <t>optiver-students</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -15244,17 +15276,17 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Lynx Asset Management</t>
+          <t>Optiver student opportunities</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>https://careers.lynxhedge.se/jobs.json</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/?level=student</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -15269,14 +15301,14 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: Teamtailor JSON feed, 17,592 chars, ratio 0.993. Tags a Hackathon 2026 row as [Student Opportunity].</t>
+          <t>Verified 2026-09-11: 2,349 chars. Optiver's Greenhouse board (optiverprivate) is small, so the student page is the better signal.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>marquette-careers</t>
+          <t>pokerbots</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -15286,17 +15318,17 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Marquette Partners</t>
+          <t>MIT Pokerbots</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>https://www.marquettepartnersholdingsllc.com/careers</t>
+          <t>https://pokerbots.org/</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -15311,14 +15343,14 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 4,406 chars. Experienced only today.</t>
+          <t>PHASE 3. Verified: 200, ~6.2KB of text over plain HTTP, no JS needed. Needs a selector - the page retains announcement banners from 2023-2026 in the markup.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>millennium-students</t>
+          <t>quantbot-careers</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -15328,35 +15360,39 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Millennium students</t>
+          <t>Quantbot Technologies</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>https://www.mlp.com/careers/students/</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr"/>
+          <t>https://www.quantbot.com/careers/</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T12:40:49+00:00</t>
+        </is>
+      </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Millennium is on no public ATS; this students page is the only automatable surface. Verified 2026-09-11: 7,366 chars. CORRECTED 2026-09-12: the "no public ATS" claim above is false -- millennium-eightfold watches campusjobs.mlp.com, which serves 59 campus postings (17 US). This page_text row is kept in case the page carries programme detail the board rows do not state.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 751 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- quantbot-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>mit-battlecode-2027</t>
+          <t>rentec-careers</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -15371,12 +15407,12 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>MIT Battlecode 2027</t>
+          <t>Renaissance Technologies</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>https://battlecode.org/</t>
+          <t>https://www.rentec.com/careers</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -15391,14 +15427,14 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Probed: HTTP 200, 1,627 chars of visible text over plain HTTP, no robots.txt. Home page carries the live season banner ('Battlecode 2026 ended on January 31st, 2026!'), so a text diff should catch the 2027 announcement.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 1,380 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>open-source-quantitative-finance</t>
+          <t>rokos-careers</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -15408,17 +15444,17 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Open Source Quantitative Finance Conference</t>
+          <t>Rokos Capital</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>https://osqf.org/</t>
+          <t>https://www.rokoscapital.com/careers</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -15433,14 +15469,14 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 1966 chars of text over plain HTTP.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 620 chars of text. Close to the 500-char floor; a redesign will trip the shrink guard rather than go quiet.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>optiver-futurefocus</t>
+          <t>stevens-high-frequency-trading</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -15455,12 +15491,12 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Optiver FutureFocus</t>
+          <t>Stevens High Frequency Trading Competition 2026</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>https://www.optiver.com/join-us/students/programs/futurefocus/</t>
+          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -15475,14 +15511,14 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Programme page for FutureFocus, Optiver's five-day discovery programme, which the page states is for FIRST and second-year students. Renamed and re-pointed 2026-09-11: the old id and URL (optiver-futurefocus-chicago-2026, /recruitment-events/futurefocus-chicago) baked in a city and a year, and the old URL now 301s here. Verified 2026-09-11: 4,591 chars. Note the page states no graduation-year window, only 'first and second-year', so eligibility cannot be confirmed from it the way Susquehanna's postings can - read the application itself before trusting the label.</t>
+          <t>Probed 2026-09-06: 200, 10400 chars of text over plain HTTP, robots.txt allows. Cleanly pollable.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>optiver-ready-trader</t>
+          <t>teza-careers</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -15492,17 +15528,17 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Optiver Ready Trader Go</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>https://readytradergo.optiver.com/</t>
+          <t>https://www.teza.com/careers/</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -15517,14 +15553,14 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>PHASE 3. Verified: 200, ~1KB of text over plain HTTP, no JS needed.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 8,134 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- teza-ashby watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>optiver-students</t>
+          <t>tgs-join-our-team</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -15534,17 +15570,17 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Optiver student opportunities</t>
+          <t>TGS Management</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/?level=student</t>
+          <t>https://www.tgsmc.com/join-our-team/</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -15559,14 +15595,14 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 2,349 chars. Optiver's Greenhouse board (optiverprivate) is small, so the student page is the better signal.</t>
+          <t>Verified 2026-09-11: 1,977 chars. The Lever slug `tgsmc` resolves but returns an empty list, so the page is the only non-alerting surface.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>pokerbots</t>
+          <t>tradebot-students</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -15576,17 +15612,17 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>MIT Pokerbots</t>
+          <t>Tradebot Systems</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>https://pokerbots.org/</t>
+          <t>https://www.tradebot.com/careers/students</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -15601,14 +15637,14 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>PHASE 3. Verified: 200, ~6.2KB of text over plain HTTP, no JS needed. Needs a selector - the page retains announcement banners from 2023-2026 in the markup.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 1,253 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>quantbot-careers</t>
+          <t>trexquant-students</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -15623,34 +15659,34 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Quantbot Technologies</t>
+          <t>Trexquant</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>https://www.quantbot.com/careers/</t>
+          <t>https://trexquant.com/careers/students</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-15T21:02:15+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 751 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- quantbot-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 891 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>rentec-careers</t>
+          <t>twosigma-campus</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -15665,19 +15701,15 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Renaissance Technologies</t>
+          <t>Two Sigma</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>https://www.rentec.com/careers</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T12:40:49+00:00</t>
-        </is>
-      </c>
+          <t>https://careers.twosigma.com/careers/OpenRoles/</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15685,14 +15717,14 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 1,380 chars of text.</t>
+          <t>Re-pointed 2026-09-12: the old /careers/students/ url 301'd to the generic /careers/ page and had been reporting success from it. The internships page is the real replacement (9,509 chars, 29 'intern' mentions). No public vendor ATS -- careers.twosigma.com is a custom board with no Greenhouse/Lever/Ashby fingerprint. Correction 2026-09-16: "no public vendor ATS" was wrong in its conclusion though right that there is no Greenhouse/Lever/Ashby fingerprint -- careers.twosigma.com is Avature (CNAME portaltwosigma.avature.net), a vendor ATS this project does not fingerprint. Re-pointed to its OpenRoles listing: 2,676 chars at ratio 0.024, including "AI Research Scientist - Intern [2027 Summer]". Vendor-hosted, so outside the WAF that 403s the runner on www.twosigma.com (WP Engine).</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>rokos-careers</t>
+          <t>vector-roles</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -15707,12 +15739,12 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Rokos Capital</t>
+          <t>Vector Trading (Chicago)</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>https://www.rokoscapital.com/careers</t>
+          <t>https://vectortrading.com/data/roles.json</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -15727,14 +15759,14 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 620 chars of text. Close to the 500-char floor; a redesign will trip the shrink guard rather than go quiet.</t>
+          <t>Verified 2026-09-11: The firm's own roles.json, 5 roles, 11,367 chars. 0 student today. Note vectortrading.io and Ashby `vector` are different companies entirely.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>stevens-high-frequency-trading</t>
+          <t>verition-careers</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -15744,17 +15776,17 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Stevens High Frequency Trading Competition 2026</t>
+          <t>Verition Fund Management</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
+          <t>https://www.verition.com/careers</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -15769,14 +15801,14 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 10400 chars of text over plain HTTP, robots.txt allows. Cleanly pollable.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 11,469 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- verition-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>teza-careers</t>
+          <t>volant-careers</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -15786,17 +15818,17 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>Volant Trading</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>https://www.teza.com/careers/</t>
+          <t>https://volanttrading.com/</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -15811,14 +15843,14 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 8,134 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- teza-ashby watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Verified 2026-09-11: 2,245 chars. Entry-level roles are Hong Kong only today.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>tgs-join-our-team</t>
+          <t>voloridge-join-our-team</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -15828,17 +15860,17 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>TGS Management</t>
+          <t>Voloridge Ascend Program</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>https://www.tgsmc.com/join-our-team/</t>
+          <t>https://www.voloridge.com/join-our-team</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -15853,14 +15885,14 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 1,977 chars. The Lever slug `tgsmc` resolves but returns an empty list, so the page is the only non-alerting surface.</t>
+          <t>Verified 2026-09-11: 9,393 chars. Kept alongside the board because it carries the Ascend eligibility text and cohort size (20 places); board rows carry the posting only.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>tower-careers</t>
+          <t>wincent-careers</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -15870,35 +15902,39 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Tower Research Capital</t>
+          <t>Wincent</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr"/>
+          <t>https://www.wincent.com/careers/</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T12:40:49+00:00</t>
+        </is>
+      </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Tower is on no public ATS. Verified 2026-09-11: 1,233 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 11,076 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>tradebot-students</t>
+          <t>wintermute-careers</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -15913,12 +15949,12 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Tradebot Systems</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>https://www.tradebot.com/careers/students</t>
+          <t>https://www.wintermute.com/company/careers</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -15933,14 +15969,14 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 1,253 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 14,346 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>trexquant-students</t>
+          <t>wolverine-careers</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -15955,34 +15991,34 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Trexquant</t>
+          <t>Wolverine Trading</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>https://trexquant.com/careers/students</t>
+          <t>https://careers.wolve.com/postings.json</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-16T12:40:49+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 891 chars of text.</t>
+          <t>Verified 2026-09-11: Pinpoint ATS JSON, 21 postings, 147,741 chars, ratio 0.99. Re-pointed from wolve.com/careers, which is 1,178 chars with zero student hits, and careers.wolve.com, which is a 317-char shell. Caveat: the feed embeds full HTML descriptions, so a reworded description will diff as changed text - if that turns noisy, write a small Pinpoint parser that keeps descriptions out of the snapshot the way the ATS methods do.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>tudor-careers</t>
+          <t>xtx-careers</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -15992,40 +16028,44 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Tudor Investment</t>
+          <t>XTX Markets</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>https://www.tudor.com/careers/</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr"/>
+          <t>https://www.xtxmarkets.com/careers/</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T12:40:49+00:00</t>
+        </is>
+      </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 3,597 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- tudor-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>XTX is on no public ATS. Verified 2026-09-11: 13,750 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- xtxmarkets-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>twosigma-campus</t>
+          <t>sig-phenom</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>phenom</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -16035,35 +16075,39 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Two Sigma</t>
+          <t>Susquehanna (SIG)</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/careers/internships/</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr"/>
+          <t>https://careers.sig.com/api/jobs</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T12:40:49+00:00</t>
+        </is>
+      </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Re-pointed 2026-09-12: the old /careers/students/ url 301'd to the generic /careers/ page and had been reporting success from it. The internships page is the real replacement (9,509 chars, 29 'intern' mentions). No public vendor ATS -- careers.twosigma.com is a custom board with no Greenhouse/Lever/Ashby fingerprint.</t>
+          <t>Phenom/iCIMS JSON API. Replaces the sig-careers manual row, which was correct about the page (402KB of HTML yields 221 chars) and wrong about the firm: this endpoint answers state.USER_AGENT with 263 postings. Verified 2026-09-11: 52 US student rows across Interns + Co-ops, New Graduates and Student Discovery Program. The five US Discovery Programs are gated to winter 2028 / spring 2029 graduates, i.e. sophomores for a four-year US degree, so they are correctly ruled out for class of 2030 until the autumn 2027 cycle.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>vector-roles</t>
+          <t>capitalgroup-workday</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -16071,14 +16115,10 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>Vector Trading (Chicago)</t>
-        </is>
-      </c>
+      <c r="D133" s="2" t="inlineStr"/>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>https://vectortrading.com/data/roles.json</t>
+          <t>https://capgroup.wd1.myworkdayjobs.com/wday/cxs/capgroup/capitalgroupcareers</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -16093,34 +16133,30 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: The firm's own roles.json, 5 roles, 11,367 chars. 0 student today. Note vectortrading.io and Ashby `vector` are different companies entirely.</t>
+          <t>Capital Group. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 1 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>verition-careers</t>
+          <t>cibc-workday</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Verition Fund Management</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr"/>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>https://www.verition.com/careers</t>
+          <t>https://cibc.wd3.myworkdayjobs.com/wday/cxs/cibc/campus</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -16135,34 +16171,34 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 11,469 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- verition-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>CIBC. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 44 postings on the board, 6 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>volant-careers</t>
+          <t>cme-workday</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Volant Trading</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>https://volanttrading.com/</t>
+          <t>https://cmegroup.wd1.myworkdayjobs.com/wday/cxs/cmegroup/cme_careers</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -16177,34 +16213,30 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 2,245 chars. Entry-level roles are Hong Kong only today.</t>
+          <t>Verified 2026-09-11: 33 postings, 0 student today. Use the CXS API only - www.cmegroup.com times out for our User-Agent.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>voloridge-join-our-team</t>
+          <t>dimensional-workday</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Voloridge Ascend Program</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr"/>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>https://www.voloridge.com/join-our-team</t>
+          <t>https://dimensional.wd5.myworkdayjobs.com/wday/cxs/dimensional/dfa_careers</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -16219,34 +16251,30 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 9,393 chars. Kept alongside the board because it carries the Ascend eligibility text and cohort size (20 places); board rows carry the posting only.</t>
+          <t>Dimensional Fund Advisors. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 72 postings on the board, 7 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>wincent-careers</t>
+          <t>draftkings-workday</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Wincent</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr"/>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>https://www.wincent.com/careers/</t>
+          <t>https://draftkings.wd1.myworkdayjobs.com/wday/cxs/draftkings/Campus_Career_Portal</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -16261,34 +16289,30 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 11,076 chars of text.</t>
+          <t>DraftKings. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 7 postings on the board, 6 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>wintermute-careers</t>
+          <t>fanniemae-workday</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Wintermute</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr"/>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>https://www.wintermute.com/company/careers</t>
+          <t>https://fanniemae.wd1.myworkdayjobs.com/wday/cxs/fanniemae/FannieMaeCareers</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -16303,34 +16327,30 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 14,346 chars of text.</t>
+          <t>Fannie Mae. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 61 postings on the board, 6 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>wolverine-careers</t>
+          <t>freddiemac-workday</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Wolverine Trading</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>https://careers.wolve.com/postings.json</t>
+          <t>https://freddiemac.wd5.myworkdayjobs.com/wday/cxs/freddiemac/External</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -16345,34 +16365,30 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: Pinpoint ATS JSON, 21 postings, 147,741 chars, ratio 0.99. Re-pointed from wolve.com/careers, which is 1,178 chars with zero student hits, and careers.wolve.com, which is a 317-char shell. Caveat: the feed embeds full HTML descriptions, so a reworded description will diff as changed text - if that turns noisy, write a small Pinpoint parser that keeps descriptions out of the snapshot the way the ATS methods do.</t>
+          <t>Freddie Mac. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 103 postings on the board, 13 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>xtx-careers</t>
+          <t>kensho-workday</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>XTX Markets</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>https://www.xtxmarkets.com/careers/</t>
+          <t>https://spgi.wd5.myworkdayjobs.com/wday/cxs/spgi/Kensho_Careers</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -16387,34 +16403,30 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>XTX is on no public ATS. Verified 2026-09-11: 13,750 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- xtxmarkets-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Kensho (S&amp;P Global). Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 9 postings on the board, 0 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>sig-phenom</t>
+          <t>lpl-workday</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>phenom</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>Susquehanna (SIG)</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr"/>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/api/jobs</t>
+          <t>https://lplfinancial.wd1.myworkdayjobs.com/wday/cxs/lplfinancial/university</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -16429,14 +16441,14 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Phenom/iCIMS JSON API. Replaces the sig-careers manual row, which was correct about the page (402KB of HTML yields 221 chars) and wrong about the firm: this endpoint answers state.USER_AGENT with 263 postings. Verified 2026-09-11: 52 US student rows across Interns + Co-ops, New Graduates and Student Discovery Program. The five US Discovery Programs are gated to winter 2028 / spring 2029 graduates, i.e. sophomores for a four-year US degree, so they are correctly ruled out for class of 2030 until the autumn 2027 cycle.</t>
+          <t>LPL Financial. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 36 postings on the board, 16 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>capitalgroup-workday</t>
+          <t>mastercard-workday</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -16452,7 +16464,7 @@
       <c r="D142" s="2" t="inlineStr"/>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>https://capgroup.wd1.myworkdayjobs.com/wday/cxs/capgroup/capitalgroupcareers</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/wday/cxs/mastercard/Campus</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -16467,14 +16479,14 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Capital Group. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 1 US student rows.</t>
+          <t>Mastercard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 52 postings on the board, 1 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>cibc-workday</t>
+          <t>northerntrust-workday</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -16490,7 +16502,7 @@
       <c r="D143" s="2" t="inlineStr"/>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>https://cibc.wd3.myworkdayjobs.com/wday/cxs/cibc/campus</t>
+          <t>https://ntrs.wd1.myworkdayjobs.com/wday/cxs/ntrs/northerntrust</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -16505,14 +16517,14 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>CIBC. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 44 postings on the board, 6 US student rows.</t>
+          <t>Northern Trust. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 665 postings on the board, 20 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>cme-workday</t>
+          <t>peak6-workday</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -16522,17 +16534,17 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>PEAK6</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>https://cmegroup.wd1.myworkdayjobs.com/wday/cxs/cmegroup/cme_careers</t>
+          <t>https://peak6group.wd1.myworkdayjobs.com/wday/cxs/peak6group/PEAK6</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -16547,14 +16559,14 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 33 postings, 0 student today. Use the CXS API only - www.cmegroup.com times out for our User-Agent.</t>
+          <t>Verified 2026-09-11: 14 postings, 3 US student rows (Trading Bootcamp Micro-Internship Summer 2027, Trading Internship for Women+ Summer 2027, Trading Associate 2027). Re-pointed from peak6.com/careers, which returns 3,100 chars of marketing copy with no job data and no outbound job links - a row that could only ever look healthy and quiet.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>dimensional-workday</t>
+          <t>pimco-workday</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -16570,7 +16582,7 @@
       <c r="D145" s="2" t="inlineStr"/>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>https://dimensional.wd5.myworkdayjobs.com/wday/cxs/dimensional/dfa_careers</t>
+          <t>https://pimco.wd1.myworkdayjobs.com/wday/cxs/pimco/pimco-careers</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -16585,14 +16597,14 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 72 postings on the board, 7 US student rows.</t>
+          <t>PIMCO. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 195 postings on the board, 7 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>draftkings-workday</t>
+          <t>rbc-workday</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -16608,7 +16620,7 @@
       <c r="D146" s="2" t="inlineStr"/>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>https://draftkings.wd1.myworkdayjobs.com/wday/cxs/draftkings/Campus_Career_Portal</t>
+          <t>https://rbc.wd3.myworkdayjobs.com/wday/cxs/rbc/RBCEARLYTALENT1</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -16623,14 +16635,14 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>DraftKings. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 7 postings on the board, 6 US student rows.</t>
+          <t>RBC Early Talent. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 3 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>fanniemae-workday</t>
+          <t>troweprice-workday</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -16646,7 +16658,7 @@
       <c r="D147" s="2" t="inlineStr"/>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>https://fanniemae.wd1.myworkdayjobs.com/wday/cxs/fanniemae/FannieMaeCareers</t>
+          <t>https://troweprice.wd5.myworkdayjobs.com/wday/cxs/troweprice/TRowePrice</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -16661,14 +16673,14 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>Fannie Mae. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 61 postings on the board, 6 US student rows.</t>
+          <t>T. Rowe Price. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 136 postings on the board, 8 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>freddiemac-workday</t>
+          <t>vanguard-workday</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -16684,7 +16696,7 @@
       <c r="D148" s="2" t="inlineStr"/>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>https://freddiemac.wd5.myworkdayjobs.com/wday/cxs/freddiemac/External</t>
+          <t>https://vanguard.wd5.myworkdayjobs.com/wday/cxs/vanguard/vanguard_external</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -16699,14 +16711,14 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Freddie Mac. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 103 postings on the board, 13 US student rows.</t>
+          <t>Vanguard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 441 postings on the board, 18 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>kensho-workday</t>
+          <t>wellington-workday</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -16722,7 +16734,7 @@
       <c r="D149" s="2" t="inlineStr"/>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>https://spgi.wd5.myworkdayjobs.com/wday/cxs/spgi/Kensho_Careers</t>
+          <t>https://wellington.wd5.myworkdayjobs.com/wday/cxs/wellington/Campus</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -16737,448 +16749,95 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>Kensho (S&amp;P Global). Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 9 postings on the board, 0 US student rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>lpl-workday</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr"/>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>https://lplfinancial.wd1.myworkdayjobs.com/wday/cxs/lplfinancial/university</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T12:40:49+00:00</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>LPL Financial. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 36 postings on the board, 16 US student rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>mastercard-workday</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr"/>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/wday/cxs/mastercard/Campus</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T12:40:49+00:00</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>Mastercard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 52 postings on the board, 1 US student rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>northerntrust-workday</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr"/>
-      <c r="E152" s="3" t="inlineStr">
-        <is>
-          <t>https://ntrs.wd1.myworkdayjobs.com/wday/cxs/ntrs/northerntrust</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T12:40:49+00:00</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>Northern Trust. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 665 postings on the board, 20 US student rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>peak6-workday</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>PEAK6</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>https://peak6group.wd1.myworkdayjobs.com/wday/cxs/peak6group/PEAK6</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T12:40:49+00:00</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>Verified 2026-09-11: 14 postings, 3 US student rows (Trading Bootcamp Micro-Internship Summer 2027, Trading Internship for Women+ Summer 2027, Trading Associate 2027). Re-pointed from peak6.com/careers, which returns 3,100 chars of marketing copy with no job data and no outbound job links - a row that could only ever look healthy and quiet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>pimco-workday</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr"/>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>https://pimco.wd1.myworkdayjobs.com/wday/cxs/pimco/pimco-careers</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T12:40:49+00:00</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>PIMCO. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 195 postings on the board, 7 US student rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>rbc-workday</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr"/>
-      <c r="E155" s="3" t="inlineStr">
-        <is>
-          <t>https://rbc.wd3.myworkdayjobs.com/wday/cxs/rbc/RBCEARLYTALENT1</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T12:40:49+00:00</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>RBC Early Talent. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 3 US student rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>troweprice-workday</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr"/>
-      <c r="E156" s="3" t="inlineStr">
-        <is>
-          <t>https://troweprice.wd5.myworkdayjobs.com/wday/cxs/troweprice/TRowePrice</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T12:40:49+00:00</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>T. Rowe Price. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 136 postings on the board, 8 US student rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>vanguard-workday</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr"/>
-      <c r="E157" s="3" t="inlineStr">
-        <is>
-          <t>https://vanguard.wd5.myworkdayjobs.com/wday/cxs/vanguard/vanguard_external</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T12:40:49+00:00</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>Vanguard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 441 postings on the board, 18 US student rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>wellington-workday</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr"/>
-      <c r="E158" s="3" t="inlineStr">
-        <is>
-          <t>https://wellington.wd5.myworkdayjobs.com/wday/cxs/wellington/Campus</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T12:40:49+00:00</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
           <t>Wellington Management. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 10 postings on the board, 4 US student rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H158"/>
+  <autoFilter ref="A1:H149"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>1c646d305b4c280a09f1fdcebc43895d8416592b0361b8f5e27f07ae39a0f064</t>
+          <t>4bc75dc7332eb96e499cda2e2fbbce876e5cb85db68480f7bce7cef57098891a</t>
         </is>
       </c>
     </row>
@@ -7942,12 +7942,12 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:08+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>7aae100d64822870cb3d2a28d1948dd7d89af148e680e1b5c8f15aee2305042c</t>
+          <t>c138777b70d1ead474c63d20398ca1f0cdf4bcbd067670199fc8e3305e3d11f0</t>
         </is>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8742,12 +8742,12 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:06:55+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="L157" s="2" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>60a880796c08ba895b63ab55bdaee867faf3afedf8135ba2a56f16e08682874a</t>
+          <t>0a65a7d54ecc562352de4dfca24a192526334f0c374fa2839c7c3dcc19d1c4f2</t>
         </is>
       </c>
     </row>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12595,7 +12595,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -13703,7 +13703,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -13997,7 +13997,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14203,7 +14203,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14453,7 +14453,11 @@
           <t>https://careers-gtsx.icims.com/jobs/search?ss=1&amp;in_iframe=1</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T00:52:12+00:00</t>
+        </is>
+      </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -14493,7 +14497,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14535,7 +14539,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -14577,7 +14581,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14619,7 +14623,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14661,7 +14665,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14703,7 +14707,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -14745,7 +14749,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14787,7 +14791,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14829,7 +14833,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14871,7 +14875,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -14913,7 +14917,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -14955,7 +14959,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -14997,7 +15001,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15039,7 +15043,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15081,7 +15085,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15123,7 +15127,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15165,7 +15169,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15207,7 +15211,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15249,7 +15253,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15291,7 +15295,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15333,7 +15337,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15375,7 +15379,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -15417,7 +15421,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15459,7 +15463,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15501,7 +15505,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15543,7 +15547,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15585,7 +15589,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15627,7 +15631,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15669,12 +15673,12 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T21:02:15+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -15709,7 +15713,11 @@
           <t>https://careers.twosigma.com/careers/OpenRoles/</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T00:52:12+00:00</t>
+        </is>
+      </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15749,7 +15757,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15791,7 +15799,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15833,7 +15841,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15875,7 +15883,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -15917,7 +15925,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -15959,7 +15967,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -16001,7 +16009,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16043,7 +16051,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -16085,7 +16093,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -16123,7 +16131,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16161,7 +16169,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16203,7 +16211,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16241,7 +16249,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16279,7 +16287,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16317,7 +16325,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16355,7 +16363,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16393,7 +16401,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16431,7 +16439,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16469,7 +16477,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16507,7 +16515,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16549,7 +16557,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16587,7 +16595,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16625,7 +16633,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -16663,7 +16671,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16701,7 +16709,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16739,7 +16747,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T00:52:12+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>4bc75dc7332eb96e499cda2e2fbbce876e5cb85db68480f7bce7cef57098891a</t>
+          <t>8f6dddcf5cda4f5703b938fb8c3902108c17e026292c8738dfee37ae8e79e423</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12595,7 +12595,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -13661,12 +13661,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:40:49+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -13703,7 +13703,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -13997,7 +13997,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14203,7 +14203,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14455,7 +14455,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -14581,7 +14581,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15085,7 +15085,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15169,7 +15169,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15253,7 +15253,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15295,7 +15295,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15337,7 +15337,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -15421,7 +15421,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15505,7 +15505,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15547,7 +15547,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15673,7 +15673,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15715,7 +15715,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15757,7 +15757,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15841,7 +15841,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16325,7 +16325,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16363,7 +16363,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16439,7 +16439,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16477,7 +16477,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16515,7 +16515,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16595,7 +16595,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -16671,7 +16671,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-17T12:40:36+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>8f6dddcf5cda4f5703b938fb8c3902108c17e026292c8738dfee37ae8e79e423</t>
+          <t>56efcece082a87b9731033eca0397d38fcaddb4542500f4540d6fbd490df44e6</t>
         </is>
       </c>
     </row>
@@ -7942,12 +7942,12 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:52:12+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>c138777b70d1ead474c63d20398ca1f0cdf4bcbd067670199fc8e3305e3d11f0</t>
+          <t>d605a0e1ee5879383316242ff0280132a6a10ea394b4e02b6497340361b17403</t>
         </is>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12595,7 +12595,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -13703,7 +13703,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -13997,7 +13997,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14203,7 +14203,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14455,7 +14455,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -14581,7 +14581,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15085,7 +15085,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15169,7 +15169,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15253,7 +15253,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15295,7 +15295,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15337,7 +15337,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -15421,7 +15421,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15505,7 +15505,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15547,7 +15547,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15673,7 +15673,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15715,7 +15715,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15757,7 +15757,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15841,7 +15841,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16325,7 +16325,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16363,7 +16363,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16439,7 +16439,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16477,7 +16477,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16515,7 +16515,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16595,7 +16595,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -16671,7 +16671,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Discovered" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Programs'!$A$1:$N$188</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$H$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Programs'!$A$1:$N$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$H$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Applied'!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Discovered'!$A$1:$H$51</definedName>
   </definedNames>
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N188"/>
+  <dimension ref="A1:N190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10526,8 +10526,124 @@
         </is>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Morgan Stanley Campus - Global Programs board</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Rolling by programme; the 2027 summer cycle closes Sep-Oct 2026</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>1st-4th year, varies by programme</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Morgan Stanley's whole campus board, on Talentlink (morganstanley.tal.net) - 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). Found 2026-09-18 while resolving a pasted posting link. IMPORTANT, the obvious URL is the wrong one: www.morganstanley.com/careers/career-opportunities-search sits behind an Akamai WAF that resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string - same machine, same IP, so the block is User-Agent based and it is the Citadel case, reachable only by misrepresenting the client. Do not re-point a source at it. Morgan Stanley's OTHER board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately NOT watched: it carries 1,327 corporate roles, caps page size at 10 (about 133 requests a day), and a query for 'Sophomore' or 'Freshman' returns zero - the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text, ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect.</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>morganstanley-campus-p1</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Morgan Stanley Investment Management Sophomore Summer Analyst Program - Private Credit &amp; Equity (New York)</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?ftq=Sophomore</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>2027 cycle closed Sep 25 2026; expect the 2028 cycle to open around Aug-Sep 2027</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Sophomore - 2027 cycle wanted graduation Dec 2028-Jun 2029</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - Jason is class of 2030, so he is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr"/>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N188"/>
+  <autoFilter ref="A1:N190"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -10711,6 +10827,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId181"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId184"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10722,7 +10840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -15144,7 +15262,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>open-source-quantitative-finance</t>
+          <t>morganstanley-campus-p1</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -15154,24 +15272,16 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Open Source Quantitative Finance Conference</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>https://osqf.org/</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-18T12:19:00+00:00</t>
-        </is>
-      </c>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15179,14 +15289,14 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 1966 chars of text over plain HTTP.</t>
+          <t>Page 1 of 3 of Morgan Stanley's campus board on Talentlink -- 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). The board pages 50 at a time and ?start= works without the xf-&lt;hash&gt; session token the site's own pagination links carry, so all three pages are watched as separate rows; num/size/limit are ignored. Added 2026-09-18 while resolving a pasted posting link. THE OBVIOUS URL IS THE WRONG ONE: www.morganstanley.com/careers/career-opportunities-search resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string -- same machine, same IP, so the block is User-Agent based and this is the Citadel case. Do not re-point a source at it. Morgan Stanley's other board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately not watched: 1,327 corporate roles, page size hard-capped at 10 (~133 requests a day), and queries for 'Sophomore' and 'Freshman' both return zero -- the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text at ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>optiver-futurefocus</t>
+          <t>morganstanley-campus-p2</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -15196,24 +15306,16 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Optiver FutureFocus</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>https://www.optiver.com/join-us/students/programs/futurefocus/</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-18T12:19:00+00:00</t>
-        </is>
-      </c>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?start=50</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15221,14 +15323,14 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Programme page for FutureFocus, Optiver's five-day discovery programme, which the page states is for FIRST and second-year students. Renamed and re-pointed 2026-09-11: the old id and URL (optiver-futurefocus-chicago-2026, /recruitment-events/futurefocus-chicago) baked in a city and a year, and the old URL now 301s here. Verified 2026-09-11: 4,591 chars. Note the page states no graduation-year window, only 'first and second-year', so eligibility cannot be confirmed from it the way Susquehanna's postings can - read the application itself before trusting the label.</t>
+          <t>Page 2 of 3 of the Morgan Stanley Campus board; see morganstanley-campus-p1 for the full finding. Probed 2026-09-18: HTTP 200, robots-allowed.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>optiver-ready-trader</t>
+          <t>morganstanley-campus-p3</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -15238,24 +15340,16 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Optiver Ready Trader Go</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr"/>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>https://readytradergo.optiver.com/</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-18T12:19:00+00:00</t>
-        </is>
-      </c>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?start=100</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15263,14 +15357,14 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>PHASE 3. Verified: 200, ~1KB of text over plain HTTP, no JS needed.</t>
+          <t>Page 3 of 3 of the Morgan Stanley Campus board; see morganstanley-campus-p1 for the full finding. Probed 2026-09-18: HTTP 200, robots-allowed.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>optiver-students</t>
+          <t>open-source-quantitative-finance</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -15285,12 +15379,12 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Optiver student opportunities</t>
+          <t>Open Source Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/?level=student</t>
+          <t>https://osqf.org/</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -15305,14 +15399,14 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 2,349 chars. Optiver's Greenhouse board (optiverprivate) is small, so the student page is the better signal.</t>
+          <t>Probed 2026-09-06: 200, 1966 chars of text over plain HTTP.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>pokerbots</t>
+          <t>optiver-futurefocus</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -15327,12 +15421,12 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>MIT Pokerbots</t>
+          <t>Optiver FutureFocus</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>https://pokerbots.org/</t>
+          <t>https://www.optiver.com/join-us/students/programs/futurefocus/</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -15347,14 +15441,14 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>PHASE 3. Verified: 200, ~6.2KB of text over plain HTTP, no JS needed. Needs a selector - the page retains announcement banners from 2023-2026 in the markup.</t>
+          <t>Programme page for FutureFocus, Optiver's five-day discovery programme, which the page states is for FIRST and second-year students. Renamed and re-pointed 2026-09-11: the old id and URL (optiver-futurefocus-chicago-2026, /recruitment-events/futurefocus-chicago) baked in a city and a year, and the old URL now 301s here. Verified 2026-09-11: 4,591 chars. Note the page states no graduation-year window, only 'first and second-year', so eligibility cannot be confirmed from it the way Susquehanna's postings can - read the application itself before trusting the label.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>quantbot-careers</t>
+          <t>optiver-ready-trader</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -15364,17 +15458,17 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Quantbot Technologies</t>
+          <t>Optiver Ready Trader Go</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>https://www.quantbot.com/careers/</t>
+          <t>https://readytradergo.optiver.com/</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -15389,14 +15483,14 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 751 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- quantbot-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>PHASE 3. Verified: 200, ~1KB of text over plain HTTP, no JS needed.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>rentec-careers</t>
+          <t>optiver-students</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -15411,12 +15505,12 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Renaissance Technologies</t>
+          <t>Optiver student opportunities</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>https://www.rentec.com/careers</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/?level=student</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -15431,14 +15525,14 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 1,380 chars of text.</t>
+          <t>Verified 2026-09-11: 2,349 chars. Optiver's Greenhouse board (optiverprivate) is small, so the student page is the better signal.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>rokos-careers</t>
+          <t>pokerbots</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -15448,17 +15542,17 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Rokos Capital</t>
+          <t>MIT Pokerbots</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>https://www.rokoscapital.com/careers</t>
+          <t>https://pokerbots.org/</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -15473,14 +15567,14 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 620 chars of text. Close to the 500-char floor; a redesign will trip the shrink guard rather than go quiet.</t>
+          <t>PHASE 3. Verified: 200, ~6.2KB of text over plain HTTP, no JS needed. Needs a selector - the page retains announcement banners from 2023-2026 in the markup.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>stevens-high-frequency-trading</t>
+          <t>quantbot-careers</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -15490,17 +15584,17 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Stevens High Frequency Trading Competition 2026</t>
+          <t>Quantbot Technologies</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
+          <t>https://www.quantbot.com/careers/</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -15515,14 +15609,14 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 10400 chars of text over plain HTTP, robots.txt allows. Cleanly pollable.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 751 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- quantbot-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>teza-careers</t>
+          <t>rentec-careers</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -15532,17 +15626,17 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>Renaissance Technologies</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>https://www.teza.com/careers/</t>
+          <t>https://www.rentec.com/careers</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -15557,14 +15651,14 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 8,134 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- teza-ashby watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 1,380 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>tgs-join-our-team</t>
+          <t>rokos-careers</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -15579,12 +15673,12 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>TGS Management</t>
+          <t>Rokos Capital</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>https://www.tgsmc.com/join-our-team/</t>
+          <t>https://www.rokoscapital.com/careers</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -15599,14 +15693,14 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 1,977 chars. The Lever slug `tgsmc` resolves but returns an empty list, so the page is the only non-alerting surface.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 620 chars of text. Close to the 500-char floor; a redesign will trip the shrink guard rather than go quiet.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>tradebot-students</t>
+          <t>stevens-high-frequency-trading</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -15616,17 +15710,17 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Tradebot Systems</t>
+          <t>Stevens High Frequency Trading Competition 2026</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>https://www.tradebot.com/careers/students</t>
+          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -15641,14 +15735,14 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 1,253 chars of text.</t>
+          <t>Probed 2026-09-06: 200, 10400 chars of text over plain HTTP, robots.txt allows. Cleanly pollable.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>trexquant-students</t>
+          <t>teza-careers</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -15663,12 +15757,12 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Trexquant</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>https://trexquant.com/careers/students</t>
+          <t>https://www.teza.com/careers/</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -15683,14 +15777,14 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 891 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 8,134 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- teza-ashby watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>twosigma-campus</t>
+          <t>tgs-join-our-team</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -15700,17 +15794,17 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Two Sigma</t>
+          <t>TGS Management</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>https://careers.twosigma.com/careers/OpenRoles/</t>
+          <t>https://www.tgsmc.com/join-our-team/</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -15725,14 +15819,14 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Re-pointed 2026-09-12: the old /careers/students/ url 301'd to the generic /careers/ page and had been reporting success from it. The internships page is the real replacement (9,509 chars, 29 'intern' mentions). No public vendor ATS -- careers.twosigma.com is a custom board with no Greenhouse/Lever/Ashby fingerprint. Correction 2026-09-16: "no public vendor ATS" was wrong in its conclusion though right that there is no Greenhouse/Lever/Ashby fingerprint -- careers.twosigma.com is Avature (CNAME portaltwosigma.avature.net), a vendor ATS this project does not fingerprint. Re-pointed to its OpenRoles listing: 2,676 chars at ratio 0.024, including "AI Research Scientist - Intern [2027 Summer]". Vendor-hosted, so outside the WAF that 403s the runner on www.twosigma.com (WP Engine).</t>
+          <t>Verified 2026-09-11: 1,977 chars. The Lever slug `tgsmc` resolves but returns an empty list, so the page is the only non-alerting surface.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>vector-roles</t>
+          <t>tradebot-students</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -15742,17 +15836,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Vector Trading (Chicago)</t>
+          <t>Tradebot Systems</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>https://vectortrading.com/data/roles.json</t>
+          <t>https://www.tradebot.com/careers/students</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -15767,14 +15861,14 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: The firm's own roles.json, 5 roles, 11,367 chars. 0 student today. Note vectortrading.io and Ashby `vector` are different companies entirely.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 1,253 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>verition-careers</t>
+          <t>trexquant-students</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -15789,12 +15883,12 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Verition Fund Management</t>
+          <t>Trexquant</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>https://www.verition.com/careers</t>
+          <t>https://trexquant.com/careers/students</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -15809,14 +15903,14 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 11,469 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- verition-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 891 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>volant-careers</t>
+          <t>twosigma-campus</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -15826,17 +15920,17 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Volant Trading</t>
+          <t>Two Sigma</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>https://volanttrading.com/</t>
+          <t>https://careers.twosigma.com/careers/OpenRoles/</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -15851,14 +15945,14 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 2,245 chars. Entry-level roles are Hong Kong only today.</t>
+          <t>Re-pointed 2026-09-12: the old /careers/students/ url 301'd to the generic /careers/ page and had been reporting success from it. The internships page is the real replacement (9,509 chars, 29 'intern' mentions). No public vendor ATS -- careers.twosigma.com is a custom board with no Greenhouse/Lever/Ashby fingerprint. Correction 2026-09-16: "no public vendor ATS" was wrong in its conclusion though right that there is no Greenhouse/Lever/Ashby fingerprint -- careers.twosigma.com is Avature (CNAME portaltwosigma.avature.net), a vendor ATS this project does not fingerprint. Re-pointed to its OpenRoles listing: 2,676 chars at ratio 0.024, including "AI Research Scientist - Intern [2027 Summer]". Vendor-hosted, so outside the WAF that 403s the runner on www.twosigma.com (WP Engine).</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>voloridge-join-our-team</t>
+          <t>vector-roles</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -15868,17 +15962,17 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Voloridge Ascend Program</t>
+          <t>Vector Trading (Chicago)</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>https://www.voloridge.com/join-our-team</t>
+          <t>https://vectortrading.com/data/roles.json</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -15893,14 +15987,14 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 9,393 chars. Kept alongside the board because it carries the Ascend eligibility text and cohort size (20 places); board rows carry the posting only.</t>
+          <t>Verified 2026-09-11: The firm's own roles.json, 5 roles, 11,367 chars. 0 student today. Note vectortrading.io and Ashby `vector` are different companies entirely.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>wincent-careers</t>
+          <t>verition-careers</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -15915,12 +16009,12 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Wincent</t>
+          <t>Verition Fund Management</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>https://www.wincent.com/careers/</t>
+          <t>https://www.verition.com/careers</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -15935,14 +16029,14 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 11,076 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 11,469 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- verition-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>wintermute-careers</t>
+          <t>volant-careers</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -15952,17 +16046,17 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Wintermute</t>
+          <t>Volant Trading</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>https://www.wintermute.com/company/careers</t>
+          <t>https://volanttrading.com/</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -15977,14 +16071,14 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 14,346 chars of text.</t>
+          <t>Verified 2026-09-11: 2,245 chars. Entry-level roles are Hong Kong only today.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>wolverine-careers</t>
+          <t>voloridge-join-our-team</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -15994,17 +16088,17 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Wolverine Trading</t>
+          <t>Voloridge Ascend Program</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>https://careers.wolve.com/postings.json</t>
+          <t>https://www.voloridge.com/join-our-team</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -16019,14 +16113,14 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: Pinpoint ATS JSON, 21 postings, 147,741 chars, ratio 0.99. Re-pointed from wolve.com/careers, which is 1,178 chars with zero student hits, and careers.wolve.com, which is a 317-char shell. Caveat: the feed embeds full HTML descriptions, so a reworded description will diff as changed text - if that turns noisy, write a small Pinpoint parser that keeps descriptions out of the snapshot the way the ATS methods do.</t>
+          <t>Verified 2026-09-11: 9,393 chars. Kept alongside the board because it carries the Ascend eligibility text and cohort size (20 places); board rows carry the posting only.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>xtx-careers</t>
+          <t>wincent-careers</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -16036,17 +16130,17 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>XTX Markets</t>
+          <t>Wincent</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>https://www.xtxmarkets.com/careers/</t>
+          <t>https://www.wincent.com/careers/</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -16061,34 +16155,34 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>XTX is on no public ATS. Verified 2026-09-11: 13,750 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- xtxmarkets-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 11,076 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>sig-phenom</t>
+          <t>wintermute-careers</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>phenom</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Susquehanna (SIG)</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/api/jobs</t>
+          <t>https://www.wintermute.com/company/careers</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -16103,30 +16197,34 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Phenom/iCIMS JSON API. Replaces the sig-careers manual row, which was correct about the page (402KB of HTML yields 221 chars) and wrong about the firm: this endpoint answers state.USER_AGENT with 263 postings. Verified 2026-09-11: 52 US student rows across Interns + Co-ops, New Graduates and Student Discovery Program. The five US Discovery Programs are gated to winter 2028 / spring 2029 graduates, i.e. sophomores for a four-year US degree, so they are correctly ruled out for class of 2030 until the autumn 2027 cycle.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 14,346 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>capitalgroup-workday</t>
+          <t>wolverine-careers</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Wolverine Trading</t>
+        </is>
+      </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>https://capgroup.wd1.myworkdayjobs.com/wday/cxs/capgroup/capitalgroupcareers</t>
+          <t>https://careers.wolve.com/postings.json</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -16141,30 +16239,34 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Capital Group. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 1 US student rows.</t>
+          <t>Verified 2026-09-11: Pinpoint ATS JSON, 21 postings, 147,741 chars, ratio 0.99. Re-pointed from wolve.com/careers, which is 1,178 chars with zero student hits, and careers.wolve.com, which is a 317-char shell. Caveat: the feed embeds full HTML descriptions, so a reworded description will diff as changed text - if that turns noisy, write a small Pinpoint parser that keeps descriptions out of the snapshot the way the ATS methods do.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>cibc-workday</t>
+          <t>xtx-careers</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>XTX Markets</t>
+        </is>
+      </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>https://cibc.wd3.myworkdayjobs.com/wday/cxs/cibc/campus</t>
+          <t>https://www.xtxmarkets.com/careers/</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -16179,34 +16281,34 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>CIBC. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 44 postings on the board, 6 US student rows.</t>
+          <t>XTX is on no public ATS. Verified 2026-09-11: 13,750 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- xtxmarkets-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>cme-workday</t>
+          <t>sig-phenom</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>phenom</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Susquehanna (SIG)</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>https://cmegroup.wd1.myworkdayjobs.com/wday/cxs/cmegroup/cme_careers</t>
+          <t>https://careers.sig.com/api/jobs</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -16221,14 +16323,14 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 33 postings, 0 student today. Use the CXS API only - www.cmegroup.com times out for our User-Agent.</t>
+          <t>Phenom/iCIMS JSON API. Replaces the sig-careers manual row, which was correct about the page (402KB of HTML yields 221 chars) and wrong about the firm: this endpoint answers state.USER_AGENT with 263 postings. Verified 2026-09-11: 52 US student rows across Interns + Co-ops, New Graduates and Student Discovery Program. The five US Discovery Programs are gated to winter 2028 / spring 2029 graduates, i.e. sophomores for a four-year US degree, so they are correctly ruled out for class of 2030 until the autumn 2027 cycle.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>dimensional-workday</t>
+          <t>capitalgroup-workday</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -16244,7 +16346,7 @@
       <c r="D136" s="2" t="inlineStr"/>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>https://dimensional.wd5.myworkdayjobs.com/wday/cxs/dimensional/dfa_careers</t>
+          <t>https://capgroup.wd1.myworkdayjobs.com/wday/cxs/capgroup/capitalgroupcareers</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -16259,14 +16361,14 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 72 postings on the board, 7 US student rows.</t>
+          <t>Capital Group. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 1 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>draftkings-workday</t>
+          <t>cibc-workday</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -16282,7 +16384,7 @@
       <c r="D137" s="2" t="inlineStr"/>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>https://draftkings.wd1.myworkdayjobs.com/wday/cxs/draftkings/Campus_Career_Portal</t>
+          <t>https://cibc.wd3.myworkdayjobs.com/wday/cxs/cibc/campus</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -16297,14 +16399,14 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>DraftKings. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 7 postings on the board, 6 US student rows.</t>
+          <t>CIBC. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 44 postings on the board, 6 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>fanniemae-workday</t>
+          <t>cme-workday</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -16314,13 +16416,17 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>CME Group</t>
+        </is>
+      </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>https://fanniemae.wd1.myworkdayjobs.com/wday/cxs/fanniemae/FannieMaeCareers</t>
+          <t>https://cmegroup.wd1.myworkdayjobs.com/wday/cxs/cmegroup/cme_careers</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -16335,14 +16441,14 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Fannie Mae. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 61 postings on the board, 6 US student rows.</t>
+          <t>Verified 2026-09-11: 33 postings, 0 student today. Use the CXS API only - www.cmegroup.com times out for our User-Agent.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>freddiemac-workday</t>
+          <t>dimensional-workday</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -16358,7 +16464,7 @@
       <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>https://freddiemac.wd5.myworkdayjobs.com/wday/cxs/freddiemac/External</t>
+          <t>https://dimensional.wd5.myworkdayjobs.com/wday/cxs/dimensional/dfa_careers</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -16373,14 +16479,14 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Freddie Mac. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 103 postings on the board, 13 US student rows.</t>
+          <t>Dimensional Fund Advisors. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 72 postings on the board, 7 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>kensho-workday</t>
+          <t>draftkings-workday</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -16396,7 +16502,7 @@
       <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>https://spgi.wd5.myworkdayjobs.com/wday/cxs/spgi/Kensho_Careers</t>
+          <t>https://draftkings.wd1.myworkdayjobs.com/wday/cxs/draftkings/Campus_Career_Portal</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -16411,14 +16517,14 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Kensho (S&amp;P Global). Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 9 postings on the board, 0 US student rows.</t>
+          <t>DraftKings. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 7 postings on the board, 6 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>lpl-workday</t>
+          <t>fanniemae-workday</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -16434,7 +16540,7 @@
       <c r="D141" s="2" t="inlineStr"/>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>https://lplfinancial.wd1.myworkdayjobs.com/wday/cxs/lplfinancial/university</t>
+          <t>https://fanniemae.wd1.myworkdayjobs.com/wday/cxs/fanniemae/FannieMaeCareers</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -16449,14 +16555,14 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>LPL Financial. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 36 postings on the board, 16 US student rows.</t>
+          <t>Fannie Mae. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 61 postings on the board, 6 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>mastercard-workday</t>
+          <t>freddiemac-workday</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -16472,7 +16578,7 @@
       <c r="D142" s="2" t="inlineStr"/>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/wday/cxs/mastercard/Campus</t>
+          <t>https://freddiemac.wd5.myworkdayjobs.com/wday/cxs/freddiemac/External</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -16487,14 +16593,14 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Mastercard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 52 postings on the board, 1 US student rows.</t>
+          <t>Freddie Mac. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 103 postings on the board, 13 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>northerntrust-workday</t>
+          <t>kensho-workday</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -16510,7 +16616,7 @@
       <c r="D143" s="2" t="inlineStr"/>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>https://ntrs.wd1.myworkdayjobs.com/wday/cxs/ntrs/northerntrust</t>
+          <t>https://spgi.wd5.myworkdayjobs.com/wday/cxs/spgi/Kensho_Careers</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -16525,14 +16631,14 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Northern Trust. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 665 postings on the board, 20 US student rows.</t>
+          <t>Kensho (S&amp;P Global). Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 9 postings on the board, 0 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>peak6-workday</t>
+          <t>lpl-workday</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -16542,17 +16648,13 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>PEAK6</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr"/>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>https://peak6group.wd1.myworkdayjobs.com/wday/cxs/peak6group/PEAK6</t>
+          <t>https://lplfinancial.wd1.myworkdayjobs.com/wday/cxs/lplfinancial/university</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -16567,14 +16669,14 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 14 postings, 3 US student rows (Trading Bootcamp Micro-Internship Summer 2027, Trading Internship for Women+ Summer 2027, Trading Associate 2027). Re-pointed from peak6.com/careers, which returns 3,100 chars of marketing copy with no job data and no outbound job links - a row that could only ever look healthy and quiet.</t>
+          <t>LPL Financial. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 36 postings on the board, 16 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>pimco-workday</t>
+          <t>mastercard-workday</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -16590,7 +16692,7 @@
       <c r="D145" s="2" t="inlineStr"/>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>https://pimco.wd1.myworkdayjobs.com/wday/cxs/pimco/pimco-careers</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/wday/cxs/mastercard/Campus</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -16605,14 +16707,14 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>PIMCO. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 195 postings on the board, 7 US student rows.</t>
+          <t>Mastercard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 52 postings on the board, 1 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>rbc-workday</t>
+          <t>northerntrust-workday</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -16628,7 +16730,7 @@
       <c r="D146" s="2" t="inlineStr"/>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>https://rbc.wd3.myworkdayjobs.com/wday/cxs/rbc/RBCEARLYTALENT1</t>
+          <t>https://ntrs.wd1.myworkdayjobs.com/wday/cxs/ntrs/northerntrust</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -16643,14 +16745,14 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>RBC Early Talent. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 3 US student rows.</t>
+          <t>Northern Trust. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 665 postings on the board, 20 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>troweprice-workday</t>
+          <t>peak6-workday</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -16660,13 +16762,17 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>PEAK6</t>
+        </is>
+      </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>https://troweprice.wd5.myworkdayjobs.com/wday/cxs/troweprice/TRowePrice</t>
+          <t>https://peak6group.wd1.myworkdayjobs.com/wday/cxs/peak6group/PEAK6</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -16681,14 +16787,14 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>T. Rowe Price. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 136 postings on the board, 8 US student rows.</t>
+          <t>Verified 2026-09-11: 14 postings, 3 US student rows (Trading Bootcamp Micro-Internship Summer 2027, Trading Internship for Women+ Summer 2027, Trading Associate 2027). Re-pointed from peak6.com/careers, which returns 3,100 chars of marketing copy with no job data and no outbound job links - a row that could only ever look healthy and quiet.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>vanguard-workday</t>
+          <t>pimco-workday</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -16704,7 +16810,7 @@
       <c r="D148" s="2" t="inlineStr"/>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>https://vanguard.wd5.myworkdayjobs.com/wday/cxs/vanguard/vanguard_external</t>
+          <t>https://pimco.wd1.myworkdayjobs.com/wday/cxs/pimco/pimco-careers</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -16719,14 +16825,14 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Vanguard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 441 postings on the board, 18 US student rows.</t>
+          <t>PIMCO. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 195 postings on the board, 7 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>wellington-workday</t>
+          <t>rbc-workday</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -16742,27 +16848,141 @@
       <c r="D149" s="2" t="inlineStr"/>
       <c r="E149" s="3" t="inlineStr">
         <is>
+          <t>https://rbc.wd3.myworkdayjobs.com/wday/cxs/rbc/RBCEARLYTALENT1</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:19:00+00:00</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>RBC Early Talent. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 3 US student rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>troweprice-workday</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr"/>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>https://troweprice.wd5.myworkdayjobs.com/wday/cxs/troweprice/TRowePrice</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:19:00+00:00</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>T. Rowe Price. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 136 postings on the board, 8 US student rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>vanguard-workday</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr"/>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>https://vanguard.wd5.myworkdayjobs.com/wday/cxs/vanguard/vanguard_external</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:19:00+00:00</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>Vanguard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 441 postings on the board, 18 US student rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>wellington-workday</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr"/>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
           <t>https://wellington.wd5.myworkdayjobs.com/wday/cxs/wellington/Campus</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>2026-09-18T12:19:00+00:00</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Wellington Management. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 10 postings on the board, 4 US student rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H149"/>
+  <autoFilter ref="A1:H152"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId2"/>
@@ -16846,6 +17066,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>56efcece082a87b9731033eca0397d38fcaddb4542500f4540d6fbd490df44e6</t>
+          <t>ca8cdb2d2b9ca1a4eba5e5178f49aba4de3ace3b3b05a88fa5b247f86350b6ca</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10919,7 +10919,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11765,7 +11765,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12713,7 +12713,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13505,7 +13505,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14405,7 +14405,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14489,7 +14489,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14909,7 +14909,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -15035,7 +15035,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -15077,7 +15077,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15284,7 +15284,7 @@
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -15318,7 +15318,7 @@
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -15352,7 +15352,7 @@
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -15389,7 +15389,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15431,7 +15431,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15767,7 +15767,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16389,7 +16389,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16431,7 +16431,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16507,7 +16507,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16621,7 +16621,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16659,7 +16659,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16697,7 +16697,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16740,7 +16740,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -16777,7 +16777,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16853,7 +16853,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -16891,7 +16891,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-19T12:01:24+00:00</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>ca8cdb2d2b9ca1a4eba5e5178f49aba4de3ace3b3b05a88fa5b247f86350b6ca</t>
+          <t>90b15d324068352a47399957f08b65cbd04e5aa6a144547f6689c0b59989aa5b</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10919,7 +10919,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11765,7 +11765,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12713,7 +12713,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13505,7 +13505,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -13779,12 +13779,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T12:40:36+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14405,7 +14405,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14489,7 +14489,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14909,7 +14909,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -15035,7 +15035,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -15077,7 +15077,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15284,7 +15284,7 @@
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -15318,7 +15318,7 @@
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -15352,7 +15352,7 @@
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -15389,7 +15389,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15431,7 +15431,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15767,7 +15767,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16389,7 +16389,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16431,7 +16431,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16507,7 +16507,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16621,7 +16621,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16659,7 +16659,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16697,7 +16697,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16735,12 +16735,12 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -16777,7 +16777,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16853,7 +16853,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -16891,7 +16891,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:24+00:00</t>
+          <t>2026-09-20T12:18:51+00:00</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Programs'!$A$1:$N$190</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$H$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Applied'!$A$1:$C$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Discovered'!$A$1:$H$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Discovered'!$A$1:$H$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>90b15d324068352a47399957f08b65cbd04e5aa6a144547f6689c0b59989aa5b</t>
+          <t>f1c69c6c475a19aa68fc1c7a194bfd8553efa4b3521c9f917b1785f1c913e0a1</t>
         </is>
       </c>
     </row>
@@ -7942,12 +7942,12 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T12:19:00+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>d605a0e1ee5879383316242ff0280132a6a10ea394b4e02b6497340361b17403</t>
+          <t>9b4b34980e7e1794b0658c67468a5ddf19c7220395b0394af11b794579fe2e2e</t>
         </is>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10919,7 +10919,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11765,7 +11765,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12713,7 +12713,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13505,7 +13505,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14405,7 +14405,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14489,7 +14489,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14909,7 +14909,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -15035,7 +15035,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -15077,7 +15077,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15284,7 +15284,7 @@
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -15318,7 +15318,7 @@
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -15352,7 +15352,7 @@
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -15389,7 +15389,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15431,7 +15431,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15767,7 +15767,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16389,7 +16389,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16431,7 +16431,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16507,7 +16507,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16621,7 +16621,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16659,7 +16659,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16697,7 +16697,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -16777,7 +16777,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16853,7 +16853,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -16891,7 +16891,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T12:18:51+00:00</t>
+          <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -17117,7 +17117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>appian</t>
+          <t>aperaaiinc</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -17190,27 +17190,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:appian</t>
+          <t>greenhouse:aperaaiinc</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/appian/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/aperaaiinc/jobs?content=true</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 172 postings, 10 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 9 postings, 0 US student rows</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>bti36021</t>
+          <t>appian</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -17232,17 +17232,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:bti36021</t>
+          <t>greenhouse:appian</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/bti36021/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/appian/jobs?content=true</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 12 postings, 1 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 172 postings, 10 US student rows</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -17264,7 +17264,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>compeerfinancial</t>
+          <t>bti36021</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -17274,17 +17274,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:compeerfinancial</t>
+          <t>greenhouse:bti36021</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/compeerfinancial/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/bti36021/jobs?content=true</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 67 postings, 0 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 12 postings, 1 US student rows</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>cssmerge</t>
+          <t>compeerfinancial</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -17316,17 +17316,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:cssmerge</t>
+          <t>greenhouse:compeerfinancial</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/cssmerge/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/compeerfinancial/jobs?content=true</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 245 postings, 2 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 67 postings, 0 US student rows</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -17348,7 +17348,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>devtechnology</t>
+          <t>cssmerge</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -17358,17 +17358,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:devtechnology</t>
+          <t>greenhouse:cssmerge</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/devtechnology/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/cssmerge/jobs?content=true</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 26 postings, 5 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 245 postings, 2 US student rows</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -17390,7 +17390,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>eulerity</t>
+          <t>devtechnology</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -17400,17 +17400,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:eulerity</t>
+          <t>greenhouse:devtechnology</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/eulerity/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/devtechnology/jobs?content=true</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 17 postings, 6 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 26 postings, 5 US student rows</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>gallup</t>
+          <t>doordashcanada</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -17442,27 +17442,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:gallup</t>
+          <t>greenhouse:doordashcanada</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/gallup/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/doordashcanada/jobs?content=true</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 54 postings, 5 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 34 postings, 0 US student rows</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>generalmatter</t>
+          <t>doordashusa</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -17484,27 +17484,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:generalmatter</t>
+          <t>greenhouse:doordashusa</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/generalmatter/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/doordashusa/jobs?content=true</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 132 postings, 24 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 462 postings, 5 US student rows</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>hpiq</t>
+          <t>duolingounirecruitment</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -17526,27 +17526,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:hpiq</t>
+          <t>greenhouse:duolingounirecruitment</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/hpiq/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/duolingounirecruitment/jobs?content=true</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 32 postings, 7 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 3 postings, 3 US student rows</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>hudl</t>
+          <t>eulerity</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -17568,17 +17568,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:hudl</t>
+          <t>greenhouse:eulerity</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/hudl/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/eulerity/jobs?content=true</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 31 postings, 3 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 17 postings, 6 US student rows</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -17600,7 +17600,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>idmeuniversityrecruiting</t>
+          <t>figma</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -17610,27 +17610,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:idmeuniversityrecruiting</t>
+          <t>greenhouse:figma</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/idmeuniversityrecruiting/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/figma/jobs?content=true</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 7 postings, 7 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 152 postings, 6 US student rows</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>k2spacecorporation</t>
+          <t>gallup</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -17652,17 +17652,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:k2spacecorporation</t>
+          <t>greenhouse:gallup</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/k2spacecorporation/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/gallup/jobs?content=true</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 219 postings, 9 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 54 postings, 5 US student rows</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -17684,7 +17684,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>klaviyocampus</t>
+          <t>generalmatter</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -17694,17 +17694,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:klaviyocampus</t>
+          <t>greenhouse:generalmatter</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/klaviyocampus/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/generalmatter/jobs?content=true</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 3 postings, 2 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 132 postings, 24 US student rows</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>nisc</t>
+          <t>hpiq</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:nisc</t>
+          <t>greenhouse:hpiq</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/nisc/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/hpiq/jobs?content=true</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 39 postings, 8 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 32 postings, 7 US student rows</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -17768,7 +17768,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>pacificfusion</t>
+          <t>hudl</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -17778,17 +17778,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:pacificfusion</t>
+          <t>greenhouse:hudl</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/pacificfusion/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/hudl/jobs?content=true</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 37 postings, 5 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 31 postings, 3 US student rows</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -17810,7 +17810,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>testnisc</t>
+          <t>idmeuniversityrecruiting</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -17820,17 +17820,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:testnisc</t>
+          <t>greenhouse:idmeuniversityrecruiting</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/testnisc/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/idmeuniversityrecruiting/jobs?content=true</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 37 postings, 9 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 7 postings, 7 US student rows</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -17852,27 +17852,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Chieler/Summer-2027-SWE-Internships</t>
+          <t>k2spacecorporation</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>repo</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>repo:chieler/summer-2027-swe-internships</t>
+          <t>greenhouse:k2spacecorporation</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Chieler/Summer-2027-SWE-Internships</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/k2spacecorporation/jobs?content=true</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26 stars, pushed 2026-09-13; matched "Summer 2027 Internships"</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 219 postings, 9 US student rows</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -17894,27 +17894,27 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>sndsh404/summer-2027-internships</t>
+          <t>klaviyocampus</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>repo</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>repo:sndsh404/summer-2027-internships</t>
+          <t>greenhouse:klaviyocampus</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sndsh404/summer-2027-internships</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/klaviyocampus/jobs?content=true</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>934 stars, pushed 2026-08-03; matched "Summer 2027 Internships"</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 3 postings, 2 US student rows</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -17931,12 +17931,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>chicagotradingcampus</t>
+          <t>nisc</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -17946,17 +17946,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:chicagotradingcampus</t>
+          <t>greenhouse:nisc</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/chicagotradingcampus/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/nisc/jobs?content=true</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 8 postings, 4 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 39 postings, 8 US student rows</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -17973,12 +17973,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ctccampusboard</t>
+          <t>pacificfusion</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -17988,17 +17988,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:ctccampusboard</t>
+          <t>greenhouse:pacificfusion</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/ctccampusboard/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/pacificfusion/jobs?content=true</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 6 postings, 4 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 37 postings, 5 US student rows</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -18015,12 +18015,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>gardacp</t>
+          <t>testnisc</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -18030,17 +18030,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:gardacp</t>
+          <t>greenhouse:testnisc</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/gardacp/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/testnisc/jobs?content=true</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 14 postings, 4 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 37 postings, 9 US student rows</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -18057,32 +18057,32 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>tgsmc</t>
+          <t>Chieler/Summer-2027-SWE-Internships</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>repo</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>lever:tgsmc</t>
+          <t>repo:chieler/summer-2027-swe-internships</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>https://api.lever.co/v0/postings/tgsmc?mode=json</t>
+          <t>https://github.com/Chieler/Summer-2027-SWE-Internships</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>found in the HTML of tgs-join-our-team, which is watched as page_text; not in sources.csv; API returns 0 postings, 0 US student rows</t>
+          <t>26 stars, pushed 2026-09-13; matched "Summer 2027 Internships"</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -18099,12 +18099,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>vanshb03/Summer2027-Internships</t>
+          <t>sndsh404/summer-2027-internships</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -18114,17 +18114,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>repo:vanshb03/summer2027-internships</t>
+          <t>repo:sndsh404/summer-2027-internships</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/vanshb03/Summer2027-Internships</t>
+          <t>https://github.com/sndsh404/summer-2027-internships</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9045 stars, pushed 2026-08-23; matched "Summer 2027 Internships"</t>
+          <t>934 stars, pushed 2026-08-03; matched "Summer 2027 Internships"</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -18141,210 +18141,210 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Allston Trading</t>
+          <t>chicagotradingcampus</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>allston-trading</t>
+          <t>greenhouse:chicagotradingcampus</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>https://allstontrading.com</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/chicagotradingcampus/jobs?content=true</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>DNS resolves, ports 443 and 80 closed. Acquired by DV Trading Dec 2021; DV's board is already watched as dvtrading-greenhouse.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 8 postings, 4 US student rows</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>AlphaGrep Securities</t>
+          <t>ctccampusboard</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>alphagrep</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>alphagrepsecurities (greenhouse)</t>
+          <t>greenhouse:ctccampusboard</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>https://boards-api.greenhouse.io/v1/boards/ctccampusboard/jobs?content=true</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16 jobs including a 2027 Campus Program, but every location is India/China/Singapore - zero US rows now or historically.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 6 postings, 4 US student rows</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>AlphaSimplex</t>
+          <t>gardacp</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>alphasimplex</t>
+          <t>greenhouse:gardacp</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>https://www.alphasimplex.com/</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/gardacp/jobs?content=true</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Acquired by Virtus (closed Apr 2023). The Workday board that answers is all-Virtus sales/advisory, not quant.</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 14 postings, 4 US student rows</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Arb Trading Group</t>
+          <t>tgsmc</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>arb-trading-group</t>
+          <t>lever:tgsmc</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>https://arb-tg.com/</t>
+          <t>https://api.lever.co/v0/postings/tgsmc?mode=json</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4,775-char Webflow site, every careers path 404. arbtrading.com is a catch-all serving the same page for all 22 paths - a trap that would look healthy.</t>
+          <t>found in the HTML of tgs-join-our-team, which is watched as page_text; not in sources.csv; API returns 0 postings, 0 US student rows</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Citadel (hedge fund)</t>
+          <t>vanshb03/Summer2027-Internships</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>repo</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>citadel</t>
+          <t>repo:vanshb03/summer2027-internships</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>https://www.citadel.com/careers/students/</t>
+          <t>https://github.com/vanshb03/Summer2027-Internships</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>403 Cloudflare intermittently (1 of 3 fetches over 12 samples); homepage always 403. An intermittent block is worse than a hard one - it would fire spurious source failures. method=manual is correct.</t>
+          <t>9045 stars, pushed 2026-08-23; matched "Summer 2027 Internships"</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -18356,7 +18356,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Consolidated Trading</t>
+          <t>Allston Trading</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -18366,17 +18366,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>consolidated-trading</t>
+          <t>allston-trading</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>http://consolidatedtrading.com/</t>
+          <t>https://allstontrading.com</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1,086 chars with no careers content, all careers paths 404, HTTPS handshake fails.</t>
+          <t>DNS resolves, ports 443 and 80 closed. Acquired by DV Trading Dec 2021; DV's board is already watched as dvtrading-greenhouse.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -18398,7 +18398,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Cutler Group</t>
+          <t>AlphaGrep Securities</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -18408,17 +18408,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>cutler-group</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>https://cutlerllc.com/</t>
+          <t>alphagrep</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>alphagrepsecurities (greenhouse)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>224 chars, under the floor; WP REST shows two pages total. NOTE cutlergroup.com is a Canadian bathroom-vanity manufacturer - wrong company.</t>
+          <t>16 jobs including a 2027 Campus Program, but every location is India/China/Singapore - zero US rows now or historically.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -18440,7 +18440,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Dark Forest Technologies</t>
+          <t>AlphaSimplex</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -18450,17 +18450,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>dark-forest-tech</t>
+          <t>alphasimplex</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>https://darkforesttech.com/</t>
+          <t>https://www.alphasimplex.com/</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>231 chars, under the floor. A single GitHub Pages placeholder; recruiting@darkforesttech.com only.</t>
+          <t>Acquired by Virtus (closed Apr 2023). The Workday board that answers is all-Virtus sales/advisory, not quant.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -18482,7 +18482,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Eisler Capital</t>
+          <t>Arb Trading Group</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -18492,17 +18492,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>eisler-capital</t>
+          <t>arb-trading-group</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>https://eislercapital.com</t>
+          <t>https://arb-tg.com/</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>DEFUNCT: no A record; www CNAMEs to a torn-down CloudFront distribution. Flagship wound down 31 Dec 2025.</t>
+          <t>4,775-char Webflow site, every careers path 404. arbtrading.com is a catch-all serving the same page for all 22 paths - a trap that would look healthy.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Emergent Trading</t>
+          <t>Citadel (hedge fund)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -18534,17 +18534,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>emergent-trading</t>
+          <t>citadel</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>https://www.emergenttrading.com/join</t>
+          <t>https://www.citadel.com/careers/students/</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Ember.js shell: /join is the real careers route and returns 0 chars. App and vendor bundles grepped, no ATS and no fetch target.</t>
+          <t>403 Cloudflare intermittently (1 of 3 fetches over 12 samples); homepage always 403. An intermittent block is worse than a hard one - it would fire spurious source failures. method=manual is correct.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Freestone Grove Partners</t>
+          <t>Consolidated Trading</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -18576,17 +18576,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>freestone-grove</t>
+          <t>consolidated-trading</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.gem.com/freestone-grove-partners</t>
+          <t>http://consolidatedtrading.com/</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Gem JS shell, 32 chars. Board verified real but empty: the GraphQL POST returns jobPostings: []. Worth re-probing later.</t>
+          <t>1,086 chars with no careers content, all careers paths 404, HTTPS handshake fails.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs Emerging Leaders Series</t>
+          <t>Cutler Group</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -18618,17 +18618,17 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>goldman-emerging-leaders</t>
+          <t>cutler-group</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships/americas/emerging-leaders-series</t>
+          <t>https://cutlerllc.com/</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>403 Akamai. higher.gs.com/roles returns 200 but 29 chars (JS shell). Programme is live for 2026 but only reachable at edition-specific Avature URLs that expire.</t>
+          <t>224 chars, under the floor; WP REST shows two pages total. NOTE cutlergroup.com is a Canadian bathroom-vanity manufacturer - wrong company.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Kinetic Trading Partners</t>
+          <t>Dark Forest Technologies</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -18660,13 +18660,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>kinetic-trading-partners</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
+          <t>dark-forest-tech</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>https://darkforesttech.com/</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Zero LinkedIn results, absent from every quant directory checked. The name collides with Kinetic Partners Management LP, Kinetix Trading Solutions and retail prop-firm affiliate sites.</t>
+          <t>231 chars, under the floor. A single GitHub Pages placeholder; recruiting@darkforesttech.com only.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -18688,7 +18692,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Laurion Capital</t>
+          <t>Eisler Capital</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -18698,17 +18702,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>laurion-capital</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>laurioncapitalmanagement (greenhouse)</t>
+          <t>eisler-capital</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>https://eislercapital.com</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Slug resolves but the board has 0 postings. A permanently empty board can only ever look healthy-and-quiet, so it is not added - same call as optiver/marshallwace in Phase 2.</t>
+          <t>DEFUNCT: no A record; www CNAMEs to a torn-down CloudFront distribution. Flagship wound down 31 Dec 2025.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -18730,7 +18734,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Nico Trading</t>
+          <t>Emergent Trading</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -18740,17 +18744,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>nico-trading</t>
+          <t>emergent-trading</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>https://nicotrading.com</t>
+          <t>https://www.emergenttrading.com/join</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>114-byte GoDaddy parking redirect, 0 chars. Firm operating but web-dark.</t>
+          <t>Ember.js shell: /join is the real careers route and returns 0 chars. App and vendor bundles grepped, no ATS and no fetch target.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -18772,7 +18776,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Numerai</t>
+          <t>Freestone Grove Partners</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -18782,17 +18786,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>numerai</t>
+          <t>freestone-grove</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>https://numer.ai/careers</t>
+          <t>https://jobs.gem.com/freestone-grove-partners</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>404. No first-party careers page; Wellfound 403s us and Built In serves nav boilerplate with zero titles.</t>
+          <t>Gem JS shell, 32 chars. Board verified real but empty: the GraphQL POST returns jobPostings: []. Worth re-probing later.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -18814,7 +18818,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Quantitative Investment Management</t>
+          <t>Goldman Sachs Emerging Leaders Series</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -18824,17 +18828,17 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>qim</t>
+          <t>goldman-emerging-leaders</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>https://quantitative.com/</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships/americas/emerging-leaders-series</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Every path 404 while robots.txt returns 200 - the site is genuinely unpublished, not blocking us. Firm is still an active RIA.</t>
+          <t>403 Akamai. higher.gs.com/roles returns 200 but 29 chars (JS shell). Programme is live for 2026 but only reachable at edition-specific Avature URLs that expire.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -18856,7 +18860,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Quantbox Research</t>
+          <t>Kinetic Trading Partners</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -18866,17 +18870,13 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>quantbox-research</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>quantboxresearchpte (greenhouse)</t>
-        </is>
-      </c>
+          <t>kinetic-trading-partners</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7 jobs, junior roles are Amsterdam/Singapore only.</t>
+          <t>Zero LinkedIn results, absent from every quant directory checked. The name collides with Kinetic Partners Management LP, Kinetix Trading Solutions and retail prop-firm affiliate sites.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Quantlab Financial</t>
+          <t>Laurion Capital</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -18908,17 +18908,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>quantlab</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>https://www.quantlab.com/careers</t>
+          <t>laurion-capital</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>laurioncapitalmanagement (greenhouse)</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>403 S3 AccessDenied, 26 chars. Its Jobvite board returns 200 with 237 chars (empty, under the 500 floor) and redirects back into the block.</t>
+          <t>Slug resolves but the board has 0 postings. A permanently empty board can only ever look healthy-and-quiet, so it is not added - same call as optiver/marshallwace in Phase 2.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>QVR Advisors</t>
+          <t>Nico Trading</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -18950,17 +18950,17 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>qvr-advisors</t>
+          <t>nico-trading</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>https://qvradvisors.com</t>
+          <t>https://nicotrading.com</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>DEFUNCT: homepage rewritten to past tense ('was formerly a boutique SEC-registered investment advisor'). Closing after ~30% losses Jan-Apr 2026.</t>
+          <t>114-byte GoDaddy parking redirect, 0 chars. Firm operating but web-dark.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Rosetta Analytics</t>
+          <t>Numerai</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -18992,17 +18992,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>rosetta-analytics</t>
+          <t>numerai</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>https://rosetta-analytics.com/</t>
+          <t>https://numer.ai/careers</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>DEFUNCT: 114 bytes, 0 chars, JS redirect to a parking lander. Closed March 2025.</t>
+          <t>404. No first-party careers page; Wellfound 403s us and Built In serves nav boilerplate with zero titles.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Sensato Investors</t>
+          <t>Quantitative Investment Management</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -19034,17 +19034,17 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>sensato-investors</t>
+          <t>qim</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>https://sensatoinvestors.com</t>
+          <t>https://quantitative.com/</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>HTTPS TLS internal error; over http, 27KB of HTML yields 44 chars. No careers link anywhere.</t>
+          <t>Every path 404 while robots.txt returns 200 - the site is genuinely unpublished, not blocking us. Firm is still an active RIA.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -19066,7 +19066,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Spot Trading</t>
+          <t>Quantbox Research</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -19076,17 +19076,17 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>spot-trading</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>https://spottradingllc.com</t>
+          <t>quantbox-research</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>quantboxresearchpte (greenhouse)</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>DEFUNCT: 'Coming Soon' placeholder, 40 chars. Firm closed 28 Feb 2018.</t>
+          <t>7 jobs, junior roles are Amsterdam/Singapore only.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -19108,7 +19108,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Summerside Capital</t>
+          <t>Quantlab Financial</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -19118,13 +19118,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>summerside-capital</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
+          <t>quantlab</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>https://www.quantlab.com/careers</t>
+        </is>
+      </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>No A record on five domain variants. No trading firm of this name appears to exist.</t>
+          <t>403 S3 AccessDenied, 26 chars. Its Jobvite board returns 200 with 237 chars (empty, under the 500 floor) and redirects back into the block.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -19146,7 +19150,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Tyler Capital</t>
+          <t>QVR Advisors</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -19156,17 +19160,17 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>tyler-capital</t>
+          <t>qvr-advisors</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>https://www.tylercapital.co.uk/</t>
+          <t>https://qvradvisors.com</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Watchable (2,093 chars) but states explicitly: 'we don't run an internship or graduate recruitment program'. UK-only. Not worth a row.</t>
+          <t>DEFUNCT: homepage rewritten to past tense ('was formerly a boutique SEC-registered investment advisor'). Closing after ~30% losses Jan-Apr 2026.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -19188,7 +19192,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>WH Trading</t>
+          <t>Rosetta Analytics</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -19198,17 +19202,17 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>wh-trading</t>
+          <t>rosetta-analytics</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>https://whtrading.com/life-at-wh-trading/</t>
+          <t>https://rosetta-analytics.com/</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Page is 2,320 chars but lists no roles; /careers and /jobs 404. Hiring via opportunities@whtrading.com only.</t>
+          <t>DEFUNCT: 114 bytes, 0 chars, JS redirect to a parking lander. Closed March 2025.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -19230,42 +19234,248 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
+          <t>Sensato Investors</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>sensato-investors</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>https://sensatoinvestors.com</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>HTTPS TLS internal error; over http, 27KB of HTML yields 44 chars. No careers link anywhere.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Spot Trading</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>spot-trading</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>https://spottradingllc.com</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>DEFUNCT: 'Coming Soon' placeholder, 40 chars. Firm closed 28 Feb 2018.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Summerside Capital</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>summerside-capital</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>No A record on five domain variants. No trading firm of this name appears to exist.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Tyler Capital</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>tyler-capital</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tylercapital.co.uk/</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Watchable (2,093 chars) but states explicitly: 'we don't run an internship or graduate recruitment program'. UK-only. Not worth a row.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>WH Trading</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>wh-trading</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>https://whtrading.com/life-at-wh-trading/</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Page is 2,320 chars but lists no roles; /careers and /jobs 404. Hiring via opportunities@whtrading.com only.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>XR Trading</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>firm</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>xr-trading</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>https://www.xrtrading.com/</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Paylocity React shell: board returns 670 chars, all of it 'unsupported browser' boilerplate, zero titles. Bundle grepped - no JSON endpoint exists.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H51"/>
+  <autoFilter ref="A1:H56"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -19291,27 +19501,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Programs'!$A$1:$N$190</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$H$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$H$149</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Applied'!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Discovered'!$A$1:$H$56</definedName>
   </definedNames>
@@ -10559,14 +10559,10 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Morgan Stanley's whole campus board, on Talentlink (morganstanley.tal.net) - 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). Found 2026-09-18 while resolving a pasted posting link. IMPORTANT, the obvious URL is the wrong one: www.morganstanley.com/careers/career-opportunities-search sits behind an Akamai WAF that resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string - same machine, same IP, so the block is User-Agent based and it is the Citadel case, reachable only by misrepresenting the client. Do not re-point a source at it. Morgan Stanley's OTHER board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately NOT watched: it carries 1,327 corporate roles, caps page size at 10 (about 133 requests a day), and a query for 'Sophomore' or 'Freshman' returns zero - the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text, ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect.</t>
-        </is>
-      </c>
-      <c r="H189" s="2" t="inlineStr">
-        <is>
-          <t>morganstanley-campus-p1</t>
-        </is>
-      </c>
+          <t>Morgan Stanley's whole campus board, on Talentlink (morganstanley.tal.net) - 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). Found 2026-09-18 while resolving a pasted posting link. IMPORTANT, the obvious URL is the wrong one: www.morganstanley.com/careers/career-opportunities-search sits behind an Akamai WAF that resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string - same machine, same IP, so the block is User-Agent based and it is the Citadel case, reachable only by misrepresenting the client. Do not re-point a source at it. Morgan Stanley's OTHER board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately NOT watched: it carries 1,327 corporate roles, caps page size at 10 (about 133 requests a day), and a query for 'Sophomore' or 'Freshman' returns zero - the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text, ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect. RETIRED 2026-09-21, asked for directly: this board is no longer watched. It failed on consecutive runs returning only ~350 characters because the Talentlink page renders its listings in JavaScript, and there is no honest route to the same content -- www.morganstanley.com refuses this tracker's User-Agent (the Citadel case) and morganstanley.eightfold.ai does not carry the campus programmes. source_id cleared, so this row is the owner's to check by hand.</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr"/>
       <c r="I189" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -10840,7 +10836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -15262,7 +15258,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>morganstanley-campus-p1</t>
+          <t>open-source-quantitative-finance</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -15272,31 +15268,39 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Open Source Quantitative Finance Conference</t>
+        </is>
+      </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr"/>
+          <t>https://osqf.org/</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:00:58+00:00</t>
+        </is>
+      </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Page 1 of 3 of Morgan Stanley's campus board on Talentlink -- 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). The board pages 50 at a time and ?start= works without the xf-&lt;hash&gt; session token the site's own pagination links carry, so all three pages are watched as separate rows; num/size/limit are ignored. Added 2026-09-18 while resolving a pasted posting link. THE OBVIOUS URL IS THE WRONG ONE: www.morganstanley.com/careers/career-opportunities-search resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string -- same machine, same IP, so the block is User-Agent based and this is the Citadel case. Do not re-point a source at it. Morgan Stanley's other board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately not watched: 1,327 corporate roles, page size hard-capped at 10 (~133 requests a day), and queries for 'Sophomore' and 'Freshman' both return zero -- the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text at ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect.</t>
+          <t>Probed 2026-09-06: 200, 1966 chars of text over plain HTTP.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>morganstanley-campus-p2</t>
+          <t>optiver-futurefocus</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -15306,31 +15310,39 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Optiver FutureFocus</t>
+        </is>
+      </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?start=50</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr"/>
+          <t>https://www.optiver.com/join-us/students/programs/futurefocus/</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:00:58+00:00</t>
+        </is>
+      </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Page 2 of 3 of the Morgan Stanley Campus board; see morganstanley-campus-p1 for the full finding. Probed 2026-09-18: HTTP 200, robots-allowed.</t>
+          <t>Programme page for FutureFocus, Optiver's five-day discovery programme, which the page states is for FIRST and second-year students. Renamed and re-pointed 2026-09-11: the old id and URL (optiver-futurefocus-chicago-2026, /recruitment-events/futurefocus-chicago) baked in a city and a year, and the old URL now 301s here. Verified 2026-09-11: 4,591 chars. Note the page states no graduation-year window, only 'first and second-year', so eligibility cannot be confirmed from it the way Susquehanna's postings can - read the application itself before trusting the label.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>morganstanley-campus-p3</t>
+          <t>optiver-ready-trader</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -15340,31 +15352,39 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Optiver Ready Trader Go</t>
+        </is>
+      </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?start=100</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr"/>
+          <t>https://readytradergo.optiver.com/</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:00:58+00:00</t>
+        </is>
+      </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Page 3 of 3 of the Morgan Stanley Campus board; see morganstanley-campus-p1 for the full finding. Probed 2026-09-18: HTTP 200, robots-allowed.</t>
+          <t>PHASE 3. Verified: 200, ~1KB of text over plain HTTP, no JS needed.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>open-source-quantitative-finance</t>
+          <t>optiver-students</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -15379,12 +15399,12 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Open Source Quantitative Finance Conference</t>
+          <t>Optiver student opportunities</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>https://osqf.org/</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/?level=student</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -15399,14 +15419,14 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 1966 chars of text over plain HTTP.</t>
+          <t>Verified 2026-09-11: 2,349 chars. Optiver's Greenhouse board (optiverprivate) is small, so the student page is the better signal.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>optiver-futurefocus</t>
+          <t>pokerbots</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -15421,12 +15441,12 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Optiver FutureFocus</t>
+          <t>MIT Pokerbots</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>https://www.optiver.com/join-us/students/programs/futurefocus/</t>
+          <t>https://pokerbots.org/</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -15441,14 +15461,14 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Programme page for FutureFocus, Optiver's five-day discovery programme, which the page states is for FIRST and second-year students. Renamed and re-pointed 2026-09-11: the old id and URL (optiver-futurefocus-chicago-2026, /recruitment-events/futurefocus-chicago) baked in a city and a year, and the old URL now 301s here. Verified 2026-09-11: 4,591 chars. Note the page states no graduation-year window, only 'first and second-year', so eligibility cannot be confirmed from it the way Susquehanna's postings can - read the application itself before trusting the label.</t>
+          <t>PHASE 3. Verified: 200, ~6.2KB of text over plain HTTP, no JS needed. Needs a selector - the page retains announcement banners from 2023-2026 in the markup.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>optiver-ready-trader</t>
+          <t>quantbot-careers</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -15458,17 +15478,17 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Optiver Ready Trader Go</t>
+          <t>Quantbot Technologies</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>https://readytradergo.optiver.com/</t>
+          <t>https://www.quantbot.com/careers/</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -15483,14 +15503,14 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>PHASE 3. Verified: 200, ~1KB of text over plain HTTP, no JS needed.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 751 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- quantbot-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>optiver-students</t>
+          <t>rentec-careers</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -15505,12 +15525,12 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Optiver student opportunities</t>
+          <t>Renaissance Technologies</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/?level=student</t>
+          <t>https://www.rentec.com/careers</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -15525,14 +15545,14 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 2,349 chars. Optiver's Greenhouse board (optiverprivate) is small, so the student page is the better signal.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 1,380 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>pokerbots</t>
+          <t>rokos-careers</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -15542,17 +15562,17 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>MIT Pokerbots</t>
+          <t>Rokos Capital</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>https://pokerbots.org/</t>
+          <t>https://www.rokoscapital.com/careers</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -15567,14 +15587,14 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>PHASE 3. Verified: 200, ~6.2KB of text over plain HTTP, no JS needed. Needs a selector - the page retains announcement banners from 2023-2026 in the markup.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 620 chars of text. Close to the 500-char floor; a redesign will trip the shrink guard rather than go quiet.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>quantbot-careers</t>
+          <t>stevens-high-frequency-trading</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -15584,17 +15604,17 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Quantbot Technologies</t>
+          <t>Stevens High Frequency Trading Competition 2026</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>https://www.quantbot.com/careers/</t>
+          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -15609,14 +15629,14 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 751 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- quantbot-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Probed 2026-09-06: 200, 10400 chars of text over plain HTTP, robots.txt allows. Cleanly pollable.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>rentec-careers</t>
+          <t>teza-careers</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -15626,17 +15646,17 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Renaissance Technologies</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>https://www.rentec.com/careers</t>
+          <t>https://www.teza.com/careers/</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -15651,14 +15671,14 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 1,380 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 8,134 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- teza-ashby watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>rokos-careers</t>
+          <t>tgs-join-our-team</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -15673,12 +15693,12 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Rokos Capital</t>
+          <t>TGS Management</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>https://www.rokoscapital.com/careers</t>
+          <t>https://www.tgsmc.com/join-our-team/</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -15693,14 +15713,14 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 620 chars of text. Close to the 500-char floor; a redesign will trip the shrink guard rather than go quiet.</t>
+          <t>Verified 2026-09-11: 1,977 chars. The Lever slug `tgsmc` resolves but returns an empty list, so the page is the only non-alerting surface.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>stevens-high-frequency-trading</t>
+          <t>tradebot-students</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -15710,17 +15730,17 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Stevens High Frequency Trading Competition 2026</t>
+          <t>Tradebot Systems</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
+          <t>https://www.tradebot.com/careers/students</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -15735,14 +15755,14 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 10400 chars of text over plain HTTP, robots.txt allows. Cleanly pollable.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 1,253 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>teza-careers</t>
+          <t>trexquant-students</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -15757,12 +15777,12 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>Trexquant</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>https://www.teza.com/careers/</t>
+          <t>https://trexquant.com/careers/students</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -15777,14 +15797,14 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 8,134 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- teza-ashby watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 891 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>tgs-join-our-team</t>
+          <t>twosigma-campus</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -15794,17 +15814,17 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>TGS Management</t>
+          <t>Two Sigma</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>https://www.tgsmc.com/join-our-team/</t>
+          <t>https://careers.twosigma.com/careers/OpenRoles/</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -15819,14 +15839,14 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 1,977 chars. The Lever slug `tgsmc` resolves but returns an empty list, so the page is the only non-alerting surface.</t>
+          <t>Re-pointed 2026-09-12: the old /careers/students/ url 301'd to the generic /careers/ page and had been reporting success from it. The internships page is the real replacement (9,509 chars, 29 'intern' mentions). No public vendor ATS -- careers.twosigma.com is a custom board with no Greenhouse/Lever/Ashby fingerprint. Correction 2026-09-16: "no public vendor ATS" was wrong in its conclusion though right that there is no Greenhouse/Lever/Ashby fingerprint -- careers.twosigma.com is Avature (CNAME portaltwosigma.avature.net), a vendor ATS this project does not fingerprint. Re-pointed to its OpenRoles listing: 2,676 chars at ratio 0.024, including "AI Research Scientist - Intern [2027 Summer]". Vendor-hosted, so outside the WAF that 403s the runner on www.twosigma.com (WP Engine).</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>tradebot-students</t>
+          <t>vector-roles</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -15836,17 +15856,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Tradebot Systems</t>
+          <t>Vector Trading (Chicago)</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>https://www.tradebot.com/careers/students</t>
+          <t>https://vectortrading.com/data/roles.json</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -15861,14 +15881,14 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 1,253 chars of text.</t>
+          <t>Verified 2026-09-11: The firm's own roles.json, 5 roles, 11,367 chars. 0 student today. Note vectortrading.io and Ashby `vector` are different companies entirely.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>trexquant-students</t>
+          <t>verition-careers</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -15883,12 +15903,12 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Trexquant</t>
+          <t>Verition Fund Management</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>https://trexquant.com/careers/students</t>
+          <t>https://www.verition.com/careers</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -15903,14 +15923,14 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 891 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 11,469 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- verition-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>twosigma-campus</t>
+          <t>volant-careers</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -15920,17 +15940,17 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Two Sigma</t>
+          <t>Volant Trading</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>https://careers.twosigma.com/careers/OpenRoles/</t>
+          <t>https://volanttrading.com/</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -15945,14 +15965,14 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Re-pointed 2026-09-12: the old /careers/students/ url 301'd to the generic /careers/ page and had been reporting success from it. The internships page is the real replacement (9,509 chars, 29 'intern' mentions). No public vendor ATS -- careers.twosigma.com is a custom board with no Greenhouse/Lever/Ashby fingerprint. Correction 2026-09-16: "no public vendor ATS" was wrong in its conclusion though right that there is no Greenhouse/Lever/Ashby fingerprint -- careers.twosigma.com is Avature (CNAME portaltwosigma.avature.net), a vendor ATS this project does not fingerprint. Re-pointed to its OpenRoles listing: 2,676 chars at ratio 0.024, including "AI Research Scientist - Intern [2027 Summer]". Vendor-hosted, so outside the WAF that 403s the runner on www.twosigma.com (WP Engine).</t>
+          <t>Verified 2026-09-11: 2,245 chars. Entry-level roles are Hong Kong only today.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>vector-roles</t>
+          <t>voloridge-join-our-team</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -15962,17 +15982,17 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Vector Trading (Chicago)</t>
+          <t>Voloridge Ascend Program</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>https://vectortrading.com/data/roles.json</t>
+          <t>https://www.voloridge.com/join-our-team</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -15987,14 +16007,14 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: The firm's own roles.json, 5 roles, 11,367 chars. 0 student today. Note vectortrading.io and Ashby `vector` are different companies entirely.</t>
+          <t>Verified 2026-09-11: 9,393 chars. Kept alongside the board because it carries the Ascend eligibility text and cohort size (20 places); board rows carry the posting only.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>verition-careers</t>
+          <t>wincent-careers</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -16009,12 +16029,12 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Verition Fund Management</t>
+          <t>Wincent</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>https://www.verition.com/careers</t>
+          <t>https://www.wincent.com/careers/</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -16029,14 +16049,14 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 11,469 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- verition-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 11,076 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>volant-careers</t>
+          <t>wintermute-careers</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -16046,17 +16066,17 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Volant Trading</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>https://volanttrading.com/</t>
+          <t>https://www.wintermute.com/company/careers</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -16071,14 +16091,14 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 2,245 chars. Entry-level roles are Hong Kong only today.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 14,346 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>voloridge-join-our-team</t>
+          <t>wolverine-careers</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -16088,17 +16108,17 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Voloridge Ascend Program</t>
+          <t>Wolverine Trading</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>https://www.voloridge.com/join-our-team</t>
+          <t>https://careers.wolve.com/postings.json</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -16113,14 +16133,14 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 9,393 chars. Kept alongside the board because it carries the Ascend eligibility text and cohort size (20 places); board rows carry the posting only.</t>
+          <t>Verified 2026-09-11: Pinpoint ATS JSON, 21 postings, 147,741 chars, ratio 0.99. Re-pointed from wolve.com/careers, which is 1,178 chars with zero student hits, and careers.wolve.com, which is a 317-char shell. Caveat: the feed embeds full HTML descriptions, so a reworded description will diff as changed text - if that turns noisy, write a small Pinpoint parser that keeps descriptions out of the snapshot the way the ATS methods do.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>wincent-careers</t>
+          <t>xtx-careers</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -16130,17 +16150,17 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Wincent</t>
+          <t>XTX Markets</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>https://www.wincent.com/careers/</t>
+          <t>https://www.xtxmarkets.com/careers/</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -16155,34 +16175,34 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 11,076 chars of text.</t>
+          <t>XTX is on no public ATS. Verified 2026-09-11: 13,750 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- xtxmarkets-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>wintermute-careers</t>
+          <t>sig-phenom</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>phenom</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Wintermute</t>
+          <t>Susquehanna (SIG)</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>https://www.wintermute.com/company/careers</t>
+          <t>https://careers.sig.com/api/jobs</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -16197,34 +16217,30 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 14,346 chars of text.</t>
+          <t>Phenom/iCIMS JSON API. Replaces the sig-careers manual row, which was correct about the page (402KB of HTML yields 221 chars) and wrong about the firm: this endpoint answers state.USER_AGENT with 263 postings. Verified 2026-09-11: 52 US student rows across Interns + Co-ops, New Graduates and Student Discovery Program. The five US Discovery Programs are gated to winter 2028 / spring 2029 graduates, i.e. sophomores for a four-year US degree, so they are correctly ruled out for class of 2030 until the autumn 2027 cycle.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>wolverine-careers</t>
+          <t>capitalgroup-workday</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>Wolverine Trading</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr"/>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>https://careers.wolve.com/postings.json</t>
+          <t>https://capgroup.wd1.myworkdayjobs.com/wday/cxs/capgroup/capitalgroupcareers</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -16239,34 +16255,30 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: Pinpoint ATS JSON, 21 postings, 147,741 chars, ratio 0.99. Re-pointed from wolve.com/careers, which is 1,178 chars with zero student hits, and careers.wolve.com, which is a 317-char shell. Caveat: the feed embeds full HTML descriptions, so a reworded description will diff as changed text - if that turns noisy, write a small Pinpoint parser that keeps descriptions out of the snapshot the way the ATS methods do.</t>
+          <t>Capital Group. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 1 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>xtx-careers</t>
+          <t>cibc-workday</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>XTX Markets</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr"/>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>https://www.xtxmarkets.com/careers/</t>
+          <t>https://cibc.wd3.myworkdayjobs.com/wday/cxs/cibc/campus</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -16281,34 +16293,34 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>XTX is on no public ATS. Verified 2026-09-11: 13,750 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- xtxmarkets-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>CIBC. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 44 postings on the board, 6 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>sig-phenom</t>
+          <t>cme-workday</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>phenom</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Susquehanna (SIG)</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/api/jobs</t>
+          <t>https://cmegroup.wd1.myworkdayjobs.com/wday/cxs/cmegroup/cme_careers</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -16323,14 +16335,14 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Phenom/iCIMS JSON API. Replaces the sig-careers manual row, which was correct about the page (402KB of HTML yields 221 chars) and wrong about the firm: this endpoint answers state.USER_AGENT with 263 postings. Verified 2026-09-11: 52 US student rows across Interns + Co-ops, New Graduates and Student Discovery Program. The five US Discovery Programs are gated to winter 2028 / spring 2029 graduates, i.e. sophomores for a four-year US degree, so they are correctly ruled out for class of 2030 until the autumn 2027 cycle.</t>
+          <t>Verified 2026-09-11: 33 postings, 0 student today. Use the CXS API only - www.cmegroup.com times out for our User-Agent.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>capitalgroup-workday</t>
+          <t>dimensional-workday</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -16346,7 +16358,7 @@
       <c r="D136" s="2" t="inlineStr"/>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>https://capgroup.wd1.myworkdayjobs.com/wday/cxs/capgroup/capitalgroupcareers</t>
+          <t>https://dimensional.wd5.myworkdayjobs.com/wday/cxs/dimensional/dfa_careers</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -16361,14 +16373,14 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Capital Group. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 1 US student rows.</t>
+          <t>Dimensional Fund Advisors. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 72 postings on the board, 7 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>cibc-workday</t>
+          <t>draftkings-workday</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -16384,7 +16396,7 @@
       <c r="D137" s="2" t="inlineStr"/>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>https://cibc.wd3.myworkdayjobs.com/wday/cxs/cibc/campus</t>
+          <t>https://draftkings.wd1.myworkdayjobs.com/wday/cxs/draftkings/Campus_Career_Portal</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -16399,14 +16411,14 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>CIBC. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 44 postings on the board, 6 US student rows.</t>
+          <t>DraftKings. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 7 postings on the board, 6 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>cme-workday</t>
+          <t>fanniemae-workday</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -16416,17 +16428,13 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>CME Group</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr"/>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>https://cmegroup.wd1.myworkdayjobs.com/wday/cxs/cmegroup/cme_careers</t>
+          <t>https://fanniemae.wd1.myworkdayjobs.com/wday/cxs/fanniemae/FannieMaeCareers</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -16441,14 +16449,14 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 33 postings, 0 student today. Use the CXS API only - www.cmegroup.com times out for our User-Agent.</t>
+          <t>Fannie Mae. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 61 postings on the board, 6 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>dimensional-workday</t>
+          <t>freddiemac-workday</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -16464,7 +16472,7 @@
       <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>https://dimensional.wd5.myworkdayjobs.com/wday/cxs/dimensional/dfa_careers</t>
+          <t>https://freddiemac.wd5.myworkdayjobs.com/wday/cxs/freddiemac/External</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -16479,14 +16487,14 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 72 postings on the board, 7 US student rows.</t>
+          <t>Freddie Mac. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 103 postings on the board, 13 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>draftkings-workday</t>
+          <t>kensho-workday</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -16502,7 +16510,7 @@
       <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>https://draftkings.wd1.myworkdayjobs.com/wday/cxs/draftkings/Campus_Career_Portal</t>
+          <t>https://spgi.wd5.myworkdayjobs.com/wday/cxs/spgi/Kensho_Careers</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -16517,14 +16525,14 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>DraftKings. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 7 postings on the board, 6 US student rows.</t>
+          <t>Kensho (S&amp;P Global). Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 9 postings on the board, 0 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>fanniemae-workday</t>
+          <t>lpl-workday</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -16540,7 +16548,7 @@
       <c r="D141" s="2" t="inlineStr"/>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>https://fanniemae.wd1.myworkdayjobs.com/wday/cxs/fanniemae/FannieMaeCareers</t>
+          <t>https://lplfinancial.wd1.myworkdayjobs.com/wday/cxs/lplfinancial/university</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -16555,14 +16563,14 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Fannie Mae. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 61 postings on the board, 6 US student rows.</t>
+          <t>LPL Financial. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 36 postings on the board, 16 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>freddiemac-workday</t>
+          <t>mastercard-workday</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -16578,7 +16586,7 @@
       <c r="D142" s="2" t="inlineStr"/>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>https://freddiemac.wd5.myworkdayjobs.com/wday/cxs/freddiemac/External</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/wday/cxs/mastercard/Campus</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -16593,14 +16601,14 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Freddie Mac. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 103 postings on the board, 13 US student rows.</t>
+          <t>Mastercard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 52 postings on the board, 1 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>kensho-workday</t>
+          <t>northerntrust-workday</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -16616,7 +16624,7 @@
       <c r="D143" s="2" t="inlineStr"/>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>https://spgi.wd5.myworkdayjobs.com/wday/cxs/spgi/Kensho_Careers</t>
+          <t>https://ntrs.wd1.myworkdayjobs.com/wday/cxs/ntrs/northerntrust</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -16631,14 +16639,14 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Kensho (S&amp;P Global). Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 9 postings on the board, 0 US student rows.</t>
+          <t>Northern Trust. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 665 postings on the board, 20 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>lpl-workday</t>
+          <t>peak6-workday</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -16648,13 +16656,17 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>PEAK6</t>
+        </is>
+      </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>https://lplfinancial.wd1.myworkdayjobs.com/wday/cxs/lplfinancial/university</t>
+          <t>https://peak6group.wd1.myworkdayjobs.com/wday/cxs/peak6group/PEAK6</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -16669,14 +16681,14 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>LPL Financial. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 36 postings on the board, 16 US student rows.</t>
+          <t>Verified 2026-09-11: 14 postings, 3 US student rows (Trading Bootcamp Micro-Internship Summer 2027, Trading Internship for Women+ Summer 2027, Trading Associate 2027). Re-pointed from peak6.com/careers, which returns 3,100 chars of marketing copy with no job data and no outbound job links - a row that could only ever look healthy and quiet.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>mastercard-workday</t>
+          <t>pimco-workday</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -16692,7 +16704,7 @@
       <c r="D145" s="2" t="inlineStr"/>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/wday/cxs/mastercard/Campus</t>
+          <t>https://pimco.wd1.myworkdayjobs.com/wday/cxs/pimco/pimco-careers</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -16707,14 +16719,14 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Mastercard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 52 postings on the board, 1 US student rows.</t>
+          <t>PIMCO. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 195 postings on the board, 7 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>northerntrust-workday</t>
+          <t>rbc-workday</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -16730,7 +16742,7 @@
       <c r="D146" s="2" t="inlineStr"/>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>https://ntrs.wd1.myworkdayjobs.com/wday/cxs/ntrs/northerntrust</t>
+          <t>https://rbc.wd3.myworkdayjobs.com/wday/cxs/rbc/RBCEARLYTALENT1</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -16745,14 +16757,14 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Northern Trust. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 665 postings on the board, 20 US student rows.</t>
+          <t>RBC Early Talent. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 3 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>peak6-workday</t>
+          <t>troweprice-workday</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -16762,17 +16774,13 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>PEAK6</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr"/>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>https://peak6group.wd1.myworkdayjobs.com/wday/cxs/peak6group/PEAK6</t>
+          <t>https://troweprice.wd5.myworkdayjobs.com/wday/cxs/troweprice/TRowePrice</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -16787,14 +16795,14 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 14 postings, 3 US student rows (Trading Bootcamp Micro-Internship Summer 2027, Trading Internship for Women+ Summer 2027, Trading Associate 2027). Re-pointed from peak6.com/careers, which returns 3,100 chars of marketing copy with no job data and no outbound job links - a row that could only ever look healthy and quiet.</t>
+          <t>T. Rowe Price. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 136 postings on the board, 8 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>pimco-workday</t>
+          <t>vanguard-workday</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -16810,7 +16818,7 @@
       <c r="D148" s="2" t="inlineStr"/>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>https://pimco.wd1.myworkdayjobs.com/wday/cxs/pimco/pimco-careers</t>
+          <t>https://vanguard.wd5.myworkdayjobs.com/wday/cxs/vanguard/vanguard_external</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -16825,14 +16833,14 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>PIMCO. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 195 postings on the board, 7 US student rows.</t>
+          <t>Vanguard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 441 postings on the board, 18 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>rbc-workday</t>
+          <t>wellington-workday</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -16848,7 +16856,7 @@
       <c r="D149" s="2" t="inlineStr"/>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>https://rbc.wd3.myworkdayjobs.com/wday/cxs/rbc/RBCEARLYTALENT1</t>
+          <t>https://wellington.wd5.myworkdayjobs.com/wday/cxs/wellington/Campus</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -16863,126 +16871,12 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>RBC Early Talent. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 3 US student rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>troweprice-workday</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr"/>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>https://troweprice.wd5.myworkdayjobs.com/wday/cxs/troweprice/TRowePrice</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21T14:00:58+00:00</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>T. Rowe Price. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 136 postings on the board, 8 US student rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>vanguard-workday</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr"/>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>https://vanguard.wd5.myworkdayjobs.com/wday/cxs/vanguard/vanguard_external</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21T14:00:58+00:00</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>Vanguard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 441 postings on the board, 18 US student rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>wellington-workday</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr"/>
-      <c r="E152" s="3" t="inlineStr">
-        <is>
-          <t>https://wellington.wd5.myworkdayjobs.com/wday/cxs/wellington/Campus</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21T14:00:58+00:00</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
           <t>Wellington Management. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 10 postings on the board, 4 US student rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H152"/>
+  <autoFilter ref="A1:H149"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId2"/>
@@ -17066,9 +16960,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Programs'!$A$1:$N$190</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$H$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$H$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Applied'!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Discovered'!$A$1:$H$56</definedName>
   </definedNames>
@@ -10836,7 +10836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -15594,7 +15594,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>stevens-high-frequency-trading</t>
+          <t>solayer-careers</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -15604,24 +15604,20 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Stevens High Frequency Trading Competition 2026</t>
+          <t>Solayer Labs</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21T14:00:58+00:00</t>
-        </is>
-      </c>
+          <t>https://solayer.org/careers</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15629,14 +15625,14 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Probed 2026-09-06: 200, 10400 chars of text over plain HTTP, robots.txt allows. Cleanly pollable.</t>
+          <t>Added 2026-09-21 from a link the owner pasted. Whole careers page, not a programme page: Solayer Labs (Solana/SVM infrastructure and payments, San Mateo CA) is on no public ATS - 226KB of Framer HTML with no greenhouse/lever/ashby/workday/iCIMS fingerprint and no external apply link, so the page itself is the durable target. Probed: HTTP 200, 2,514 characters of visible text, ratio 0.011, roles are server-rendered and clear both content floors; robots.txt allows. One role listed on the day it was added - Marketing Lead, full-time permanent, master's required, apply by posting a resume with code SLML - which is off-field and not applicable; watched for the engineering and internship postings it may carry later.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>teza-careers</t>
+          <t>stevens-high-frequency-trading</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -15646,17 +15642,17 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>Stevens High Frequency Trading Competition 2026</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>https://www.teza.com/careers/</t>
+          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -15671,14 +15667,14 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 8,134 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- teza-ashby watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Probed 2026-09-06: 200, 10400 chars of text over plain HTTP, robots.txt allows. Cleanly pollable.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>tgs-join-our-team</t>
+          <t>teza-careers</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -15688,17 +15684,17 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>TGS Management</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>https://www.tgsmc.com/join-our-team/</t>
+          <t>https://www.teza.com/careers/</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -15713,14 +15709,14 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 1,977 chars. The Lever slug `tgsmc` resolves but returns an empty list, so the page is the only non-alerting surface.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 8,134 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- teza-ashby watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>tradebot-students</t>
+          <t>tgs-join-our-team</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -15730,17 +15726,17 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Tradebot Systems</t>
+          <t>TGS Management</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>https://www.tradebot.com/careers/students</t>
+          <t>https://www.tgsmc.com/join-our-team/</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -15755,14 +15751,14 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 1,253 chars of text.</t>
+          <t>Verified 2026-09-11: 1,977 chars. The Lever slug `tgsmc` resolves but returns an empty list, so the page is the only non-alerting surface.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>trexquant-students</t>
+          <t>tradebot-students</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -15777,12 +15773,12 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Trexquant</t>
+          <t>Tradebot Systems</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>https://trexquant.com/careers/students</t>
+          <t>https://www.tradebot.com/careers/students</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -15797,14 +15793,14 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 891 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 1,253 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>twosigma-campus</t>
+          <t>trexquant-students</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -15814,17 +15810,17 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Two Sigma</t>
+          <t>Trexquant</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>https://careers.twosigma.com/careers/OpenRoles/</t>
+          <t>https://trexquant.com/careers/students</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -15839,14 +15835,14 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Re-pointed 2026-09-12: the old /careers/students/ url 301'd to the generic /careers/ page and had been reporting success from it. The internships page is the real replacement (9,509 chars, 29 'intern' mentions). No public vendor ATS -- careers.twosigma.com is a custom board with no Greenhouse/Lever/Ashby fingerprint. Correction 2026-09-16: "no public vendor ATS" was wrong in its conclusion though right that there is no Greenhouse/Lever/Ashby fingerprint -- careers.twosigma.com is Avature (CNAME portaltwosigma.avature.net), a vendor ATS this project does not fingerprint. Re-pointed to its OpenRoles listing: 2,676 chars at ratio 0.024, including "AI Research Scientist - Intern [2027 Summer]". Vendor-hosted, so outside the WAF that 403s the runner on www.twosigma.com (WP Engine).</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 891 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>vector-roles</t>
+          <t>twosigma-campus</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -15856,17 +15852,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Vector Trading (Chicago)</t>
+          <t>Two Sigma</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>https://vectortrading.com/data/roles.json</t>
+          <t>https://careers.twosigma.com/careers/OpenRoles/</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -15881,14 +15877,14 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: The firm's own roles.json, 5 roles, 11,367 chars. 0 student today. Note vectortrading.io and Ashby `vector` are different companies entirely.</t>
+          <t>Re-pointed 2026-09-12: the old /careers/students/ url 301'd to the generic /careers/ page and had been reporting success from it. The internships page is the real replacement (9,509 chars, 29 'intern' mentions). No public vendor ATS -- careers.twosigma.com is a custom board with no Greenhouse/Lever/Ashby fingerprint. Correction 2026-09-16: "no public vendor ATS" was wrong in its conclusion though right that there is no Greenhouse/Lever/Ashby fingerprint -- careers.twosigma.com is Avature (CNAME portaltwosigma.avature.net), a vendor ATS this project does not fingerprint. Re-pointed to its OpenRoles listing: 2,676 chars at ratio 0.024, including "AI Research Scientist - Intern [2027 Summer]". Vendor-hosted, so outside the WAF that 403s the runner on www.twosigma.com (WP Engine).</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>verition-careers</t>
+          <t>vector-roles</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -15898,17 +15894,17 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Verition Fund Management</t>
+          <t>Vector Trading (Chicago)</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>https://www.verition.com/careers</t>
+          <t>https://vectortrading.com/data/roles.json</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -15923,14 +15919,14 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 11,469 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- verition-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Verified 2026-09-11: The firm's own roles.json, 5 roles, 11,367 chars. 0 student today. Note vectortrading.io and Ashby `vector` are different companies entirely.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>volant-careers</t>
+          <t>verition-careers</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -15940,17 +15936,17 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Volant Trading</t>
+          <t>Verition Fund Management</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>https://volanttrading.com/</t>
+          <t>https://www.verition.com/careers</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -15965,14 +15961,14 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 2,245 chars. Entry-level roles are Hong Kong only today.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 11,469 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- verition-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>voloridge-join-our-team</t>
+          <t>volant-careers</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -15982,17 +15978,17 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Voloridge Ascend Program</t>
+          <t>Volant Trading</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>https://www.voloridge.com/join-our-team</t>
+          <t>https://volanttrading.com/</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -16007,14 +16003,14 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 9,393 chars. Kept alongside the board because it carries the Ascend eligibility text and cohort size (20 places); board rows carry the posting only.</t>
+          <t>Verified 2026-09-11: 2,245 chars. Entry-level roles are Hong Kong only today.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>wincent-careers</t>
+          <t>voloridge-join-our-team</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -16024,17 +16020,17 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Wincent</t>
+          <t>Voloridge Ascend Program</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>https://www.wincent.com/careers/</t>
+          <t>https://www.voloridge.com/join-our-team</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -16049,14 +16045,14 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 11,076 chars of text.</t>
+          <t>Verified 2026-09-11: 9,393 chars. Kept alongside the board because it carries the Ascend eligibility text and cohort size (20 places); board rows carry the posting only.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>wintermute-careers</t>
+          <t>wincent-careers</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -16071,12 +16067,12 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Wintermute</t>
+          <t>Wincent</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>https://www.wintermute.com/company/careers</t>
+          <t>https://www.wincent.com/careers/</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -16091,14 +16087,14 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Firm is on no public ATS. Verified 2026-09-11: 14,346 chars of text.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 11,076 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>wolverine-careers</t>
+          <t>wintermute-careers</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -16113,12 +16109,12 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Wolverine Trading</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>https://careers.wolve.com/postings.json</t>
+          <t>https://www.wintermute.com/company/careers</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -16133,14 +16129,14 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: Pinpoint ATS JSON, 21 postings, 147,741 chars, ratio 0.99. Re-pointed from wolve.com/careers, which is 1,178 chars with zero student hits, and careers.wolve.com, which is a 317-char shell. Caveat: the feed embeds full HTML descriptions, so a reworded description will diff as changed text - if that turns noisy, write a small Pinpoint parser that keeps descriptions out of the snapshot the way the ATS methods do.</t>
+          <t>Firm is on no public ATS. Verified 2026-09-11: 14,346 chars of text.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>xtx-careers</t>
+          <t>wolverine-careers</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -16150,17 +16146,17 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>XTX Markets</t>
+          <t>Wolverine Trading</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>https://www.xtxmarkets.com/careers/</t>
+          <t>https://careers.wolve.com/postings.json</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -16175,19 +16171,19 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>XTX is on no public ATS. Verified 2026-09-11: 13,750 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- xtxmarkets-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
+          <t>Verified 2026-09-11: Pinpoint ATS JSON, 21 postings, 147,741 chars, ratio 0.99. Re-pointed from wolve.com/careers, which is 1,178 chars with zero student hits, and careers.wolve.com, which is a 317-char shell. Caveat: the feed embeds full HTML descriptions, so a reworded description will diff as changed text - if that turns noisy, write a small Pinpoint parser that keeps descriptions out of the snapshot the way the ATS methods do.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>sig-phenom</t>
+          <t>xtx-careers</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>phenom</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -16197,12 +16193,12 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Susquehanna (SIG)</t>
+          <t>XTX Markets</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/api/jobs</t>
+          <t>https://www.xtxmarkets.com/careers/</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -16217,30 +16213,34 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Phenom/iCIMS JSON API. Replaces the sig-careers manual row, which was correct about the page (402KB of HTML yields 221 chars) and wrong about the firm: this endpoint answers state.USER_AGENT with 263 postings. Verified 2026-09-11: 52 US student rows across Interns + Co-ops, New Graduates and Student Discovery Program. The five US Discovery Programs are gated to winter 2028 / spring 2029 graduates, i.e. sophomores for a four-year US degree, so they are correctly ruled out for class of 2030 until the autumn 2027 cycle.</t>
+          <t>XTX is on no public ATS. Verified 2026-09-11: 13,750 chars of text. CORRECTED 2026-09-12: the 'no public ATS' claim above is false -- xtxmarkets-greenhouse watches the real board, found by a domain-anchored fingerprint probe. This page_text row is kept because the page may still carry programme detail the board rows do not state; retire it if it proves redundant.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>capitalgroup-workday</t>
+          <t>sig-phenom</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>phenom</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Susquehanna (SIG)</t>
+        </is>
+      </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>https://capgroup.wd1.myworkdayjobs.com/wday/cxs/capgroup/capitalgroupcareers</t>
+          <t>https://careers.sig.com/api/jobs</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -16255,14 +16255,14 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Capital Group. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 1 US student rows.</t>
+          <t>Phenom/iCIMS JSON API. Replaces the sig-careers manual row, which was correct about the page (402KB of HTML yields 221 chars) and wrong about the firm: this endpoint answers state.USER_AGENT with 263 postings. Verified 2026-09-11: 52 US student rows across Interns + Co-ops, New Graduates and Student Discovery Program. The five US Discovery Programs are gated to winter 2028 / spring 2029 graduates, i.e. sophomores for a four-year US degree, so they are correctly ruled out for class of 2030 until the autumn 2027 cycle.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>cibc-workday</t>
+          <t>capitalgroup-workday</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -16278,7 +16278,7 @@
       <c r="D134" s="2" t="inlineStr"/>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>https://cibc.wd3.myworkdayjobs.com/wday/cxs/cibc/campus</t>
+          <t>https://capgroup.wd1.myworkdayjobs.com/wday/cxs/capgroup/capitalgroupcareers</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -16293,14 +16293,14 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>CIBC. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 44 postings on the board, 6 US student rows.</t>
+          <t>Capital Group. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 1 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>cme-workday</t>
+          <t>cibc-workday</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -16310,17 +16310,13 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>CME Group</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr"/>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>https://cmegroup.wd1.myworkdayjobs.com/wday/cxs/cmegroup/cme_careers</t>
+          <t>https://cibc.wd3.myworkdayjobs.com/wday/cxs/cibc/campus</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -16335,14 +16331,14 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 33 postings, 0 student today. Use the CXS API only - www.cmegroup.com times out for our User-Agent.</t>
+          <t>CIBC. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 44 postings on the board, 6 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>dimensional-workday</t>
+          <t>cme-workday</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -16352,13 +16348,17 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>CME Group</t>
+        </is>
+      </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>https://dimensional.wd5.myworkdayjobs.com/wday/cxs/dimensional/dfa_careers</t>
+          <t>https://cmegroup.wd1.myworkdayjobs.com/wday/cxs/cmegroup/cme_careers</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -16373,14 +16373,14 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 72 postings on the board, 7 US student rows.</t>
+          <t>Verified 2026-09-11: 33 postings, 0 student today. Use the CXS API only - www.cmegroup.com times out for our User-Agent.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>draftkings-workday</t>
+          <t>dimensional-workday</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -16396,7 +16396,7 @@
       <c r="D137" s="2" t="inlineStr"/>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>https://draftkings.wd1.myworkdayjobs.com/wday/cxs/draftkings/Campus_Career_Portal</t>
+          <t>https://dimensional.wd5.myworkdayjobs.com/wday/cxs/dimensional/dfa_careers</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -16411,14 +16411,14 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>DraftKings. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 7 postings on the board, 6 US student rows.</t>
+          <t>Dimensional Fund Advisors. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 72 postings on the board, 7 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>fanniemae-workday</t>
+          <t>draftkings-workday</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -16434,7 +16434,7 @@
       <c r="D138" s="2" t="inlineStr"/>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>https://fanniemae.wd1.myworkdayjobs.com/wday/cxs/fanniemae/FannieMaeCareers</t>
+          <t>https://draftkings.wd1.myworkdayjobs.com/wday/cxs/draftkings/Campus_Career_Portal</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -16449,14 +16449,14 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Fannie Mae. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 61 postings on the board, 6 US student rows.</t>
+          <t>DraftKings. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 7 postings on the board, 6 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>freddiemac-workday</t>
+          <t>fanniemae-workday</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -16472,7 +16472,7 @@
       <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>https://freddiemac.wd5.myworkdayjobs.com/wday/cxs/freddiemac/External</t>
+          <t>https://fanniemae.wd1.myworkdayjobs.com/wday/cxs/fanniemae/FannieMaeCareers</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -16487,14 +16487,14 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Freddie Mac. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 103 postings on the board, 13 US student rows.</t>
+          <t>Fannie Mae. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 61 postings on the board, 6 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>kensho-workday</t>
+          <t>freddiemac-workday</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -16510,7 +16510,7 @@
       <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>https://spgi.wd5.myworkdayjobs.com/wday/cxs/spgi/Kensho_Careers</t>
+          <t>https://freddiemac.wd5.myworkdayjobs.com/wday/cxs/freddiemac/External</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -16525,14 +16525,14 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Kensho (S&amp;P Global). Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 9 postings on the board, 0 US student rows.</t>
+          <t>Freddie Mac. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 103 postings on the board, 13 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>lpl-workday</t>
+          <t>kensho-workday</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -16548,7 +16548,7 @@
       <c r="D141" s="2" t="inlineStr"/>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>https://lplfinancial.wd1.myworkdayjobs.com/wday/cxs/lplfinancial/university</t>
+          <t>https://spgi.wd5.myworkdayjobs.com/wday/cxs/spgi/Kensho_Careers</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -16563,14 +16563,14 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>LPL Financial. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 36 postings on the board, 16 US student rows.</t>
+          <t>Kensho (S&amp;P Global). Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 9 postings on the board, 0 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>mastercard-workday</t>
+          <t>lpl-workday</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -16586,7 +16586,7 @@
       <c r="D142" s="2" t="inlineStr"/>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/wday/cxs/mastercard/Campus</t>
+          <t>https://lplfinancial.wd1.myworkdayjobs.com/wday/cxs/lplfinancial/university</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -16601,14 +16601,14 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Mastercard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 52 postings on the board, 1 US student rows.</t>
+          <t>LPL Financial. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 36 postings on the board, 16 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>northerntrust-workday</t>
+          <t>mastercard-workday</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -16624,7 +16624,7 @@
       <c r="D143" s="2" t="inlineStr"/>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>https://ntrs.wd1.myworkdayjobs.com/wday/cxs/ntrs/northerntrust</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/wday/cxs/mastercard/Campus</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -16639,14 +16639,14 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Northern Trust. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 665 postings on the board, 20 US student rows.</t>
+          <t>Mastercard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 52 postings on the board, 1 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>peak6-workday</t>
+          <t>northerntrust-workday</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -16656,17 +16656,13 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>PEAK6</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr"/>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>https://peak6group.wd1.myworkdayjobs.com/wday/cxs/peak6group/PEAK6</t>
+          <t>https://ntrs.wd1.myworkdayjobs.com/wday/cxs/ntrs/northerntrust</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -16681,14 +16677,14 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 14 postings, 3 US student rows (Trading Bootcamp Micro-Internship Summer 2027, Trading Internship for Women+ Summer 2027, Trading Associate 2027). Re-pointed from peak6.com/careers, which returns 3,100 chars of marketing copy with no job data and no outbound job links - a row that could only ever look healthy and quiet.</t>
+          <t>Northern Trust. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 665 postings on the board, 20 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>pimco-workday</t>
+          <t>peak6-workday</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -16698,13 +16694,17 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>PEAK6</t>
+        </is>
+      </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>https://pimco.wd1.myworkdayjobs.com/wday/cxs/pimco/pimco-careers</t>
+          <t>https://peak6group.wd1.myworkdayjobs.com/wday/cxs/peak6group/PEAK6</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -16719,14 +16719,14 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>PIMCO. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 195 postings on the board, 7 US student rows.</t>
+          <t>Verified 2026-09-11: 14 postings, 3 US student rows (Trading Bootcamp Micro-Internship Summer 2027, Trading Internship for Women+ Summer 2027, Trading Associate 2027). Re-pointed from peak6.com/careers, which returns 3,100 chars of marketing copy with no job data and no outbound job links - a row that could only ever look healthy and quiet.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>rbc-workday</t>
+          <t>pimco-workday</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -16742,7 +16742,7 @@
       <c r="D146" s="2" t="inlineStr"/>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>https://rbc.wd3.myworkdayjobs.com/wday/cxs/rbc/RBCEARLYTALENT1</t>
+          <t>https://pimco.wd1.myworkdayjobs.com/wday/cxs/pimco/pimco-careers</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -16757,14 +16757,14 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>RBC Early Talent. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 3 US student rows.</t>
+          <t>PIMCO. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 195 postings on the board, 7 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>troweprice-workday</t>
+          <t>rbc-workday</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -16780,7 +16780,7 @@
       <c r="D147" s="2" t="inlineStr"/>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>https://troweprice.wd5.myworkdayjobs.com/wday/cxs/troweprice/TRowePrice</t>
+          <t>https://rbc.wd3.myworkdayjobs.com/wday/cxs/rbc/RBCEARLYTALENT1</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -16795,14 +16795,14 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>T. Rowe Price. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 136 postings on the board, 8 US student rows.</t>
+          <t>RBC Early Talent. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 152 postings on the board, 3 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>vanguard-workday</t>
+          <t>troweprice-workday</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -16818,7 +16818,7 @@
       <c r="D148" s="2" t="inlineStr"/>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>https://vanguard.wd5.myworkdayjobs.com/wday/cxs/vanguard/vanguard_external</t>
+          <t>https://troweprice.wd5.myworkdayjobs.com/wday/cxs/troweprice/TRowePrice</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -16833,14 +16833,14 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Vanguard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 441 postings on the board, 18 US student rows.</t>
+          <t>T. Rowe Price. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 136 postings on the board, 8 US student rows.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>wellington-workday</t>
+          <t>vanguard-workday</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -16856,27 +16856,65 @@
       <c r="D149" s="2" t="inlineStr"/>
       <c r="E149" s="3" t="inlineStr">
         <is>
+          <t>https://vanguard.wd5.myworkdayjobs.com/wday/cxs/vanguard/vanguard_external</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:00:58+00:00</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>Vanguard. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 441 postings on the board, 18 US student rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>wellington-workday</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr"/>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
           <t>https://wellington.wd5.myworkdayjobs.com/wday/cxs/wellington/Campus</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>2026-09-21T14:00:58+00:00</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>Wellington Management. Workday CXS JSON API - the HTML page renders in JavaScript and yields zero text. Verified 2026-09-11: 10 postings on the board, 4 US student rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H149"/>
+  <autoFilter ref="A1:H150"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId2"/>
@@ -16960,6 +16998,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId83"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>f1c69c6c475a19aa68fc1c7a194bfd8553efa4b3521c9f917b1785f1c913e0a1</t>
+          <t>7c177cf55b24ea1cfcfef30c9acbe7b9219b6ea5c191c0e78820e7d94f81a0e3</t>
         </is>
       </c>
     </row>
@@ -7942,12 +7942,12 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>9b4b34980e7e1794b0658c67468a5ddf19c7220395b0394af11b794579fe2e2e</t>
+          <t>5211633896d1f19a2c25272d82debf587fe742b7b9611d3239d20246ed9b2213</t>
         </is>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12389,7 +12389,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13189,7 +13189,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13265,7 +13265,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13733,7 +13733,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -13943,7 +13943,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -14027,7 +14027,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -14069,7 +14069,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -14359,7 +14359,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14485,7 +14485,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14569,7 +14569,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14653,7 +14653,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14779,7 +14779,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14821,7 +14821,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -14863,7 +14863,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14989,7 +14989,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -15073,7 +15073,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15157,7 +15157,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15241,7 +15241,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -15535,7 +15535,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15617,7 +15617,11 @@
           <t>https://solayer.org/careers</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:39:39+00:00</t>
+        </is>
+      </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -15657,7 +15661,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15699,7 +15703,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15741,7 +15745,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15783,7 +15787,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15825,7 +15829,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15867,7 +15871,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15909,7 +15913,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15951,7 +15955,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15993,7 +15997,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -16035,7 +16039,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -16077,7 +16081,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -16119,7 +16123,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16161,7 +16165,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -16203,7 +16207,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -16245,7 +16249,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16283,7 +16287,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16321,7 +16325,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16363,7 +16367,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16401,7 +16405,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16439,7 +16443,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16477,7 +16481,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16515,7 +16519,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16553,7 +16557,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16591,7 +16595,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16629,7 +16633,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16667,7 +16671,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16709,7 +16713,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16747,7 +16751,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -16785,7 +16789,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16823,7 +16827,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16861,7 +16865,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -16899,7 +16903,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T14:00:58+00:00</t>
+          <t>2026-09-22T12:39:39+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2873,15 +2873,19 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>open</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t>2026-09-23T12:49:57+00:00</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23T12:49:57+00:00</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -2890,7 +2894,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>36cfe7e7863f9d1460b8dc4a91e8c1baec01e9664a492fb99d918b34bf2b6ea3</t>
+          <t>2959d548616852711e1dc9a8dabc9bed791fca8d77122e8792af1c662e96519b</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4486,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7810,7 +7814,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7874,12 +7878,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7890,7 +7894,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>7c177cf55b24ea1cfcfef30c9acbe7b9219b6ea5c191c0e78820e7d94f81a0e3</t>
+          <t>d874699a98a98c1eb6c7ef79f07d060a6e16093391ef7df0168b3c8947dd3762</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7946,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8010,7 +8014,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8074,7 +8078,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8410,7 +8414,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8478,7 +8482,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8546,7 +8550,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8674,7 +8678,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8742,7 +8746,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8814,7 +8818,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10506,7 +10510,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10915,7 +10919,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10953,7 +10957,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10991,7 +10995,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11029,7 +11033,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11067,7 +11071,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11105,7 +11109,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11147,7 +11151,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11189,7 +11193,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11231,7 +11235,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11273,7 +11277,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11315,7 +11319,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11357,7 +11361,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11399,7 +11403,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11437,7 +11441,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11479,7 +11483,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11517,7 +11521,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11559,7 +11563,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11601,7 +11605,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11643,7 +11647,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11685,7 +11689,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11723,7 +11727,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11761,7 +11765,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11799,7 +11803,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11841,7 +11845,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11883,7 +11887,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11921,7 +11925,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11959,7 +11963,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12001,7 +12005,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12039,7 +12043,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12081,7 +12085,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12119,7 +12123,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12157,7 +12161,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12195,7 +12199,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12233,7 +12237,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12271,7 +12275,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12309,7 +12313,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12351,7 +12355,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12389,7 +12393,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12431,7 +12435,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12473,7 +12477,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12511,7 +12515,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12549,7 +12553,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12587,7 +12591,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12629,7 +12633,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12667,7 +12671,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12709,7 +12713,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12751,7 +12755,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12789,7 +12793,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12831,7 +12835,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12873,7 +12877,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12911,7 +12915,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12949,7 +12953,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12991,7 +12995,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -13033,7 +13037,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -13075,7 +13079,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13113,7 +13117,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13151,7 +13155,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13189,7 +13193,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13227,7 +13231,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13265,7 +13269,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13307,7 +13311,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13345,7 +13349,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13387,7 +13391,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13425,7 +13429,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13463,7 +13467,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13501,7 +13505,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13539,7 +13543,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13733,7 +13737,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -13780,7 +13784,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -13817,7 +13821,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -13859,7 +13863,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13901,7 +13905,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -13943,7 +13947,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13985,7 +13989,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -14027,7 +14031,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -14069,7 +14073,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -14111,7 +14115,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14153,7 +14157,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14195,7 +14199,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -14233,7 +14237,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14275,7 +14279,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14317,7 +14321,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -14359,7 +14363,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14401,7 +14405,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14443,7 +14447,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14485,7 +14489,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14527,7 +14531,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14569,7 +14573,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14611,7 +14615,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14653,7 +14657,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -14695,7 +14699,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14737,7 +14741,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14779,7 +14783,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14821,7 +14825,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -14863,7 +14867,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14905,7 +14909,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14947,7 +14951,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14989,7 +14993,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -15031,7 +15035,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -15073,7 +15077,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -15115,7 +15119,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15157,7 +15161,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15199,7 +15203,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15241,7 +15245,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15283,7 +15287,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15325,7 +15329,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15367,7 +15371,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15409,7 +15413,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15451,7 +15455,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15493,7 +15497,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -15535,7 +15539,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15577,7 +15581,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15619,7 +15623,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15661,7 +15665,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15703,7 +15707,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15745,7 +15749,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15787,7 +15791,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15829,7 +15833,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15871,7 +15875,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15913,7 +15917,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15955,7 +15959,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15997,7 +16001,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -16039,7 +16043,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -16081,7 +16085,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -16123,7 +16127,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16165,7 +16169,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -16207,7 +16211,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -16249,7 +16253,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16287,7 +16291,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16325,7 +16329,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16367,7 +16371,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16405,7 +16409,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16443,7 +16447,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16481,7 +16485,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16519,7 +16523,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16557,7 +16561,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16595,7 +16599,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16633,7 +16637,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16671,7 +16675,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16713,7 +16717,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16751,7 +16755,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -16789,7 +16793,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16827,7 +16831,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16865,7 +16869,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -16903,7 +16907,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-23T12:49:57+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7878,12 +7878,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>d874699a98a98c1eb6c7ef79f07d060a6e16093391ef7df0168b3c8947dd3762</t>
+          <t>f54812d8301383ddec3b01e830249087e4ff30b95a4a40528d71c41c593cfb07</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10919,7 +10919,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11765,7 +11765,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12713,7 +12713,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13505,7 +13505,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14405,7 +14405,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14489,7 +14489,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14909,7 +14909,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -15035,7 +15035,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -15077,7 +15077,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15329,7 +15329,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15497,7 +15497,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15665,7 +15665,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15754,7 +15754,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15833,7 +15833,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15875,7 +15875,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15917,7 +15917,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15959,7 +15959,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -16085,7 +16085,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16329,7 +16329,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16447,7 +16447,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16485,7 +16485,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16523,7 +16523,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16561,7 +16561,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16599,7 +16599,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16675,7 +16675,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16717,7 +16717,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -16793,7 +16793,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16869,7 +16869,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-24T12:48:38+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7878,12 +7878,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>f54812d8301383ddec3b01e830249087e4ff30b95a4a40528d71c41c593cfb07</t>
+          <t>9d50868a4f375af4073f1702fa95c5beab51ce17ecb88c6afbda4f6caaea8e5d</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8482,10 +8482,14 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
-        </is>
-      </c>
-      <c r="K153" s="2" t="inlineStr"/>
+          <t>2026-09-25T12:50:11+00:00</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:50:11+00:00</t>
+        </is>
+      </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
           <t>2026-09-06</t>
@@ -8498,7 +8502,7 @@
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>9ffe37a558c138b12b627dad42b2b5031f97c8f9606ff73420c4d90e25a5aa62</t>
+          <t>6719b2608fc54b0cd475a3bec8eddd667a0640a47d368c62655d2344e22e2a66</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8554,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8678,7 +8682,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8746,7 +8750,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8818,7 +8822,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10510,7 +10514,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10919,7 +10923,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10957,7 +10961,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10995,7 +10999,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11033,7 +11037,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11071,7 +11075,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11109,7 +11113,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11151,7 +11155,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11193,7 +11197,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11235,7 +11239,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11277,7 +11281,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11319,7 +11323,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11361,7 +11365,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11403,7 +11407,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11441,7 +11445,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11483,7 +11487,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11521,7 +11525,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11563,7 +11567,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11605,7 +11609,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11647,7 +11651,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11689,7 +11693,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11727,7 +11731,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11765,7 +11769,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11803,7 +11807,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11845,7 +11849,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11887,7 +11891,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11925,7 +11929,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11963,7 +11967,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12005,7 +12009,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12043,7 +12047,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12085,7 +12089,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12123,7 +12127,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12161,7 +12165,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12199,7 +12203,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12237,7 +12241,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12275,7 +12279,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12313,7 +12317,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12355,7 +12359,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12393,7 +12397,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12435,7 +12439,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12477,7 +12481,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12515,7 +12519,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12553,7 +12557,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12591,7 +12595,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12633,7 +12637,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12671,7 +12675,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12713,7 +12717,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12755,7 +12759,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12793,7 +12797,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12835,7 +12839,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12877,7 +12881,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12915,7 +12919,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12953,7 +12957,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12995,7 +12999,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -13037,7 +13041,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -13079,7 +13083,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13117,7 +13121,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13155,7 +13159,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13193,7 +13197,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13231,7 +13235,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13269,7 +13273,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13311,7 +13315,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13349,7 +13353,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13391,7 +13395,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13429,7 +13433,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13467,7 +13471,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13505,7 +13509,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13543,7 +13547,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13737,7 +13741,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -13779,12 +13783,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -13821,7 +13825,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -13863,7 +13867,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13905,7 +13909,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -13947,7 +13951,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13989,7 +13993,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -14031,7 +14035,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -14073,7 +14077,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -14115,7 +14119,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14157,7 +14161,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14199,7 +14203,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -14237,7 +14241,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14279,7 +14283,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14321,7 +14325,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -14363,7 +14367,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14405,7 +14409,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14447,7 +14451,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14489,7 +14493,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14531,7 +14535,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14573,7 +14577,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14615,7 +14619,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14657,7 +14661,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -14699,7 +14703,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14746,7 +14750,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -14788,7 +14792,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -14825,7 +14829,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -14867,7 +14871,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14909,7 +14913,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14951,7 +14955,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14993,7 +14997,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -15035,7 +15039,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -15077,7 +15081,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -15119,7 +15123,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15161,7 +15165,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15203,7 +15207,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15245,7 +15249,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15287,7 +15291,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15329,7 +15333,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15371,7 +15375,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15413,7 +15417,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15455,7 +15459,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15497,7 +15501,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -15539,7 +15543,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15581,7 +15585,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15623,7 +15627,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15665,7 +15669,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15707,7 +15711,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15749,12 +15753,12 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T12:49:57+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -15791,7 +15795,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15833,7 +15837,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15875,7 +15879,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15917,7 +15921,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15959,7 +15963,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -16001,7 +16005,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -16043,7 +16047,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -16085,7 +16089,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -16127,7 +16131,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16169,7 +16173,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -16211,7 +16215,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -16253,7 +16257,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16291,7 +16295,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16329,7 +16333,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16371,7 +16375,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16409,7 +16413,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16447,7 +16451,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16485,7 +16489,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16523,7 +16527,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16561,7 +16565,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16599,7 +16603,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16637,7 +16641,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16675,7 +16679,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16717,7 +16721,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16755,7 +16759,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -16793,7 +16797,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16831,7 +16835,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16869,7 +16873,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -16907,7 +16911,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:38+00:00</t>
+          <t>2026-09-25T12:50:11+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7878,12 +7878,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>9d50868a4f375af4073f1702fa95c5beab51ce17ecb88c6afbda4f6caaea8e5d</t>
+          <t>25d9060444d819c24c18ac01280aa99235cc539bc0d5501e340e0abdaa16ad27</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11197,7 +11197,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11525,7 +11525,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11567,7 +11567,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12595,7 +12595,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13121,7 +13121,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13197,7 +13197,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -13315,7 +13315,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -13547,7 +13547,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -14077,7 +14077,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -14203,7 +14203,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -14283,7 +14283,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -14493,7 +14493,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -14661,7 +14661,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -14750,7 +14750,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -14955,7 +14955,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -15207,7 +15207,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -15417,7 +15417,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -15501,7 +15501,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15837,7 +15837,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15963,7 +15963,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -16005,7 +16005,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -16295,7 +16295,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16375,7 +16375,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16451,7 +16451,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16527,7 +16527,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16565,7 +16565,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16603,7 +16603,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16679,7 +16679,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -16759,7 +16759,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -16797,7 +16797,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -16873,7 +16873,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -16911,7 +16911,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T12:50:11+00:00</t>
+          <t>2026-09-26T12:17:03+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Programs'!$A$1:$N$213</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$H$192</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Applied'!$A$1:$C$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Discovered'!$A$1:$H$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Discovered'!$A$1:$H$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
@@ -3804,7 +3804,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="N63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>a6d079ec7f9100088d25f39f43f86faf2667be43dd7f05f21fd7b900739a3760</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4102,7 +4106,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
@@ -4166,7 +4170,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
@@ -4230,7 +4234,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
@@ -4294,7 +4298,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
@@ -4358,7 +4362,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
@@ -4422,7 +4426,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
@@ -4590,7 +4594,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -5114,7 +5118,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
@@ -6498,10 +6502,14 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
-        </is>
-      </c>
-      <c r="K114" s="2" t="inlineStr"/>
+          <t>2026-09-28T15:25:45+00:00</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:25:45+00:00</t>
+        </is>
+      </c>
       <c r="L114" s="2" t="inlineStr"/>
       <c r="M114" s="2" t="inlineStr">
         <is>
@@ -6510,7 +6518,7 @@
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>c73cabb199b26e430f8dee053f572be42d8f6665df50643fb64e8ca6bf064772</t>
+          <t>62d32530d603b027f9449498244ff9de23502a87dc8d606d86478637471e5684</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6674,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr"/>
@@ -6730,7 +6738,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr"/>
@@ -7970,7 +7978,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -8034,12 +8042,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -8050,7 +8058,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>52802246bbef831b31b7e9d9be931e4e3fa5f7ffe9138e5e40daa184a7e65486</t>
+          <t>4f009f794507f781652d228af6a53f321291f2e3ce5f378536471ea3d600b2e5</t>
         </is>
       </c>
     </row>
@@ -8102,12 +8110,12 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T12:39:39+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr"/>
@@ -8118,7 +8126,7 @@
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>5211633896d1f19a2c25272d82debf587fe742b7b9611d3239d20246ed9b2213</t>
+          <t>25f3e22ab690e5dc0b3394bca1518de4dc0a25382e535bd2abdd744ff813ee90</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8178,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8234,7 +8242,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8570,7 +8578,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8638,7 +8646,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -8710,7 +8718,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8838,7 +8846,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8906,7 +8914,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8978,7 +8986,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10670,7 +10678,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10850,7 +10858,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
@@ -10918,7 +10926,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
@@ -10986,10 +10994,14 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
-        </is>
-      </c>
-      <c r="K193" s="2" t="inlineStr"/>
+          <t>2026-09-28T15:25:45+00:00</t>
+        </is>
+      </c>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:25:45+00:00</t>
+        </is>
+      </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -11002,7 +11014,7 @@
       </c>
       <c r="N193" s="2" t="inlineStr">
         <is>
-          <t>508589d77b4091cb91503fd2e8f89c487efe1700ee453cdab3fd578c2506a127</t>
+          <t>8d5be6c2e2d53d3c482b997109b4d440a4cb9f42b421c59e9660932a23a483b9</t>
         </is>
       </c>
     </row>
@@ -11054,7 +11066,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
@@ -11122,10 +11134,14 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
-        </is>
-      </c>
-      <c r="K195" s="2" t="inlineStr"/>
+          <t>2026-09-28T15:25:45+00:00</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:25:45+00:00</t>
+        </is>
+      </c>
       <c r="L195" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -11138,7 +11154,7 @@
       </c>
       <c r="N195" s="2" t="inlineStr">
         <is>
-          <t>24b7e680af6978f17b5eebaf4a17959124498c2ab61679421666e71ecc2c4b3f</t>
+          <t>4a082bd8ae515f500fdf636e7d9d1b17188a776a9936aee26a03d7a531030ddc</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11206,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
@@ -11258,7 +11274,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
@@ -11326,7 +11342,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
@@ -11394,7 +11410,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
@@ -11462,7 +11478,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
@@ -11530,7 +11546,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
@@ -11598,7 +11614,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr"/>
@@ -11666,7 +11682,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr"/>
@@ -11734,7 +11750,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr"/>
@@ -11802,7 +11818,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr"/>
@@ -11870,7 +11886,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr"/>
@@ -11934,10 +11950,14 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
-        </is>
-      </c>
-      <c r="K207" s="2" t="inlineStr"/>
+          <t>2026-09-28T15:25:45+00:00</t>
+        </is>
+      </c>
+      <c r="K207" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:25:45+00:00</t>
+        </is>
+      </c>
       <c r="L207" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -11950,7 +11970,7 @@
       </c>
       <c r="N207" s="2" t="inlineStr">
         <is>
-          <t>91d5fb062194e170ca2e9688a9586bacd8e1202b3cbcbe53555801441f8118e9</t>
+          <t>8f5ce11e6e144e5fcab44fb1da76c9a2231fa37f5ec7c670d3e7d7ee137c39fc</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12022,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K208" s="2" t="inlineStr"/>
@@ -12070,10 +12090,14 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
-        </is>
-      </c>
-      <c r="K209" s="2" t="inlineStr"/>
+          <t>2026-09-28T15:25:45+00:00</t>
+        </is>
+      </c>
+      <c r="K209" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:25:45+00:00</t>
+        </is>
+      </c>
       <c r="L209" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -12086,7 +12110,7 @@
       </c>
       <c r="N209" s="2" t="inlineStr">
         <is>
-          <t>9dc659d5a1fe3b03e2ee07ac61ff49350faf5a66cf12f7e0d9c141c6ecc1c17d</t>
+          <t>2b48cfa758cf26f1d5088203c6833faf49ccc262a35081cbeac530c44ab1f8c3</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12162,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="K210" s="2" t="inlineStr"/>
@@ -12626,7 +12650,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -12664,7 +12688,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -12702,7 +12726,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12740,7 +12764,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12778,7 +12802,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12816,7 +12840,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12858,7 +12882,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12900,7 +12924,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12942,7 +12966,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12984,7 +13008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13026,7 +13050,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13068,7 +13092,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13110,7 +13134,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13152,7 +13176,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13194,7 +13218,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13232,7 +13256,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13274,7 +13298,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13312,7 +13336,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13354,7 +13378,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13396,7 +13420,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13438,7 +13462,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13480,7 +13504,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13522,7 +13546,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13560,7 +13584,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13598,7 +13622,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13636,7 +13660,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13678,7 +13702,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13720,7 +13744,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13758,7 +13782,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13796,7 +13820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13838,7 +13862,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13876,7 +13900,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -13918,7 +13942,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -13956,7 +13980,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -13994,7 +14018,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14032,7 +14056,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14070,7 +14094,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14108,7 +14132,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14146,7 +14170,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14188,7 +14212,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14226,7 +14250,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14268,7 +14292,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -14310,7 +14334,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -14352,7 +14376,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -14390,7 +14414,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -14428,7 +14452,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -14466,7 +14490,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -14508,7 +14532,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -14546,7 +14570,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -14588,7 +14612,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -14630,7 +14654,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -14668,7 +14692,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -14710,7 +14734,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -14752,7 +14776,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -14790,7 +14814,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -14832,7 +14856,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -14870,7 +14894,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -14912,7 +14936,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -14954,7 +14978,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -14996,7 +15020,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -15034,7 +15058,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -15072,7 +15096,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -15110,7 +15134,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -15148,7 +15172,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -15186,7 +15210,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -15228,7 +15252,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -15266,7 +15290,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -15308,7 +15332,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -15346,7 +15370,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -15388,7 +15412,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -15426,7 +15450,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -15464,7 +15488,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -15502,7 +15526,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -15696,7 +15720,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -15743,7 +15767,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -15780,7 +15804,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -15822,7 +15846,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -15864,7 +15888,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -15906,7 +15930,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -15948,7 +15972,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -15990,7 +16014,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -16032,7 +16056,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -16074,7 +16098,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -16116,7 +16140,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -16158,7 +16182,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -16200,7 +16224,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -16242,7 +16266,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -16284,7 +16308,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -16326,7 +16350,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -16368,7 +16392,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -16410,7 +16434,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -16452,7 +16476,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -16494,7 +16518,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -16536,7 +16560,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -16578,7 +16602,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -16616,7 +16640,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -16658,7 +16682,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -16700,7 +16724,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -16742,7 +16766,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -16784,7 +16808,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -16826,7 +16850,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -16868,7 +16892,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -16910,7 +16934,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -16952,7 +16976,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -16994,7 +17018,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -17036,7 +17060,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -17078,7 +17102,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -17120,7 +17144,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -17162,7 +17186,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -17209,7 +17233,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -17251,7 +17275,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -17288,7 +17312,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -17330,7 +17354,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -17372,7 +17396,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -17414,7 +17438,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -17456,7 +17480,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -17498,7 +17522,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -17540,7 +17564,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -17582,7 +17606,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -17624,7 +17648,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -17666,7 +17690,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -17708,7 +17732,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -17750,7 +17774,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -17792,7 +17816,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -17834,7 +17858,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -17876,7 +17900,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -17918,7 +17942,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -17960,7 +17984,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -18002,7 +18026,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -18044,7 +18068,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -18086,7 +18110,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -18128,7 +18152,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -18170,7 +18194,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -18212,7 +18236,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -18254,7 +18278,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -18296,7 +18320,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -18338,7 +18362,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -18380,7 +18404,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -18422,7 +18446,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -18464,7 +18488,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -18506,7 +18530,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -18548,7 +18572,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -18590,7 +18614,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -18632,7 +18656,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -18674,7 +18698,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -18717,7 +18741,7 @@
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -18754,7 +18778,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -18796,7 +18820,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -18838,7 +18862,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -18880,7 +18904,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -18922,7 +18946,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -18964,7 +18988,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -19006,7 +19030,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -19048,7 +19072,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -19090,7 +19114,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -19132,7 +19156,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -19174,7 +19198,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -19216,7 +19240,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -19258,7 +19282,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -19300,7 +19324,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -19342,7 +19366,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -19384,7 +19408,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -19424,10 +19448,14 @@
           <t>https://www.worldquant.com/brain/iqc/</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:25:45+00:00</t>
+        </is>
+      </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -19464,7 +19492,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -19506,7 +19534,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -19548,7 +19576,7 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -19590,7 +19618,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -19628,7 +19656,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -19670,7 +19698,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -19708,7 +19736,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -19750,7 +19778,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -19792,7 +19820,7 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -19830,7 +19858,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -19868,7 +19896,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -19906,7 +19934,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -19944,7 +19972,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -19982,7 +20010,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -20020,7 +20048,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -20058,7 +20086,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -20096,7 +20124,7 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -20138,7 +20166,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -20180,7 +20208,7 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -20218,7 +20246,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -20256,7 +20284,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -20294,7 +20322,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -20332,7 +20360,7 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -20370,7 +20398,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T13:03:11+00:00</t>
+          <t>2026-09-28T15:25:45+00:00</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -20554,7 +20582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20701,7 +20729,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>bti36021</t>
+          <t>astranis</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -20711,27 +20739,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:bti36021</t>
+          <t>greenhouse:astranis</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/bti36021/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/astranis/jobs?content=true</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 12 postings, 1 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 164 postings, 86 US student rows</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20743,7 +20771,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>compeerfinancial</t>
+          <t>bti36021</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -20753,17 +20781,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:compeerfinancial</t>
+          <t>greenhouse:bti36021</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/compeerfinancial/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/bti36021/jobs?content=true</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 67 postings, 0 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 12 postings, 1 US student rows</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -20785,7 +20813,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>cssmerge</t>
+          <t>compeerfinancial</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -20795,17 +20823,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:cssmerge</t>
+          <t>greenhouse:compeerfinancial</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/cssmerge/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/compeerfinancial/jobs?content=true</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 245 postings, 2 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 67 postings, 0 US student rows</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -20827,7 +20855,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>devtechnology</t>
+          <t>cssmerge</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -20837,17 +20865,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:devtechnology</t>
+          <t>greenhouse:cssmerge</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/devtechnology/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/cssmerge/jobs?content=true</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 26 postings, 5 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 245 postings, 2 US student rows</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -20869,7 +20897,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>doordashcanada</t>
+          <t>devtechnology</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -20879,27 +20907,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:doordashcanada</t>
+          <t>greenhouse:devtechnology</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/doordashcanada/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/devtechnology/jobs?content=true</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 34 postings, 0 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 26 postings, 5 US student rows</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -20911,7 +20939,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>doordashusa</t>
+          <t>doordashcanada</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -20921,17 +20949,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:doordashusa</t>
+          <t>greenhouse:doordashcanada</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/doordashusa/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/doordashcanada/jobs?content=true</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 462 postings, 5 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 34 postings, 0 US student rows</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -20953,7 +20981,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>duolingounirecruitment</t>
+          <t>doordashusa</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -20963,17 +20991,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:duolingounirecruitment</t>
+          <t>greenhouse:doordashusa</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/duolingounirecruitment/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/doordashusa/jobs?content=true</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 3 postings, 3 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 462 postings, 5 US student rows</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -20995,7 +21023,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>eulerity</t>
+          <t>duolingounirecruitment</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -21005,27 +21033,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:eulerity</t>
+          <t>greenhouse:duolingounirecruitment</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/eulerity/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/duolingounirecruitment/jobs?content=true</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 17 postings, 6 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 3 postings, 3 US student rows</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -21037,7 +21065,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>figma</t>
+          <t>eulerity</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -21047,27 +21075,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:figma</t>
+          <t>greenhouse:eulerity</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/figma/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/eulerity/jobs?content=true</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 152 postings, 6 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 17 postings, 6 US student rows</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -21079,7 +21107,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>gallup</t>
+          <t>figma</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -21089,27 +21117,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:gallup</t>
+          <t>greenhouse:figma</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/gallup/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/figma/jobs?content=true</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 54 postings, 5 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 152 postings, 6 US student rows</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -21121,7 +21149,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>generalmatter</t>
+          <t>gallup</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -21131,17 +21159,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:generalmatter</t>
+          <t>greenhouse:gallup</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/generalmatter/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/gallup/jobs?content=true</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 132 postings, 24 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 54 postings, 5 US student rows</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -21163,7 +21191,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>hpiq</t>
+          <t>generalmatter</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -21173,17 +21201,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:hpiq</t>
+          <t>greenhouse:generalmatter</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/hpiq/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/generalmatter/jobs?content=true</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 32 postings, 7 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 132 postings, 24 US student rows</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -21205,7 +21233,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>hudl</t>
+          <t>hpiq</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -21215,17 +21243,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:hudl</t>
+          <t>greenhouse:hpiq</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/hudl/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/hpiq/jobs?content=true</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 31 postings, 3 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 32 postings, 7 US student rows</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -21247,7 +21275,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>idmeuniversityrecruiting</t>
+          <t>hudl</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -21257,17 +21285,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:idmeuniversityrecruiting</t>
+          <t>greenhouse:hudl</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/idmeuniversityrecruiting/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/hudl/jobs?content=true</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 7 postings, 7 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 31 postings, 3 US student rows</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -21289,7 +21317,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>k2spacecorporation</t>
+          <t>idmeuniversityrecruiting</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -21299,17 +21327,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:k2spacecorporation</t>
+          <t>greenhouse:idmeuniversityrecruiting</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/k2spacecorporation/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/idmeuniversityrecruiting/jobs?content=true</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 219 postings, 9 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 7 postings, 7 US student rows</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -21331,7 +21359,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>klaviyocampus</t>
+          <t>k2spacecorporation</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -21341,17 +21369,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:klaviyocampus</t>
+          <t>greenhouse:k2spacecorporation</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/klaviyocampus/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/k2spacecorporation/jobs?content=true</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 3 postings, 2 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 219 postings, 9 US student rows</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -21373,7 +21401,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>nisc</t>
+          <t>klaviyocampus</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -21383,17 +21411,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:nisc</t>
+          <t>greenhouse:klaviyocampus</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/nisc/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/klaviyocampus/jobs?content=true</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 39 postings, 8 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 3 postings, 2 US student rows</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -21415,7 +21443,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>pacificfusion</t>
+          <t>nisc</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -21425,17 +21453,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:pacificfusion</t>
+          <t>greenhouse:nisc</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/pacificfusion/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/nisc/jobs?content=true</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 37 postings, 5 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 39 postings, 8 US student rows</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -21457,7 +21485,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>testnisc</t>
+          <t>pacificfusion</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -21467,17 +21495,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:testnisc</t>
+          <t>greenhouse:pacificfusion</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/testnisc/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/pacificfusion/jobs?content=true</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 37 postings, 9 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 37 postings, 5 US student rows</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -21499,27 +21527,27 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Chieler/Summer-2027-SWE-Internships</t>
+          <t>testnisc</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>repo</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>repo:chieler/summer-2027-swe-internships</t>
+          <t>greenhouse:testnisc</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Chieler/Summer-2027-SWE-Internships</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/testnisc/jobs?content=true</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26 stars, pushed 2026-09-13; matched "Summer 2027 Internships"</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 37 postings, 9 US student rows</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -21541,7 +21569,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>sndsh404/summer-2027-internships</t>
+          <t>Chieler/Summer-2027-SWE-Internships</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -21551,17 +21579,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>repo:sndsh404/summer-2027-internships</t>
+          <t>repo:chieler/summer-2027-swe-internships</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sndsh404/summer-2027-internships</t>
+          <t>https://github.com/Chieler/Summer-2027-SWE-Internships</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>934 stars, pushed 2026-08-03; matched "Summer 2027 Internships"</t>
+          <t>26 stars, pushed 2026-09-13; matched "Summer 2027 Internships"</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -21578,32 +21606,32 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>discarded-low-priority</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>chicagotradingcampus</t>
+          <t>sndsh404/summer-2027-internships</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>repo</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:chicagotradingcampus</t>
+          <t>repo:sndsh404/summer-2027-internships</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/chicagotradingcampus/jobs?content=true</t>
+          <t>https://github.com/sndsh404/summer-2027-internships</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 8 postings, 4 US student rows</t>
+          <t>934 stars, pushed 2026-08-03; matched "Summer 2027 Internships"</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -21625,7 +21653,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ctccampusboard</t>
+          <t>chicagotradingcampus</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -21635,17 +21663,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:ctccampusboard</t>
+          <t>greenhouse:chicagotradingcampus</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/ctccampusboard/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/chicagotradingcampus/jobs?content=true</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 6 postings, 4 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 8 postings, 4 US student rows</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -21667,7 +21695,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>gardacp</t>
+          <t>ctccampusboard</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -21677,17 +21705,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>greenhouse:gardacp</t>
+          <t>greenhouse:ctccampusboard</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>https://boards-api.greenhouse.io/v1/boards/gardacp/jobs?content=true</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/ctccampusboard/jobs?content=true</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 14 postings, 4 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 6 postings, 4 US student rows</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -21709,37 +21737,37 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>tgsmc</t>
+          <t>drwuniversityjobs</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>lever:tgsmc</t>
+          <t>greenhouse:drwuniversityjobs</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>https://api.lever.co/v0/postings/tgsmc?mode=json</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/drwuniversityjobs/jobs?content=true</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>found in the HTML of tgs-join-our-team, which is watched as page_text; not in sources.csv; API returns 0 postings, 0 US student rows</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 2 postings, 1 US student rows</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -21751,27 +21779,27 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>vanshb03/Summer2027-Internships</t>
+          <t>gardacp</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>repo</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>repo:vanshb03/summer2027-internships</t>
+          <t>greenhouse:gardacp</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/vanshb03/Summer2027-Internships</t>
+          <t>https://boards-api.greenhouse.io/v1/boards/gardacp/jobs?content=true</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9045 stars, pushed 2026-08-23; matched "Summer 2027 Internships"</t>
+          <t>linked from simplify-2027.tsv; not in sources.csv; API returns 14 postings, 4 US student rows</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -21788,84 +21816,84 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Allston Trading</t>
+          <t>tgsmc</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>allston-trading</t>
+          <t>lever:tgsmc</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>https://allstontrading.com</t>
+          <t>https://api.lever.co/v0/postings/tgsmc?mode=json</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>DNS resolves, ports 443 and 80 closed. Acquired by DV Trading Dec 2021; DV's board is already watched as dvtrading-greenhouse.</t>
+          <t>found in the HTML of tgs-join-our-team, which is watched as page_text; not in sources.csv; API returns 0 postings, 0 US student rows</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>AlphaGrep Securities</t>
+          <t>vanshb03/Summer2027-Internships</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>firm</t>
+          <t>repo</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>alphagrep</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>alphagrepsecurities (greenhouse)</t>
+          <t>repo:vanshb03/summer2027-internships</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/vanshb03/Summer2027-Internships</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16 jobs including a 2027 Campus Program, but every location is India/China/Singapore - zero US rows now or historically.</t>
+          <t>9045 stars, pushed 2026-08-23; matched "Summer 2027 Internships"</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -21877,7 +21905,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>AlphaSimplex</t>
+          <t>Allston Trading</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -21887,17 +21915,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>alphasimplex</t>
+          <t>allston-trading</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>https://www.alphasimplex.com/</t>
+          <t>https://allstontrading.com</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Acquired by Virtus (closed Apr 2023). The Workday board that answers is all-Virtus sales/advisory, not quant.</t>
+          <t>DNS resolves, ports 443 and 80 closed. Acquired by DV Trading Dec 2021; DV's board is already watched as dvtrading-greenhouse.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -21919,7 +21947,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Arb Trading Group</t>
+          <t>AlphaGrep Securities</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -21929,17 +21957,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>arb-trading-group</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>https://arb-tg.com/</t>
+          <t>alphagrep</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>alphagrepsecurities (greenhouse)</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4,775-char Webflow site, every careers path 404. arbtrading.com is a catch-all serving the same page for all 22 paths - a trap that would look healthy.</t>
+          <t>16 jobs including a 2027 Campus Program, but every location is India/China/Singapore - zero US rows now or historically.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -21961,7 +21989,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Citadel (hedge fund)</t>
+          <t>AlphaSimplex</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -21971,17 +21999,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>citadel</t>
+          <t>alphasimplex</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>https://www.citadel.com/careers/students/</t>
+          <t>https://www.alphasimplex.com/</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>403 Cloudflare intermittently (1 of 3 fetches over 12 samples); homepage always 403. An intermittent block is worse than a hard one - it would fire spurious source failures. method=manual is correct.</t>
+          <t>Acquired by Virtus (closed Apr 2023). The Workday board that answers is all-Virtus sales/advisory, not quant.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -22003,7 +22031,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Consolidated Trading</t>
+          <t>Arb Trading Group</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -22013,17 +22041,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>consolidated-trading</t>
+          <t>arb-trading-group</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>http://consolidatedtrading.com/</t>
+          <t>https://arb-tg.com/</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1,086 chars with no careers content, all careers paths 404, HTTPS handshake fails.</t>
+          <t>4,775-char Webflow site, every careers path 404. arbtrading.com is a catch-all serving the same page for all 22 paths - a trap that would look healthy.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -22045,7 +22073,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Cutler Group</t>
+          <t>Citadel (hedge fund)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -22055,17 +22083,17 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>cutler-group</t>
+          <t>citadel</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>https://cutlerllc.com/</t>
+          <t>https://www.citadel.com/careers/students/</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>224 chars, under the floor; WP REST shows two pages total. NOTE cutlergroup.com is a Canadian bathroom-vanity manufacturer - wrong company.</t>
+          <t>403 Cloudflare intermittently (1 of 3 fetches over 12 samples); homepage always 403. An intermittent block is worse than a hard one - it would fire spurious source failures. method=manual is correct.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -22087,7 +22115,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Dark Forest Technologies</t>
+          <t>Consolidated Trading</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -22097,17 +22125,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>dark-forest-tech</t>
+          <t>consolidated-trading</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>https://darkforesttech.com/</t>
+          <t>http://consolidatedtrading.com/</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>231 chars, under the floor. A single GitHub Pages placeholder; recruiting@darkforesttech.com only.</t>
+          <t>1,086 chars with no careers content, all careers paths 404, HTTPS handshake fails.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -22129,7 +22157,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Eisler Capital</t>
+          <t>Cutler Group</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -22139,17 +22167,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>eisler-capital</t>
+          <t>cutler-group</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>https://eislercapital.com</t>
+          <t>https://cutlerllc.com/</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>DEFUNCT: no A record; www CNAMEs to a torn-down CloudFront distribution. Flagship wound down 31 Dec 2025.</t>
+          <t>224 chars, under the floor; WP REST shows two pages total. NOTE cutlergroup.com is a Canadian bathroom-vanity manufacturer - wrong company.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -22171,7 +22199,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Emergent Trading</t>
+          <t>Dark Forest Technologies</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -22181,17 +22209,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>emergent-trading</t>
+          <t>dark-forest-tech</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>https://www.emergenttrading.com/join</t>
+          <t>https://darkforesttech.com/</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Ember.js shell: /join is the real careers route and returns 0 chars. App and vendor bundles grepped, no ATS and no fetch target.</t>
+          <t>231 chars, under the floor. A single GitHub Pages placeholder; recruiting@darkforesttech.com only.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -22213,7 +22241,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Freestone Grove Partners</t>
+          <t>Eisler Capital</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -22223,17 +22251,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>freestone-grove</t>
+          <t>eisler-capital</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.gem.com/freestone-grove-partners</t>
+          <t>https://eislercapital.com</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Gem JS shell, 32 chars. Board verified real but empty: the GraphQL POST returns jobPostings: []. Worth re-probing later.</t>
+          <t>DEFUNCT: no A record; www CNAMEs to a torn-down CloudFront distribution. Flagship wound down 31 Dec 2025.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -22255,7 +22283,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs Emerging Leaders Series</t>
+          <t>Emergent Trading</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -22265,17 +22293,17 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>goldman-emerging-leaders</t>
+          <t>emergent-trading</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships/americas/emerging-leaders-series</t>
+          <t>https://www.emergenttrading.com/join</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>403 Akamai. higher.gs.com/roles returns 200 but 29 chars (JS shell). Programme is live for 2026 but only reachable at edition-specific Avature URLs that expire.</t>
+          <t>Ember.js shell: /join is the real careers route and returns 0 chars. App and vendor bundles grepped, no ATS and no fetch target.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -22297,7 +22325,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Kinetic Trading Partners</t>
+          <t>Freestone Grove Partners</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -22307,13 +22335,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>kinetic-trading-partners</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
+          <t>freestone-grove</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.gem.com/freestone-grove-partners</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Zero LinkedIn results, absent from every quant directory checked. The name collides with Kinetic Partners Management LP, Kinetix Trading Solutions and retail prop-firm affiliate sites.</t>
+          <t>Gem JS shell, 32 chars. Board verified real but empty: the GraphQL POST returns jobPostings: []. Worth re-probing later.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -22335,7 +22367,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Laurion Capital</t>
+          <t>Goldman Sachs Emerging Leaders Series</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -22345,17 +22377,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>laurion-capital</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>laurioncapitalmanagement (greenhouse)</t>
+          <t>goldman-emerging-leaders</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships/americas/emerging-leaders-series</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Slug resolves but the board has 0 postings. A permanently empty board can only ever look healthy-and-quiet, so it is not added - same call as optiver/marshallwace in Phase 2.</t>
+          <t>403 Akamai. higher.gs.com/roles returns 200 but 29 chars (JS shell). Programme is live for 2026 but only reachable at edition-specific Avature URLs that expire.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -22377,7 +22409,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Nico Trading</t>
+          <t>Kinetic Trading Partners</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -22387,17 +22419,13 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>nico-trading</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>https://nicotrading.com</t>
-        </is>
-      </c>
+          <t>kinetic-trading-partners</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>114-byte GoDaddy parking redirect, 0 chars. Firm operating but web-dark.</t>
+          <t>Zero LinkedIn results, absent from every quant directory checked. The name collides with Kinetic Partners Management LP, Kinetix Trading Solutions and retail prop-firm affiliate sites.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -22419,7 +22447,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Numerai</t>
+          <t>Laurion Capital</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -22429,17 +22457,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>numerai</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>https://numer.ai/careers</t>
+          <t>laurion-capital</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>laurioncapitalmanagement (greenhouse)</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>404. No first-party careers page; Wellfound 403s us and Built In serves nav boilerplate with zero titles.</t>
+          <t>Slug resolves but the board has 0 postings. A permanently empty board can only ever look healthy-and-quiet, so it is not added - same call as optiver/marshallwace in Phase 2.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -22461,7 +22489,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Quantitative Investment Management</t>
+          <t>Nico Trading</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -22471,17 +22499,17 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>qim</t>
+          <t>nico-trading</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>https://quantitative.com/</t>
+          <t>https://nicotrading.com</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Every path 404 while robots.txt returns 200 - the site is genuinely unpublished, not blocking us. Firm is still an active RIA.</t>
+          <t>114-byte GoDaddy parking redirect, 0 chars. Firm operating but web-dark.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -22503,7 +22531,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Quantbox Research</t>
+          <t>Numerai</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -22513,17 +22541,17 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>quantbox-research</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>quantboxresearchpte (greenhouse)</t>
+          <t>numerai</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>https://numer.ai/careers</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>7 jobs, junior roles are Amsterdam/Singapore only.</t>
+          <t>404. No first-party careers page; Wellfound 403s us and Built In serves nav boilerplate with zero titles.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -22545,7 +22573,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Quantlab Financial</t>
+          <t>Quantitative Investment Management</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -22555,17 +22583,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>quantlab</t>
+          <t>qim</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>https://www.quantlab.com/careers</t>
+          <t>https://quantitative.com/</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>403 S3 AccessDenied, 26 chars. Its Jobvite board returns 200 with 237 chars (empty, under the 500 floor) and redirects back into the block.</t>
+          <t>Every path 404 while robots.txt returns 200 - the site is genuinely unpublished, not blocking us. Firm is still an active RIA.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -22587,7 +22615,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>QVR Advisors</t>
+          <t>Quantbox Research</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -22597,17 +22625,17 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>qvr-advisors</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>https://qvradvisors.com</t>
+          <t>quantbox-research</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>quantboxresearchpte (greenhouse)</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>DEFUNCT: homepage rewritten to past tense ('was formerly a boutique SEC-registered investment advisor'). Closing after ~30% losses Jan-Apr 2026.</t>
+          <t>7 jobs, junior roles are Amsterdam/Singapore only.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -22629,7 +22657,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Rosetta Analytics</t>
+          <t>Quantlab Financial</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -22639,17 +22667,17 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>rosetta-analytics</t>
+          <t>quantlab</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>https://rosetta-analytics.com/</t>
+          <t>https://www.quantlab.com/careers</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>DEFUNCT: 114 bytes, 0 chars, JS redirect to a parking lander. Closed March 2025.</t>
+          <t>403 S3 AccessDenied, 26 chars. Its Jobvite board returns 200 with 237 chars (empty, under the 500 floor) and redirects back into the block.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -22671,7 +22699,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Sensato Investors</t>
+          <t>QVR Advisors</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -22681,17 +22709,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>sensato-investors</t>
+          <t>qvr-advisors</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>https://sensatoinvestors.com</t>
+          <t>https://qvradvisors.com</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>HTTPS TLS internal error; over http, 27KB of HTML yields 44 chars. No careers link anywhere.</t>
+          <t>DEFUNCT: homepage rewritten to past tense ('was formerly a boutique SEC-registered investment advisor'). Closing after ~30% losses Jan-Apr 2026.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -22713,7 +22741,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Spot Trading</t>
+          <t>Rosetta Analytics</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -22723,17 +22751,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>spot-trading</t>
+          <t>rosetta-analytics</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>https://spottradingllc.com</t>
+          <t>https://rosetta-analytics.com/</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>DEFUNCT: 'Coming Soon' placeholder, 40 chars. Firm closed 28 Feb 2018.</t>
+          <t>DEFUNCT: 114 bytes, 0 chars, JS redirect to a parking lander. Closed March 2025.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -22755,7 +22783,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Summerside Capital</t>
+          <t>Sensato Investors</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -22765,13 +22793,17 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>summerside-capital</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr"/>
+          <t>sensato-investors</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>https://sensatoinvestors.com</t>
+        </is>
+      </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>No A record on five domain variants. No trading firm of this name appears to exist.</t>
+          <t>HTTPS TLS internal error; over http, 27KB of HTML yields 44 chars. No careers link anywhere.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -22793,7 +22825,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Tyler Capital</t>
+          <t>Spot Trading</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -22803,17 +22835,17 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>tyler-capital</t>
+          <t>spot-trading</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>https://www.tylercapital.co.uk/</t>
+          <t>https://spottradingllc.com</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Watchable (2,093 chars) but states explicitly: 'we don't run an internship or graduate recruitment program'. UK-only. Not worth a row.</t>
+          <t>DEFUNCT: 'Coming Soon' placeholder, 40 chars. Firm closed 28 Feb 2018.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -22835,7 +22867,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>WH Trading</t>
+          <t>Summerside Capital</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -22845,17 +22877,13 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>wh-trading</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>https://whtrading.com/life-at-wh-trading/</t>
-        </is>
-      </c>
+          <t>summerside-capital</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Page is 2,320 chars but lists no roles; /careers and /jobs 404. Hiring via opportunities@whtrading.com only.</t>
+          <t>No A record on five domain variants. No trading firm of this name appears to exist.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -22877,42 +22905,126 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
+          <t>Tyler Capital</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>tyler-capital</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tylercapital.co.uk/</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Watchable (2,093 chars) but states explicitly: 'we don't run an internship or graduate recruitment program'. UK-only. Not worth a row.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>WH Trading</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>firm</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>wh-trading</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>https://whtrading.com/life-at-wh-trading/</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Page is 2,320 chars but lists no roles; /careers and /jobs 404. Hiring via opportunities@whtrading.com only.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>XR Trading</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>firm</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>xr-trading</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>https://www.xrtrading.com/</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Paylocity React shell: board returns 670 chars, all of it 'unsupported browser' boilerplate, zero titles. Bundle grepped - no JSON endpoint exists.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H56"/>
+  <autoFilter ref="A1:H58"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -22943,8 +23055,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId34"/>
@@ -22953,17 +23065,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
@@ -6502,7 +6502,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr"/>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -8042,12 +8042,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>4f009f794507f781652d228af6a53f321291f2e3ce5f378536471ea3d600b2e5</t>
+          <t>fae966e585e0cfc03b511c9b0ddbaf66b38bf2019562119a82de3bfac8f9696f</t>
         </is>
       </c>
     </row>
@@ -8110,12 +8110,12 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr"/>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>25f3e22ab690e5dc0b3394bca1518de4dc0a25382e535bd2abdd744ff813ee90</t>
+          <t>035e6db5adfcc3203bbde0cad2342afeaadf660bc36c79c535e32e070f27e849</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
@@ -10994,12 +10994,12 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="L193" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="N193" s="2" t="inlineStr">
         <is>
-          <t>8d5be6c2e2d53d3c482b997109b4d440a4cb9f42b421c59e9660932a23a483b9</t>
+          <t>b41f6ade7438c1edf733e205a9a0f4779780ddebc887fa6f67305765f3fe7e66</t>
         </is>
       </c>
     </row>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr">
@@ -11206,10 +11206,14 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
-        </is>
-      </c>
-      <c r="K196" s="2" t="inlineStr"/>
+          <t>2026-09-29T14:07:58+00:00</t>
+        </is>
+      </c>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29T14:07:58+00:00</t>
+        </is>
+      </c>
       <c r="L196" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -11222,7 +11226,7 @@
       </c>
       <c r="N196" s="2" t="inlineStr">
         <is>
-          <t>63485420a1d693d73c277ad75bc4354af21ef4b7c6986bae53385c03009f1e8a</t>
+          <t>de7b874fd5a83c4536690d1ad528cd9d62752306bbc232ae50be8766906fd725</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11278,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
@@ -11342,7 +11346,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
@@ -11410,7 +11414,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
@@ -11478,7 +11482,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
@@ -11546,7 +11550,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
@@ -11614,7 +11618,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr"/>
@@ -11682,7 +11686,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr"/>
@@ -11750,7 +11754,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr"/>
@@ -11818,7 +11822,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr"/>
@@ -11886,7 +11890,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr"/>
@@ -11950,12 +11954,12 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="L207" s="2" t="inlineStr">
@@ -11970,7 +11974,7 @@
       </c>
       <c r="N207" s="2" t="inlineStr">
         <is>
-          <t>8f5ce11e6e144e5fcab44fb1da76c9a2231fa37f5ec7c670d3e7d7ee137c39fc</t>
+          <t>8bbb4508176879484ace92088f23c8a074716a937a534c74d58986992a48a01d</t>
         </is>
       </c>
     </row>
@@ -12022,7 +12026,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K208" s="2" t="inlineStr"/>
@@ -12090,7 +12094,7 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K209" s="2" t="inlineStr">
@@ -12162,7 +12166,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="K210" s="2" t="inlineStr"/>
@@ -12650,7 +12654,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -12688,7 +12692,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -12726,7 +12730,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12764,7 +12768,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12802,7 +12806,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12840,7 +12844,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12882,7 +12886,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12924,7 +12928,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12966,7 +12970,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13008,7 +13012,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13050,7 +13054,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13092,7 +13096,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13134,7 +13138,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13176,7 +13180,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13218,7 +13222,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13256,7 +13260,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13298,7 +13302,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13336,7 +13340,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13378,7 +13382,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13420,7 +13424,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13462,7 +13466,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13504,7 +13508,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13546,7 +13550,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13584,7 +13588,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13622,7 +13626,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13660,7 +13664,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13702,7 +13706,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13744,7 +13748,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13782,7 +13786,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13820,7 +13824,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13862,7 +13866,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13900,7 +13904,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -13942,7 +13946,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -13980,7 +13984,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14018,7 +14022,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14056,7 +14060,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14094,7 +14098,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14132,7 +14136,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14170,7 +14174,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14212,7 +14216,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14250,7 +14254,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14292,7 +14296,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -14334,7 +14338,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -14376,7 +14380,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -14414,7 +14418,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -14452,7 +14456,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -14490,7 +14494,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -14532,7 +14536,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -14570,7 +14574,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -14612,7 +14616,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -14654,7 +14658,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -14692,7 +14696,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -14734,7 +14738,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -14776,7 +14780,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -14814,7 +14818,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -14856,7 +14860,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -14894,7 +14898,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -14936,7 +14940,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -14978,7 +14982,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -15020,7 +15024,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -15058,7 +15062,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -15096,7 +15100,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -15134,7 +15138,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -15172,7 +15176,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -15210,7 +15214,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -15252,7 +15256,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -15290,7 +15294,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -15332,7 +15336,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -15370,7 +15374,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -15412,7 +15416,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -15450,7 +15454,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -15488,7 +15492,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -15526,7 +15530,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -15720,7 +15724,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -15762,12 +15766,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:17:03+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -15804,7 +15808,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -15846,7 +15850,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -15888,7 +15892,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -15930,7 +15934,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -15972,7 +15976,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -16014,7 +16018,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -16056,7 +16060,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -16098,7 +16102,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -16140,7 +16144,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -16182,7 +16186,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -16224,7 +16228,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -16266,7 +16270,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -16308,7 +16312,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -16350,7 +16354,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -16392,7 +16396,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -16434,7 +16438,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -16476,7 +16480,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -16518,7 +16522,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -16560,7 +16564,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -16602,7 +16606,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -16640,7 +16644,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -16682,7 +16686,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -16724,7 +16728,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -16766,7 +16770,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -16808,7 +16812,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -16850,7 +16854,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -16892,7 +16896,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -16934,7 +16938,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -16976,7 +16980,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -17018,7 +17022,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -17060,7 +17064,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -17102,7 +17106,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -17144,7 +17148,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -17186,7 +17190,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -17233,7 +17237,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -17275,7 +17279,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -17312,7 +17316,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -17354,7 +17358,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -17396,7 +17400,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -17438,7 +17442,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -17480,7 +17484,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -17522,7 +17526,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -17564,7 +17568,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -17606,7 +17610,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -17648,7 +17652,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -17690,7 +17694,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -17732,7 +17736,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -17774,7 +17778,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -17816,7 +17820,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -17858,7 +17862,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -17900,7 +17904,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -17942,7 +17946,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -17984,7 +17988,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -18026,7 +18030,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -18068,7 +18072,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -18110,7 +18114,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -18152,7 +18156,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -18194,7 +18198,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -18236,7 +18240,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -18278,7 +18282,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -18320,7 +18324,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -18362,7 +18366,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -18404,7 +18408,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -18446,7 +18450,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -18488,7 +18492,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -18530,7 +18534,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -18572,7 +18576,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -18614,7 +18618,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -18656,7 +18660,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -18698,7 +18702,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -18741,7 +18745,7 @@
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -18778,7 +18782,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -18820,7 +18824,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -18862,7 +18866,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -18904,7 +18908,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -18946,7 +18950,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -18988,7 +18992,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -19030,7 +19034,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -19072,7 +19076,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -19114,7 +19118,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -19156,7 +19160,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -19198,7 +19202,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -19240,7 +19244,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -19282,7 +19286,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -19324,7 +19328,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -19366,7 +19370,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -19408,7 +19412,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -19455,7 +19459,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -19492,7 +19496,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -19534,7 +19538,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -19576,7 +19580,7 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -19618,7 +19622,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -19656,7 +19660,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -19698,7 +19702,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -19736,7 +19740,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -19778,7 +19782,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -19820,7 +19824,7 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -19858,7 +19862,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -19896,7 +19900,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -19934,7 +19938,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -19972,7 +19976,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -20010,7 +20014,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -20048,7 +20052,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -20086,7 +20090,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -20124,7 +20128,7 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -20166,7 +20170,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -20208,7 +20212,7 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -20246,7 +20250,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -20284,7 +20288,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -20322,7 +20326,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -20360,7 +20364,7 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -20398,7 +20402,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-29T14:07:58+00:00</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
@@ -6502,7 +6502,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr"/>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -8042,12 +8042,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>fae966e585e0cfc03b511c9b0ddbaf66b38bf2019562119a82de3bfac8f9696f</t>
+          <t>c4938f052d21ad86e6e914c6617f9c9eac4c172b49af8d73ba56e155189542e2</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
@@ -10994,12 +10994,12 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="L193" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="N193" s="2" t="inlineStr">
         <is>
-          <t>b41f6ade7438c1edf733e205a9a0f4779780ddebc887fa6f67305765f3fe7e66</t>
+          <t>c9179eee7c2097bc14698f27863e7d34f3348e1d94ec0795ff47e3d5ab436e77</t>
         </is>
       </c>
     </row>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
@@ -11134,12 +11134,12 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="L195" s="2" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="N195" s="2" t="inlineStr">
         <is>
-          <t>4a082bd8ae515f500fdf636e7d9d1b17188a776a9936aee26a03d7a531030ddc</t>
+          <t>f167aa848901d0363e8144b4e47d45f95149d16f975ec408ea04835e0c642ed9</t>
         </is>
       </c>
     </row>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr"/>
@@ -11686,7 +11686,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr"/>
@@ -11754,10 +11754,14 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
-        </is>
-      </c>
-      <c r="K204" s="2" t="inlineStr"/>
+          <t>2026-09-30T13:45:29+00:00</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30T13:45:29+00:00</t>
+        </is>
+      </c>
       <c r="L204" s="2" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -11770,7 +11774,7 @@
       </c>
       <c r="N204" s="2" t="inlineStr">
         <is>
-          <t>5cfd18060b4b9d51508a27ad7ae69e86d8234409eae29b9687f6ad71ac3ac4dc</t>
+          <t>d577854726860cefa8b7bc5191fbef689f636ecf12b7ec70b4be78748becacf0</t>
         </is>
       </c>
     </row>
@@ -11822,7 +11826,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr"/>
@@ -11890,7 +11894,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr"/>
@@ -11954,12 +11958,12 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="L207" s="2" t="inlineStr">
@@ -11974,7 +11978,7 @@
       </c>
       <c r="N207" s="2" t="inlineStr">
         <is>
-          <t>8bbb4508176879484ace92088f23c8a074716a937a534c74d58986992a48a01d</t>
+          <t>16fc244bf83875312381ece0dcc56b27d08a673a002c038732648cd73fc6a36d</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12030,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K208" s="2" t="inlineStr"/>
@@ -12094,12 +12098,12 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T15:25:45+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="L209" s="2" t="inlineStr">
@@ -12114,7 +12118,7 @@
       </c>
       <c r="N209" s="2" t="inlineStr">
         <is>
-          <t>2b48cfa758cf26f1d5088203c6833faf49ccc262a35081cbeac530c44ab1f8c3</t>
+          <t>9dc659d5a1fe3b03e2ee07ac61ff49350faf5a66cf12f7e0d9c141c6ecc1c17d</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12170,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="K210" s="2" t="inlineStr"/>
@@ -12654,7 +12658,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -12692,7 +12696,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -12730,7 +12734,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12768,7 +12772,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12806,7 +12810,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12844,7 +12848,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12886,7 +12890,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12928,7 +12932,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12970,7 +12974,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13012,7 +13016,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13054,7 +13058,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13096,7 +13100,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13138,7 +13142,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13180,7 +13184,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13222,7 +13226,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13260,7 +13264,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13302,7 +13306,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13340,7 +13344,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13382,7 +13386,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13424,7 +13428,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13466,7 +13470,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13508,7 +13512,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13550,7 +13554,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13588,7 +13592,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13626,7 +13630,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13664,7 +13668,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13706,7 +13710,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13748,7 +13752,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13786,7 +13790,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13824,7 +13828,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13866,7 +13870,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13904,7 +13908,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -13946,7 +13950,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -13984,7 +13988,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14022,7 +14026,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14060,7 +14064,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14098,7 +14102,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14136,7 +14140,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14174,7 +14178,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14216,7 +14220,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14254,7 +14258,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14296,7 +14300,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -14338,7 +14342,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -14380,7 +14384,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -14418,7 +14422,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -14456,7 +14460,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -14494,7 +14498,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -14536,7 +14540,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -14574,7 +14578,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -14616,7 +14620,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -14658,7 +14662,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -14696,7 +14700,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -14738,7 +14742,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -14780,7 +14784,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -14818,7 +14822,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -14860,7 +14864,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -14898,7 +14902,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -14940,7 +14944,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -14982,7 +14986,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -15024,7 +15028,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -15062,7 +15066,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -15100,7 +15104,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -15138,7 +15142,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -15176,7 +15180,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -15214,7 +15218,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -15256,7 +15260,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -15294,7 +15298,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -15336,7 +15340,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -15374,7 +15378,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -15416,7 +15420,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -15454,7 +15458,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -15492,7 +15496,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -15530,7 +15534,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -15724,7 +15728,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -15771,7 +15775,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -15808,7 +15812,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -15850,7 +15854,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -15892,7 +15896,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -15934,7 +15938,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -15976,7 +15980,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -16018,7 +16022,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -16060,7 +16064,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -16102,7 +16106,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -16144,7 +16148,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -16186,7 +16190,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -16228,7 +16232,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -16270,7 +16274,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -16312,7 +16316,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -16354,7 +16358,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -16396,7 +16400,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -16438,7 +16442,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -16480,7 +16484,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -16522,7 +16526,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -16564,7 +16568,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -16606,7 +16610,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -16644,7 +16648,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -16686,7 +16690,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -16728,7 +16732,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -16770,7 +16774,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -16812,7 +16816,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -16854,7 +16858,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -16896,7 +16900,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -16938,7 +16942,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -16980,7 +16984,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -17022,7 +17026,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -17064,7 +17068,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -17106,7 +17110,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -17148,7 +17152,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -17190,7 +17194,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -17316,7 +17320,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -17358,7 +17362,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -17400,7 +17404,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -17442,7 +17446,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -17484,7 +17488,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -17526,7 +17530,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -17568,7 +17572,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -17610,7 +17614,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -17652,7 +17656,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -17694,7 +17698,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -17736,7 +17740,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -17778,7 +17782,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -17820,7 +17824,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -17862,7 +17866,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -17904,7 +17908,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -17951,7 +17955,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -17988,7 +17992,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -18030,7 +18034,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -18072,7 +18076,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -18114,7 +18118,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -18156,7 +18160,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -18198,7 +18202,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -18240,7 +18244,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -18282,7 +18286,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -18324,7 +18328,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -18366,7 +18370,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -18408,7 +18412,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -18450,7 +18454,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -18492,7 +18496,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -18534,7 +18538,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -18576,7 +18580,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -18618,7 +18622,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -18660,7 +18664,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -18702,7 +18706,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -18745,7 +18749,7 @@
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -18782,7 +18786,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -18824,7 +18828,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -18866,7 +18870,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -18908,7 +18912,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -18950,7 +18954,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -18992,7 +18996,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -19034,7 +19038,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -19076,7 +19080,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -19118,7 +19122,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -19160,7 +19164,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -19202,7 +19206,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -19244,7 +19248,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -19286,7 +19290,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -19328,7 +19332,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -19370,7 +19374,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -19412,7 +19416,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -19459,7 +19463,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -19496,7 +19500,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -19538,7 +19542,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -19580,7 +19584,7 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -19622,7 +19626,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -19660,7 +19664,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -19702,7 +19706,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -19740,7 +19744,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -19782,7 +19786,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -19824,7 +19828,7 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -19862,7 +19866,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -19900,7 +19904,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -19938,7 +19942,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -19976,7 +19980,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -20014,7 +20018,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -20052,7 +20056,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -20090,7 +20094,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -20128,7 +20132,7 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -20170,7 +20174,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -20212,7 +20216,7 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -20250,7 +20254,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -20288,7 +20292,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -20326,7 +20330,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -20364,7 +20368,7 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -20402,7 +20406,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:07:58+00:00</t>
+          <t>2026-09-30T13:45:29+00:00</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -2475,7 +2475,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>THE one for you next year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>THE one for a first-year to target the following year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Open to RISING sophomores - you qualify spring 2027. Computational biochemistry entity, not the fund. | Checked 2026-09-26: now redirects to deshawresearch.com/joining.html, which mentions only summer internships. Kept: it may reopen.</t>
+          <t>Open to RISING sophomores - a first-year qualifies in spring 2027. Computational biochemistry entity, not the fund. | Checked 2026-09-26: now redirects to deshawresearch.com/joining.html, which mentions only summer internships. Kept: it may reopen.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Highest pay in the industry, but you are too early.</t>
+          <t>Highest pay in the industry, but a first-year is too early.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Geographic exclusion - you are US-based.</t>
+          <t>Geographic exclusion - excludes US-based students.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Largest intercollegiate competition, $20,000+. NOT the same as Pokerbots - this one IS open to you.</t>
+          <t>Largest intercollegiate competition, $20,000+. NOT the same as Pokerbots - this one IS open to first-years.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>40+ universities, RIT Market Simulator. Entry runs through Traders @ Stanford, not you directly.</t>
+          <t>40+ universities, RIT Market Simulator. Entry runs through Traders @ Stanford, not by individual application.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Highest-signal single line you can add to a quant resume in year one. A high placement reportedly overrides GPA and non-target background. | Checked 2026-09-26: maa.org returns 403 to this client, so it cannot be watched; registration goes through Stanford's local supervisor, typically opening in September and closing before the early-December exam.</t>
+          <t>Among the highest-signal lines a first-year can add to a quant resume. A high placement reportedly overrides GPA and non-target background. | Checked 2026-09-26: maa.org returns 403 to this client, so it cannot be watched; registration goes through Stanford's local supervisor, typically opening in September and closing before the early-December exam.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Built for you: 5 weeks, discrete math, for students not yet in advanced courses. Apprentices often return to the full program. | Checked 2026-09-26: the URL is year-specific; REU2027/ returns 404 today and the parent page does not link it yet. Kept.</t>
+          <t>Built for first-years: 5 weeks, discrete math, for students not yet in advanced courses. Apprentices often return to the full program. | Checked 2026-09-26: the URL is year-specific; REU2027/ returns 404 today and the parent page does not link it yet. Kept.</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr"/>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>THE right entry point for a freshman - a professor applies on your behalf. VPUE calls these 'good starting points'.</t>
+          <t>THE right entry point for a freshman - a professor applies on the student's behalf. VPUE calls these 'good starting points'.</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr"/>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>You can attend; low relative value for you.</t>
+          <t>Open to attend; low relative value for a first-year.</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr"/>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>That is a junior-year window. Not you.</t>
+          <t>That is a junior-year window; a first-year does not qualify.</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr"/>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Morgan Stanley's whole campus board, on Talentlink (morganstanley.tal.net) - 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). Found 2026-09-18 while resolving a pasted posting link. IMPORTANT, the obvious URL is the wrong one: www.morganstanley.com/careers/career-opportunities-search sits behind an Akamai WAF that resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string - same machine, same IP, so the block is User-Agent based and it is the Citadel case, reachable only by misrepresenting the client. Do not re-point a source at it. Morgan Stanley's OTHER board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately NOT watched: it carries 1,327 corporate roles, caps page size at 10 (about 133 requests a day), and a query for 'Sophomore' or 'Freshman' returns zero - the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text, ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect. RETIRED 2026-09-21, asked for directly: this board is no longer watched. It failed on consecutive runs returning only ~350 characters because the Talentlink page renders its listings in JavaScript, and there is no honest route to the same content -- www.morganstanley.com refuses this tracker's User-Agent (the Citadel case) and morganstanley.eightfold.ai does not carry the campus programmes. source_id cleared, so this row is the owner's to check by hand.</t>
+          <t>Morgan Stanley's whole campus board, on Talentlink (morganstanley.tal.net) - 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). Found 2026-09-18 while resolving a pasted posting link. IMPORTANT, the obvious URL is the wrong one: www.morganstanley.com/careers/career-opportunities-search sits behind an Akamai WAF that resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string - same machine, same IP, so the block is User-Agent based and it is the Citadel case, reachable only by misrepresenting the client. Do not re-point a source at it. Morgan Stanley's OTHER board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately NOT watched: it carries 1,327 corporate roles, caps page size at 10 (about 133 requests a day), and a query for 'Sophomore' or 'Freshman' returns zero - the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text, ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect. RETIRED 2026-09-21: this board is no longer watched. It failed on consecutive runs returning only ~350 characters because the Talentlink page renders its listings in JavaScript, and there is no honest route to the same content -- www.morganstanley.com refuses this tracker's User-Agent (the Citadel case) and morganstanley.eightfold.ai does not carry the campus programmes. source_id cleared, so this row is the owner's to check by hand.</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr"/>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - Jason is class of 2030, so he is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
+          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - a class of 2030 student is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr"/>
@@ -13805,7 +13805,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The teza-careers row's note claimed the firm was on no public ATS; it is not true. 9 postings, 0 early-career today.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The teza-careers row's note claimed the firm was on no public ATS; it is not true. 9 postings, 0 early-career today.</t>
         </is>
       </c>
     </row>
@@ -14217,7 +14217,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-30 from the 2026-09-14 discovery proposal, asked for directly. Default branch dev. 267 rows on 2026-09-30, 216 not closed; 49 carry a recognisable posting id and 19 of those are already on a watched source. Newest row and last commit both 2026-08-23 -- possibly dormant.</t>
+          <t>Added 2026-09-30 from the 2026-09-14 discovery proposal. Default branch dev. 267 rows on 2026-09-30, 216 not closed; 49 carry a recognisable posting id and 19 of those are already on a watched source. Newest row and last commit both 2026-08-23 -- possibly dormant.</t>
         </is>
       </c>
     </row>
@@ -14743,7 +14743,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The eclipse-careers row's note claimed the firm was on no public ATS; it is not true. 18 postings, 4 early-career ('Graduate Trader | 2027 Intake'). Slug was only visible in a grnhse_app embed script on eclipsetrading.com/all-jobs/.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The eclipse-careers row's note claimed the firm was on no public ATS; it is not true. 18 postings, 4 early-career ('Graduate Trader | 2027 Intake'). Slug was only visible in a grnhse_app embed script on eclipsetrading.com/all-jobs/.</t>
         </is>
       </c>
     </row>
@@ -15063,7 +15063,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The gsr-careers row's note claimed the firm was on no public ATS; it is not true. 5 postings, 0 early-career today. Advertised on the EU host, but boards-api.eu.greenhouse.io does not resolve and the plain host serves the slug fine.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The gsr-careers row's note claimed the firm was on no public ATS; it is not true. 5 postings, 0 early-career today. Advertised on the EU host, but boards-api.eu.greenhouse.io does not resolve and the plain host serves the slug fine.</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The headlands-careers row's note claimed the firm was on no public ATS; it is not true. 7 postings, 1 early-career ('Quantitative Researcher - New Grad'). The page_text row stays: headlands-careers does enumerate roles inline.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The headlands-careers row's note claimed the firm was on no public ATS; it is not true. 7 postings, 1 early-career ('Quantitative Researcher - New Grad'). The page_text row stays: headlands-careers does enumerate roles inline.</t>
         </is>
       </c>
     </row>
@@ -15143,7 +15143,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The hrt-careers / hrt-student-opportunities row's note claimed the firm was on no public ATS; it is not true. 3 postings, 2 early-career ('Campus Talent Community', 'FPGA Verification and Developer (Internships and Campus Full-time)'). Both HRT page_text rows claimed no public ATS. | CORRECTED 2026-09-30: 'hrttalentcommunity' is HRT's talent-pool board -- three placeholder postings, none a real opening. HRT's actual board is 'wehrtyou' (90 postings on 2026-09-30, including the Summer 2027 Algorithm Development, Software Engineering, Hardware and Data Scientist internships and WiTTI). Re-pointed; the two hudsonrivertrading.com page watchers were retired the same day because the site now answers 403 to every client.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The hrt-careers / hrt-student-opportunities row's note claimed the firm was on no public ATS; it is not true. 3 postings, 2 early-career ('Campus Talent Community', 'FPGA Verification and Developer (Internships and Campus Full-time)'). Both HRT page_text rows claimed no public ATS. | CORRECTED 2026-09-30: 'hrttalentcommunity' is HRT's talent-pool board -- three placeholder postings, none a real opening. HRT's actual board is 'wehrtyou' (90 postings on 2026-09-30, including the Summer 2027 Algorithm Development, Software Engineering, Hardware and Data Scientist internships and WiTTI). Re-pointed; the two hudsonrivertrading.com page watchers were retired the same day because the site now answers 403 to every client.</t>
         </is>
       </c>
     </row>
@@ -15821,7 +15821,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The quantbot-careers row's note claimed the firm was on no public ATS; it is not true. 7 postings, all 7 early-career: 'Quantitative Researcher Internship - 2027 [NY/London/HK]', 'Data Trading Analyst Summer Internship - 2027'.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The quantbot-careers row's note claimed the firm was on no public ATS; it is not true. 7 postings, all 7 early-career: 'Quantitative Researcher Internship - 2027 [NY/London/HK]', 'Data Trading Analyst Summer Internship - 2027'.</t>
         </is>
       </c>
     </row>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The tudor-careers row's note claimed the firm was on no public ATS; it is not true. 4 postings, 0 early-career today.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The tudor-careers row's note claimed the firm was on no public ATS; it is not true. 4 postings, 0 early-career today.</t>
         </is>
       </c>
     </row>
@@ -16301,7 +16301,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The verition-careers row's note claimed the firm was on no public ATS; it is not true. 32 postings, 3 early-career ('2027 Investment/Technology/Platform Internship (US)'). Slug was only visible in a grnhse_app embed script on verition.com/open-positions.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The verition-careers row's note claimed the firm was on no public ATS; it is not true. 32 postings, 3 early-career ('2027 Investment/Technology/Platform Internship (US)'). Slug was only visible in a grnhse_app embed script on verition.com/open-positions.</t>
         </is>
       </c>
     </row>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The xtx-careers row's note claimed the firm was on no public ATS; it is not true. 10 postings, 1 early-career ('AI Research Internship - XTY Labs').</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The xtx-careers row's note claimed the firm was on no public ATS; it is not true. 10 postings, 1 early-career ('AI Research Internship - XTY Labs').</t>
         </is>
       </c>
     </row>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed the owner's report that watched careers pages were not the real job boards. The eagleseven-careers row's note claimed the firm was on no public ATS; it is not true. 5 postings. Watched as page_text on the Workable widget JSON, the same shape as the existing capula-workable row, because there is no workable method.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The eagleseven-careers row's note claimed the firm was on no public ATS; it is not true. 5 postings. Watched as page_text on the Workable widget JSON, the same shape as the existing capula-workable row, because there is no workable method.</t>
         </is>
       </c>
     </row>
@@ -19991,7 +19991,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-21 from a link the owner pasted. Whole careers page, not a programme page: Solayer Labs (Solana/SVM infrastructure and payments, San Mateo CA) is on no public ATS - 226KB of Framer HTML with no greenhouse/lever/ashby/workday/iCIMS fingerprint and no external apply link, so the page itself is the durable target. Probed: HTTP 200, 2,514 characters of visible text, ratio 0.011, roles are server-rendered and clear both content floors; robots.txt allows. One role listed on the day it was added - Marketing Lead, full-time permanent, master's required, apply by posting a resume with code SLML - which is off-field and not applicable; watched for the engineering and internship postings it may carry later.</t>
+          <t>Added 2026-09-21 from a pasted link. Whole careers page, not a programme page: Solayer Labs (Solana/SVM infrastructure and payments, San Mateo CA) is on no public ATS - 226KB of Framer HTML with no greenhouse/lever/ashby/workday/iCIMS fingerprint and no external apply link, so the page itself is the durable target. Probed: HTTP 200, 2,514 characters of visible text, ratio 0.011, roles are server-rendered and clear both content floors; robots.txt allows. One role listed on the day it was added - Marketing Lead, full-time permanent, master's required, apply by posting a resume with code SLML - which is off-field and not applicable; watched for the engineering and internship postings it may carry later.</t>
         </is>
       </c>
     </row>

--- a/out/tracked.xlsx
+++ b/out/tracked.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Discovered" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Programs'!$A$1:$N$320</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$H$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Programs'!$A$1:$N$323</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$H$219</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Applied'!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Discovered'!$A$1:$H$58</definedName>
   </definedNames>
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N320"/>
+  <dimension ref="A1:N323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18490,8 +18490,188 @@
       </c>
       <c r="N320" s="2" t="inlineStr"/>
     </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>Built In software engineering internships</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>https://builtin.com/jobs/dev-engineering/internship</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>Varies by posting</t>
+        </is>
+      </c>
+      <c r="F321" s="4" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>Front page of Built In's software engineering internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>builtin-dev-engineering</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J321" s="2" t="inlineStr"/>
+      <c r="K321" s="2" t="inlineStr"/>
+      <c r="L321" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M321" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N321" s="2" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>Built In data and analytics internships</t>
+        </is>
+      </c>
+      <c r="C322" s="3" t="inlineStr">
+        <is>
+          <t>https://builtin.com/jobs/data-analytics/internship</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>Varies by posting</t>
+        </is>
+      </c>
+      <c r="F322" s="4" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>Front page of Built In's data and analytics internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>builtin-data-analytics</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J322" s="2" t="inlineStr"/>
+      <c r="K322" s="2" t="inlineStr"/>
+      <c r="L322" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M322" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N322" s="2" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>Built In finance internships</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>https://builtin.com/jobs/finance/internship</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>Varies by posting</t>
+        </is>
+      </c>
+      <c r="F323" s="4" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>Front page of Built In's finance internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>builtin-finance</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J323" s="2" t="inlineStr"/>
+      <c r="K323" s="2" t="inlineStr"/>
+      <c r="L323" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M323" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N323" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N320"/>
+  <autoFilter ref="A1:N323"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -18807,6 +18987,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C318" r:id="rId312"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C319" r:id="rId313"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C320" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C321" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C322" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C323" r:id="rId317"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18818,7 +19001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H213"/>
+  <dimension ref="A1:H219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -19146,12 +19329,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>millennium-eightfold</t>
+          <t>smallco-ashby</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>eightfold</t>
+          <t>ashby_bulk</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -19159,17 +19342,17 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>https://campusjobs.mlp.com/api/apply/v2/jobs?domain=mlp.com</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01T14:34:49+00:00</t>
-        </is>
-      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Small-company boards (Ashby)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>ashby.txt</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -19177,19 +19360,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12. The largest hole the source audit found: millennium-students watched a careers page whose note said Millennium was on no public ATS, while this Eightfold board answers our own User-Agent with 59 campus postings (17 US), including '2027 Quantitative Researcher Intern, Austin' and '2027 Applied AI Engineer Intern, New York'. Descriptions are absent from the list payload, so posting bodies are fetched per changed row.</t>
+          <t>Added 2026-10-01. 136 Ashby boards listed in data/boards/ashby.txt, each kept because it carried an in-field US undergraduate internship when probed. A board that fails on a given run keeps its previous rows; HEALTH names it.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>aprameyak-2027</t>
+          <t>millennium-eightfold</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>github_readme</t>
+          <t>eightfold</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -19197,17 +19380,17 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>aprameyak 2027 Tech Jobs</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>aprameyak/2027-tech-jobs</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>https://campusjobs.mlp.com/api/apply/v2/jobs?domain=mlp.com</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01T14:34:49+00:00</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -19215,14 +19398,14 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-10-01. Measured before adding: about 17 in-field US internships on neither Simplify's full list nor the existing watchlist. Links to the employer's own posting, so cross-source dedupe works on it.</t>
+          <t>Added 2026-09-12. The largest hole the source audit found: millennium-students watched a careers page whose note said Millennium was on no public ATS, while this Eightfold board answers our own User-Agent with 59 campus postings (17 US), including '2027 Quantitative Researcher Intern, Austin' and '2027 Applied AI Engineer Intern, New York'. Descriptions are absent from the list payload, so posting bodies are fetched per changed row.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>dreamworkhq-2027</t>
+          <t>aprameyak-2027</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -19237,12 +19420,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Dreamwork Open Tech Internships 2027</t>
+          <t>aprameyak 2027 Tech Jobs</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>dreamworkhq/Open-Tech-Internships-2027</t>
+          <t>aprameyak/2027-tech-jobs</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -19253,14 +19436,14 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-10-01. Measured before adding: about 175 in-field US internships on neither Simplify's full list nor the existing watchlist. Links to the employer's own posting, so cross-source dedupe works on it.</t>
+          <t>Added 2026-10-01. Measured before adding: about 17 in-field US internships on neither Simplify's full list nor the existing watchlist. Links to the employer's own posting, so cross-source dedupe works on it.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>luisae</t>
+          <t>dreamworkhq-2027</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -19270,24 +19453,20 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>LuisaE/opportunities</t>
+          <t>Dreamwork Open Tech Internships 2027</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>LuisaE/opportunities</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01T14:34:49+00:00</t>
-        </is>
-      </c>
+          <t>dreamworkhq/Open-Tech-Internships-2027</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -19295,14 +19474,14 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Default branch is master, not main.</t>
+          <t>Added 2026-10-01. Measured before adding: about 175 in-field US internships on neither Simplify's full list nor the existing watchlist. Links to the employer's own posting, so cross-source dedupe works on it.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>mehek-2027</t>
+          <t>luisae</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -19312,20 +19491,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>mehek-builds Summer 2027 Internships (Litos)</t>
+          <t>LuisaE/opportunities</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>mehek-builds/Summer2027-Internships</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
+          <t>LuisaE/opportunities</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01T14:34:49+00:00</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -19333,14 +19516,14 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-10-01. Measured before adding: about 19, quant-dense in-field US internships on neither Simplify's full list nor the existing watchlist. Links to the employer's own posting, so cross-source dedupe works on it.</t>
+          <t>Default branch is master, not main.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>nuft-2027</t>
+          <t>mehek-2027</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -19350,24 +19533,20 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>NUFT 2027 Quant Internships</t>
+          <t>mehek-builds Summer 2027 Internships (Litos)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>northwesternfintech/2027QuantInternships</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01T14:34:49+00:00</t>
-        </is>
-      </c>
+          <t>mehek-builds/Summer2027-Internships</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -19375,14 +19554,14 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47 firms, no class-year tags. Company is the ## heading above each table; watch for new firm sections and new role rows.</t>
+          <t>Added 2026-10-01. Measured before adding: about 19, quant-dense in-field US internships on neither Simplify's full list nor the existing watchlist. Links to the employer's own posting, so cross-source dedupe works on it.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>simplify-2027</t>
+          <t>nuft-2027</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -19392,17 +19571,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>SimplifyJobs Summer 2027 Internships</t>
+          <t>NUFT 2027 Quant Internships</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>SimplifyJobs/Summer2027-Internships</t>
+          <t>northwesternfintech/2027QuantInternships</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -19417,14 +19596,14 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1169 roles on branch dev. README uses HTML &lt;table&gt;, not markdown. Low signal - no class-year tagging - so filtered to the SWE and quant sections only.</t>
+          <t>47 firms, no class-year tags. Company is the ## heading above each table; watch for new firm sections and new role rows.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>speedyapply-ai-2027</t>
+          <t>simplify-2027</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -19434,17 +19613,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>speedyapply 2027 AI College Jobs (Quant)</t>
+          <t>SimplifyJobs Summer 2027 Internships</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>speedyapply/2027-AI-College-Jobs</t>
+          <t>SimplifyJobs/Summer2027-Internships</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -19459,14 +19638,14 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 6.5K stars, pushed daily, branch main. Quant section only: 40 rows, 12 of them Citadel / Citadel Securities US - the only honest route to those, since citadel.com refuses paths.USER_AGENT. Citadel posting links will 403 in enrich, so those rows arrive without a body.</t>
+          <t>1169 roles on branch dev. README uses HTML &lt;table&gt;, not markdown. Low signal - no class-year tagging - so filtered to the SWE and quant sections only.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>speedyapply-swe-2027</t>
+          <t>speedyapply-ai-2027</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -19481,12 +19660,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>speedyapply 2027 SWE College Jobs (Quant)</t>
+          <t>speedyapply 2027 AI College Jobs (Quant)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>speedyapply/2027-SWE-College-Jobs</t>
+          <t>speedyapply/2027-AI-College-Jobs</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -19501,14 +19680,14 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 9.4K stars, pushed daily, branch main. Quant section only: 15 rows, 1 Citadel. FAANG+/Other sections are excluded: 414 of 735 rows share a posting id with Simplify/zshah.</t>
+          <t>Verified 2026-09-26: 6.5K stars, pushed daily, branch main. Quant section only: 40 rows, 12 of them Citadel / Citadel Securities US - the only honest route to those, since citadel.com refuses paths.USER_AGENT. Citadel posting links will 403 in enrich, so those rows arrive without a body.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>underclassmen-cruz</t>
+          <t>speedyapply-swe-2027</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -19523,12 +19702,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>underclassmen-opportunities (Cruz-Lopez)</t>
+          <t>speedyapply 2027 SWE College Jobs (Quant)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
+          <t>speedyapply/2027-SWE-College-Jobs</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -19543,14 +19722,14 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Best-maintained underclassmen list. Explicit [OPEN]/[CLOSING SOON] status column and grad windows inline in role titles. Six tables with differing headers.</t>
+          <t>Verified 2026-09-26: 9.4K stars, pushed daily, branch main. Quant section only: 15 rows, 1 Citadel. FAANG+/Other sections are excluded: 414 of 735 rows share a posting id with Simplify/zshah.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>underclassmen-zapply</t>
+          <t>underclassmen-cruz</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -19565,12 +19744,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>zapplyjobs underclassmen-internships</t>
+          <t>underclassmen-opportunities (Cruz-Lopez)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>zapplyjobs/underclassmen-internships</t>
+          <t>Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -19585,14 +19764,14 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Stale but occasionally updated. Company and role are combined into a single linked Name column.</t>
+          <t>Best-maintained underclassmen list. Explicit [OPEN]/[CLOSING SOON] status column and grad windows inline in role titles. Six tables with differing headers.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>vanshb03-2027</t>
+          <t>underclassmen-zapply</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -19602,17 +19781,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>vanshb03 Summer 2027 Tech Internships</t>
+          <t>zapplyjobs underclassmen-internships</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>vanshb03/Summer2027-Internships</t>
+          <t>zapplyjobs/underclassmen-internships</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -19627,14 +19806,14 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-30 from the 2026-09-14 discovery proposal. Default branch dev. 267 rows on 2026-09-30, 216 not closed; 49 carry a recognisable posting id and 19 of those are already on a watched source. Newest row and last commit both 2026-08-23 -- possibly dormant.</t>
+          <t>Stale but occasionally updated. Company and role are combined into a single linked Name column.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>zshah-2027</t>
+          <t>vanshb03-2027</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -19649,12 +19828,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>zshah Summer 2027 / Fall 2026 Tech Internships</t>
+          <t>vanshb03 Summer 2027 Tech Internships</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>zshah101/Automated-List-Of-Summer-2027-and-Fall-2026-Tech-Internships</t>
+          <t>vanshb03/Summer2027-Internships</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -19669,34 +19848,34 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,803 ATS endpoints polled every 30 min, 12 connectors, no LLM anywhere. Wide and large-firm-heavy like Simplify, so signal=low, but it carries a stated posting date and a visa/H-1B verdict neither of which we compute.</t>
+          <t>Added 2026-09-30 from the 2026-09-14 discovery proposal. Default branch dev. 267 rows on 2026-09-30, 216 not closed; 49 carry a recognisable posting id and 19 of those are already on a watched source. Newest row and last commit both 2026-08-23 -- possibly dormant.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>3red-greenhouse</t>
+          <t>zshah-2027</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>github_readme</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3Red Partners</t>
+          <t>zshah Summer 2027 / Fall 2026 Tech Internships</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3redpartners</t>
+          <t>zshah101/Automated-List-Of-Summer-2027-and-Fall-2026-Tech-Internships</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -19711,14 +19890,14 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 8 jobs.</t>
+          <t>4,803 ATS endpoints polled every 30 min, 12 connectors, no LLM anywhere. Wide and large-firm-heavy like Simplify, so signal=low, but it carries a stated posting date and a visa/H-1B verdict neither of which we compute.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>akunacapital-greenhouse</t>
+          <t>3red-greenhouse</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -19728,13 +19907,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3Red Partners</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>akunacapital</t>
+          <t>3redpartners</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -19749,14 +19932,14 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Akuna Capital. Verified 2026-09-11: 38 postings, 9 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 8 jobs.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>aqr-greenhouse</t>
+          <t>akunacapital-greenhouse</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -19766,17 +19949,13 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>AQR Capital</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>aqr</t>
+          <t>akunacapital</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -19791,14 +19970,14 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 54 jobs.</t>
+          <t>Akuna Capital. Verified 2026-09-11: 38 postings, 9 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>aquaticcapitalmanagement-greenhouse</t>
+          <t>aqr-greenhouse</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -19808,13 +19987,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>AQR Capital</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>aquaticcapitalmanagement</t>
+          <t>aqr</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -19829,14 +20012,14 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Aquatic Capital. Verified 2026-09-11: 8 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 54 jobs.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>axq-greenhouse</t>
+          <t>aquaticcapitalmanagement-greenhouse</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -19846,17 +20029,13 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>AXQ Capital</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>axq</t>
+          <t>aquaticcapitalmanagement</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -19871,14 +20050,14 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26 by source research against published firm lists (chrisaycock quant-firm gist, nuft headings, quant-bobby), probed under paths.USER_AGENT: 23 postings, 1 US intern (Quantitative Research Intern, Summer 2027, New York), targeting 2027/2028 graduates. Quant firm, so the whole board is kept even though Simplify and zshah carry some rows.</t>
+          <t>Aquatic Capital. Verified 2026-09-11: 8 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>blackedge-greenhouse</t>
+          <t>axq-greenhouse</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -19888,17 +20067,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>BlackEdge Capital</t>
+          <t>AXQ Capital</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>blackedgecapital</t>
+          <t>axq</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -19913,14 +20092,14 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 independently of the agent report: 6 jobs, 2 US student (Quant Developer Intern, Quant Trader Intern - Chicago).</t>
+          <t>Verified 2026-09-26 by source research against published firm lists (chrisaycock quant-firm gist, nuft headings, quant-bobby), probed under paths.USER_AGENT: 23 postings, 1 US intern (Quantitative Research Intern, Summer 2027, New York), targeting 2027/2028 graduates. Quant firm, so the whole board is kept even though Simplify and zshah carry some rows.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>bluecrest-greenhouse</t>
+          <t>blackedge-greenhouse</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -19930,17 +20109,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>BlueCrest Capital</t>
+          <t>BlackEdge Capital</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>bluecrestcapitalmanagement</t>
+          <t>blackedgecapital</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -19955,14 +20134,14 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 independently of the agent report: 9 jobs, 0 student today.</t>
+          <t>Verified 2026-09-11 independently of the agent report: 6 jobs, 2 US student (Quant Developer Intern, Quant Trader Intern - Chicago).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>boerboel-greenhouse</t>
+          <t>bluecrest-greenhouse</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -19977,12 +20156,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Boerboel Trading</t>
+          <t>BlueCrest Capital</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>boerboeltrading</t>
+          <t>bluecrestcapitalmanagement</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -19997,14 +20176,14 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 independently of the agent report: 4 jobs, 0 student today.</t>
+          <t>Verified 2026-09-11 independently of the agent report: 9 jobs, 0 student today.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>chicagotrading-greenhouse</t>
+          <t>boerboel-greenhouse</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -20014,17 +20193,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Chicago Trading Company (CTC)</t>
+          <t>Boerboel Trading</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>chicagotrading</t>
+          <t>boerboeltrading</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -20039,14 +20218,14 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 25 jobs.</t>
+          <t>Verified 2026-09-11 independently of the agent report: 4 jobs, 0 student today.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>drweng-greenhouse</t>
+          <t>chicagotrading-greenhouse</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -20056,13 +20235,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Chicago Trading Company (CTC)</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>drweng</t>
+          <t>chicagotrading</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -20077,14 +20260,14 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>DRW. Verified 2026-09-11: 157 postings, 8 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 25 jobs.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>dvtrading-greenhouse</t>
+          <t>drweng-greenhouse</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -20100,7 +20283,7 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>dvtrading</t>
+          <t>drweng</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -20115,14 +20298,14 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>DV Trading. Verified 2026-09-11: 67 postings, 11 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>DRW. Verified 2026-09-11: 157 postings, 8 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>eclipse-greenhouse</t>
+          <t>dvtrading-greenhouse</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -20138,7 +20321,7 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>eclipsetrading</t>
+          <t>dvtrading</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -20153,14 +20336,14 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The eclipse-careers row's note claimed the firm was on no public ATS; it is not true. 18 postings, 4 early-career ('Graduate Trader | 2027 Intake'). Slug was only visible in a grnhse_app embed script on eclipsetrading.com/all-jobs/.</t>
+          <t>DV Trading. Verified 2026-09-11: 67 postings, 11 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>engineersgate-greenhouse</t>
+          <t>eclipse-greenhouse</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -20170,17 +20353,13 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Engineers Gate</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>engineersgate</t>
+          <t>eclipsetrading</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -20195,14 +20374,14 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 7 jobs.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The eclipse-careers row's note claimed the firm was on no public ATS; it is not true. 18 postings, 4 early-career ('Graduate Trader | 2027 Intake'). Slug was only visible in a grnhse_app embed script on eclipsetrading.com/all-jobs/.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>exoduspoint-greenhouse</t>
+          <t>engineersgate-greenhouse</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -20217,12 +20396,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>ExodusPoint Capital</t>
+          <t>Engineers Gate</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>exoduspoint</t>
+          <t>engineersgate</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -20237,14 +20416,14 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 2 jobs.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 7 jobs.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>fiveringsllc-greenhouse</t>
+          <t>exoduspoint-greenhouse</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -20254,13 +20433,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>ExodusPoint Capital</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>fiveringsllc</t>
+          <t>exoduspoint</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -20275,14 +20458,14 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Five Rings. Verified 2026-09-11: 16 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 2 jobs.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>flowtraders-greenhouse</t>
+          <t>fiveringsllc-greenhouse</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -20298,7 +20481,7 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>flowtraders</t>
+          <t>fiveringsllc</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -20313,14 +20496,14 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Flow Traders. Verified 2026-09-11: 41 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Five Rings. Verified 2026-09-11: 16 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>gelber-greenhouse</t>
+          <t>flowtraders-greenhouse</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -20330,17 +20513,13 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Gelber Group</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>gelbergroup</t>
+          <t>flowtraders</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -20355,14 +20534,14 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 8 jobs.</t>
+          <t>Flow Traders. Verified 2026-09-11: 41 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>genevatrading-greenhouse</t>
+          <t>gelber-greenhouse</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -20372,13 +20551,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Gelber Group</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>genevatrading</t>
+          <t>gelbergroup</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -20393,14 +20576,14 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Geneva Trading. Verified 2026-09-11: 10 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 8 jobs.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>gsacapital-greenhouse</t>
+          <t>genevatrading-greenhouse</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -20410,17 +20593,13 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>GSA Capital</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>gsacapital</t>
+          <t>genevatrading</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -20435,14 +20614,14 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 independently of the agent report: 9 jobs, 1 US student (Quantitative Researcher - Intern, London/New York). GSA was NOT acquired by Eisler - it converted to a proprietary firm in Nov 2021 and hires actively.</t>
+          <t>Geneva Trading. Verified 2026-09-11: 10 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>gsr-greenhouse</t>
+          <t>gsacapital-greenhouse</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -20452,13 +20631,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>GSA Capital</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>gsrmarkets</t>
+          <t>gsacapital</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -20473,14 +20656,14 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The gsr-careers row's note claimed the firm was on no public ATS; it is not true. 5 postings, 0 early-career today. Advertised on the EU host, but boards-api.eu.greenhouse.io does not resolve and the plain host serves the slug fine.</t>
+          <t>Verified 2026-09-11 independently of the agent report: 9 jobs, 1 US student (Quantitative Researcher - Intern, London/New York). GSA was NOT acquired by Eisler - it converted to a proprietary firm in Nov 2021 and hires actively.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>headlands-greenhouse</t>
+          <t>gsr-greenhouse</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -20496,7 +20679,7 @@
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>headlandstechnologiesllc</t>
+          <t>gsrmarkets</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -20511,14 +20694,14 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The headlands-careers row's note claimed the firm was on no public ATS; it is not true. 7 postings, 1 early-career ('Quantitative Researcher - New Grad'). The page_text row stays: headlands-careers does enumerate roles inline.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The gsr-careers row's note claimed the firm was on no public ATS; it is not true. 5 postings, 0 early-career today. Advertised on the EU host, but boards-api.eu.greenhouse.io does not resolve and the plain host serves the slug fine.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>hrt-greenhouse</t>
+          <t>headlands-greenhouse</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -20528,17 +20711,13 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Hudson River Trading</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>wehrtyou</t>
+          <t>headlandstechnologiesllc</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -20553,14 +20732,14 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The hrt-careers / hrt-student-opportunities row's note claimed the firm was on no public ATS; it is not true. 3 postings, 2 early-career ('Campus Talent Community', 'FPGA Verification and Developer (Internships and Campus Full-time)'). Both HRT page_text rows claimed no public ATS. | CORRECTED 2026-09-30: 'hrttalentcommunity' is HRT's talent-pool board -- three placeholder postings, none a real opening. HRT's actual board is 'wehrtyou' (90 postings on 2026-09-30, including the Summer 2027 Algorithm Development, Software Engineering, Hardware and Data Scientist internships and WiTTI). Re-pointed; the two hudsonrivertrading.com page watchers were retired the same day because the site now answers 403 to every client.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The headlands-careers row's note claimed the firm was on no public ATS; it is not true. 7 postings, 1 early-career ('Quantitative Researcher - New Grad'). The page_text row stays: headlands-careers does enumerate roles inline.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>hyannisportresearch-greenhouse</t>
+          <t>hrt-greenhouse</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -20570,13 +20749,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Hudson River Trading</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>hyannisportresearch</t>
+          <t>wehrtyou</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -20591,14 +20774,14 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Hyannisport Research. Verified 2026-09-11: 10 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The hrt-careers / hrt-student-opportunities row's note claimed the firm was on no public ATS; it is not true. 3 postings, 2 early-career ('Campus Talent Community', 'FPGA Verification and Developer (Internships and Campus Full-time)'). Both HRT page_text rows claimed no public ATS. | CORRECTED 2026-09-30: 'hrttalentcommunity' is HRT's talent-pool board -- three placeholder postings, none a real opening. HRT's actual board is 'wehrtyou' (90 postings on 2026-09-30, including the Summer 2027 Algorithm Development, Software Engineering, Hardware and Data Scientist internships and WiTTI). Re-pointed; the two hudsonrivertrading.com page watchers were retired the same day because the site now answers 403 to every client.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>imc-greenhouse</t>
+          <t>hyannisportresearch-greenhouse</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -20614,7 +20797,7 @@
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>imc</t>
+          <t>hyannisportresearch</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -20629,14 +20812,14 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>IMC. Verified 2026-09-11: 170 postings, 7 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Hyannisport Research. Verified 2026-09-11: 10 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>janestreet-greenhouse</t>
+          <t>imc-greenhouse</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -20652,7 +20835,7 @@
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>janestreet</t>
+          <t>imc</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -20667,14 +20850,14 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Jane Street. Verified 2026-09-11: 230 postings, 20 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>IMC. Verified 2026-09-11: 170 postings, 7 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>jumpcrypto-greenhouse</t>
+          <t>janestreet-greenhouse</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -20684,17 +20867,13 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Jump Crypto</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>jumpcrypto</t>
+          <t>janestreet</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -20709,14 +20888,14 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 5 jobs.</t>
+          <t>Jane Street. Verified 2026-09-11: 230 postings, 20 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>jumptrading-greenhouse</t>
+          <t>jumpcrypto-greenhouse</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -20726,13 +20905,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Jump Crypto</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>jumptrading</t>
+          <t>jumpcrypto</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -20747,14 +20930,14 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Jump Trading. Verified 2026-09-11: 106 postings, 10 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 5 jobs.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>kkr-greenhouse</t>
+          <t>jumptrading-greenhouse</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -20764,17 +20947,13 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>KKR</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>jumptrading</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -20789,14 +20968,14 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: the KKR student-careers page embeds boards.greenhouse.io/embed/job_board/js?for=staged; boards-api.../boards/staged/jobs returns 22 KKR student jobs (2027 K-Star, MBA, PE internships). The slug name is odd but it is KKR's own board. KKR Scholars (first-year) posts here ~Feb.</t>
+          <t>Jump Trading. Verified 2026-09-11: 106 postings, 10 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>mako-greenhouse</t>
+          <t>kkr-greenhouse</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -20806,17 +20985,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Mako Global</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>mako</t>
+          <t>staged</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -20831,14 +21010,14 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 independently of the agent report: 8 jobs, 0 US student today (graduate roles are Sydney/London). Watched for when a US role appears.</t>
+          <t>Verified 2026-09-30: the KKR student-careers page embeds boards.greenhouse.io/embed/job_board/js?for=staged; boards-api.../boards/staged/jobs returns 22 KKR student jobs (2027 K-Star, MBA, PE internships). The slug name is odd but it is KKR's own board. KKR Scholars (first-year) posts here ~Feb.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>mangroup-greenhouse</t>
+          <t>mako-greenhouse</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -20848,17 +21027,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Man Group / AHL / Numeric</t>
+          <t>Mako Global</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>mangroup</t>
+          <t>mako</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -20873,14 +21052,14 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 53 jobs.</t>
+          <t>Verified 2026-09-11 independently of the agent report: 8 jobs, 0 US student today (graduate roles are Sydney/London). Watched for when a US role appears.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>marshallwace-intern-greenhouse</t>
+          <t>mangroup-greenhouse</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -20890,17 +21069,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Marshall Wace</t>
+          <t>Man Group / AHL / Numeric</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>mwinternshipprogram</t>
+          <t>mangroup</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -20915,14 +21094,14 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26 by source research against published firm lists (chrisaycock quant-firm gist, nuft headings, quant-bobby), probed under paths.USER_AGENT: 7 intern postings, 1 in New York. The main `marshallwace` slug has 0 postings, which is why earlier sweeps passed it; this slug is linked only from mwam.com/technology-internship-programme/.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 53 jobs.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>mavensecuritiesholdingltd-greenhouse</t>
+          <t>marshallwace-intern-greenhouse</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -20932,13 +21111,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Marshall Wace</t>
+        </is>
+      </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>mavensecuritiesholdingltd</t>
+          <t>mwinternshipprogram</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -20953,14 +21136,14 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Maven Securities. Verified 2026-09-11: 46 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-26 by source research against published firm lists (chrisaycock quant-firm gist, nuft headings, quant-bobby), probed under paths.USER_AGENT: 7 intern postings, 1 in New York. The main `marshallwace` slug has 0 postings, which is why earlier sweeps passed it; this slug is linked only from mwam.com/technology-internship-programme/.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>oldmissioncapital-greenhouse</t>
+          <t>mavensecuritiesholdingltd-greenhouse</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -20976,7 +21159,7 @@
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>oldmissioncapital</t>
+          <t>mavensecuritiesholdingltd</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -20991,14 +21174,14 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Old Mission. Verified 2026-09-11: 38 postings, 3 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Maven Securities. Verified 2026-09-11: 46 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>optiverprivate-greenhouse</t>
+          <t>oldmissioncapital-greenhouse</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -21014,7 +21197,7 @@
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>optiverprivate</t>
+          <t>oldmissioncapital</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -21029,14 +21212,14 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Optiver. Verified 2026-09-11: 10 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Old Mission. Verified 2026-09-11: 38 postings, 3 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>optiverus-greenhouse</t>
+          <t>optiverprivate-greenhouse</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -21046,17 +21229,13 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Optiver US</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>optiverus</t>
+          <t>optiverprivate</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -21071,14 +21250,14 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 163 jobs. The `optiver` and `optiverprivate` slugs return 0 and 1; this is the live US board.</t>
+          <t>Optiver. Verified 2026-09-11: 10 postings, 1 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>pdtpartners-greenhouse</t>
+          <t>optiverus-greenhouse</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -21088,13 +21267,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Optiver US</t>
+        </is>
+      </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>pdtpartners</t>
+          <t>optiverus</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -21109,14 +21292,14 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>PDT Partners. Verified 2026-09-11: 9 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 163 jobs. The `optiver` and `optiverprivate` slugs return 0 and 1; this is the live US board.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>point72-greenhouse</t>
+          <t>pdtpartners-greenhouse</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -21126,17 +21309,13 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Point72 / Cubist</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>point72</t>
+          <t>pdtpartners</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -21151,14 +21330,14 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 227 jobs.</t>
+          <t>PDT Partners. Verified 2026-09-11: 9 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>quadrature-greenhouse</t>
+          <t>point72-greenhouse</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -21173,12 +21352,12 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Quadrature Capital</t>
+          <t>Point72 / Cubist</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>quadraturecapital</t>
+          <t>point72</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -21193,14 +21372,14 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 4 jobs.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 227 jobs.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>quantbot-greenhouse</t>
+          <t>quadrature-greenhouse</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -21210,13 +21389,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Quadrature Capital</t>
+        </is>
+      </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>quantbot-technologies</t>
+          <t>quadraturecapital</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -21231,14 +21414,14 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The quantbot-careers row's note claimed the firm was on no public ATS; it is not true. 7 postings, all 7 early-career: 'Quantitative Researcher Internship - 2027 [NY/London/HK]', 'Data Trading Analyst Summer Internship - 2027'.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 4 jobs.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>qube-greenhouse</t>
+          <t>quantbot-greenhouse</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -21248,17 +21431,13 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Qube Research &amp; Technologies</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>quberesearchandtechnologies</t>
+          <t>quantbot-technologies</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -21273,14 +21452,14 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 198 jobs.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The quantbot-careers row's note claimed the firm was on no public ATS; it is not true. 7 postings, all 7 early-career: 'Quantitative Researcher Internship - 2027 [NY/London/HK]', 'Data Trading Analyst Summer Internship - 2027'.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>radix-greenhouse</t>
+          <t>qube-greenhouse</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -21295,12 +21474,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Radix Trading</t>
+          <t>Qube Research &amp; Technologies</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>radixuniversity</t>
+          <t>quberesearchandtechnologies</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -21315,14 +21494,14 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 independently of the agent report: 8 jobs, 1 US student (Quantitative Technologist, C++ Intern - Chicago). The `radix` and `radixexperienced` slugs are the wrong board and the experienced board respectively.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 198 jobs.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>schonfeld-greenhouse</t>
+          <t>radix-greenhouse</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -21332,13 +21511,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Radix Trading</t>
+        </is>
+      </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>schonfeld</t>
+          <t>radixuniversity</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -21353,14 +21536,14 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Schonfeld. Verified 2026-09-11: 71 postings, 13 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 independently of the agent report: 8 jobs, 1 US student (Quantitative Technologist, C++ Intern - Chicago). The `radix` and `radixexperienced` slugs are the wrong board and the experienced board respectively.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>scm-greenhouse</t>
+          <t>schonfeld-greenhouse</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -21370,17 +21553,13 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Stevens Capital Management</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>scm</t>
+          <t>schonfeld</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -21395,14 +21574,14 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26 by source research against published firm lists (chrisaycock quant-firm gist, nuft headings, quant-bobby), probed under paths.USER_AGENT: 29 postings, 2 internships (Quantitative Research Analyst Internship, Developer Internship; Radnor, PA). Slug found by rendering the JS careers page.</t>
+          <t>Schonfeld. Verified 2026-09-11: 71 postings, 13 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>sevenresearch-greenhouse</t>
+          <t>scm-greenhouse</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -21412,13 +21591,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Stevens Capital Management</t>
+        </is>
+      </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>sevenresearch</t>
+          <t>scm</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -21433,14 +21616,14 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Seven Research. Verified 2026-09-11: 8 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-26 by source research against published firm lists (chrisaycock quant-firm gist, nuft headings, quant-bobby), probed under paths.USER_AGENT: 29 postings, 2 internships (Quantitative Research Analyst Internship, Developer Internship; Radnor, PA). Slug found by rendering the JS careers page.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>simplex-greenhouse</t>
+          <t>sevenresearch-greenhouse</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -21450,17 +21633,13 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Simplex Trading</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>simplextrading</t>
+          <t>sevenresearch</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -21475,14 +21654,14 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 5 jobs.</t>
+          <t>Seven Research. Verified 2026-09-11: 8 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>squarepoint-greenhouse</t>
+          <t>simplex-greenhouse</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -21492,17 +21671,17 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Squarepoint Capital</t>
+          <t>Simplex Trading</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>squarepointcapital</t>
+          <t>simplextrading</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -21517,14 +21696,14 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 93 jobs.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 5 jobs.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>towerresearch-greenhouse</t>
+          <t>squarepoint-greenhouse</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -21539,12 +21718,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Tower Research Capital</t>
+          <t>Squarepoint Capital</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>towerresearchcapital</t>
+          <t>squarepointcapital</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -21559,14 +21738,14 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 86 jobs. Richer than the tower-careers page watcher, which is kept as a second signal.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 93 jobs.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>transmarketgroup-greenhouse</t>
+          <t>towerresearch-greenhouse</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -21576,13 +21755,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Tower Research Capital</t>
+        </is>
+      </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>transmarketgroup</t>
+          <t>towerresearchcapital</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -21597,14 +21780,14 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>TransMarket Group. Verified 2026-09-11: 19 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 86 jobs. Richer than the tower-careers page watcher, which is kept as a second signal.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>tudor-greenhouse</t>
+          <t>transmarketgroup-greenhouse</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -21620,7 +21803,7 @@
       <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>tudorgroup</t>
+          <t>transmarketgroup</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -21635,14 +21818,14 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The tudor-careers row's note claimed the firm was on no public ATS; it is not true. 4 postings, 0 early-career today.</t>
+          <t>TransMarket Group. Verified 2026-09-11: 19 postings, 4 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>vaticlabs-greenhouse</t>
+          <t>tudor-greenhouse</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -21658,7 +21841,7 @@
       <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>vaticlabs</t>
+          <t>tudorgroup</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -21673,14 +21856,14 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Vatic Labs. Verified 2026-09-11: 9 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The tudor-careers row's note claimed the firm was on no public ATS; it is not true. 4 postings, 0 early-career today.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>verition-greenhouse</t>
+          <t>vaticlabs-greenhouse</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -21696,7 +21879,7 @@
       <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>veritiongroupllc</t>
+          <t>vaticlabs</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -21711,14 +21894,14 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The verition-careers row's note claimed the firm was on no public ATS; it is not true. 32 postings, 3 early-career ('2027 Investment/Technology/Platform Internship (US)'). Slug was only visible in a grnhse_app embed script on verition.com/open-positions.</t>
+          <t>Vatic Labs. Verified 2026-09-11: 9 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>virtu-greenhouse</t>
+          <t>verition-greenhouse</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -21734,7 +21917,7 @@
       <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>virtu</t>
+          <t>veritiongroupllc</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -21749,14 +21932,14 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Virtu Financial. Verified 2026-09-11: 50 postings, 6 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The verition-careers row's note claimed the firm was on no public ATS; it is not true. 32 postings, 3 early-career ('2027 Investment/Technology/Platform Internship (US)'). Slug was only visible in a grnhse_app embed script on verition.com/open-positions.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>voloridge-greenhouse</t>
+          <t>virtu-greenhouse</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -21766,17 +21949,13 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Voloridge / Ascend Program</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>voloridgeinvestmentmanagement</t>
+          <t>virtu</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -21791,14 +21970,14 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11: 8 jobs, 4 US student rows including ASCEND PROGRAM 2027 - one of the very few programmes whose stated eligibility is 'first and second-year undergraduate students', so it is open to class of 2030 now. Two bugs had to be fixed before this row worked: 'Ascend Program 2027' contains no 'intern' and was only caught once the title screen learned Summer-Analyst/year vocabulary, and its location reads 'Jupiter, Florida' while the rest of the board reads 'Jupiter, FL', so the US filter dropped exactly this posting until it learned spelled-out state names.</t>
+          <t>Virtu Financial. Verified 2026-09-11: 50 postings, 6 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>walleyecapital-external-students-greenhouse</t>
+          <t>voloridge-greenhouse</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -21808,13 +21987,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Voloridge / Ascend Program</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>walleyecapital-external-students</t>
+          <t>voloridgeinvestmentmanagement</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -21829,14 +22012,14 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Walleye Capital. Verified 2026-09-11: 3 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11: 8 jobs, 4 US student rows including ASCEND PROGRAM 2027 - one of the very few programmes whose stated eligibility is 'first and second-year undergraduate students', so it is open to class of 2030 now. Two bugs had to be fixed before this row worked: 'Ascend Program 2027' contains no 'intern' and was only caught once the title screen learned Summer-Analyst/year vocabulary, and its location reads 'Jupiter, Florida' while the rest of the board reads 'Jupiter, FL', so the US filter dropped exactly this posting until it learned spelled-out state names.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>winton-greenhouse</t>
+          <t>walleyecapital-external-students-greenhouse</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -21846,17 +22029,13 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Winton</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>winton</t>
+          <t>walleyecapital-external-students</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -21871,14 +22050,14 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-11 by firm sweep against external firm lists: 10 jobs.</t>
+          <t>Walleye Capital. Verified 2026-09-11: 3 postings, 2 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>worldquant-greenhouse</t>
+          <t>winton-greenhouse</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -21888,13 +22067,17 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Winton</t>
+        </is>
+      </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>worldquant</t>
+          <t>winton</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -21909,14 +22092,14 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>WorldQuant. Verified 2026-09-11: 103 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Verified 2026-09-11 by firm sweep against external firm lists: 10 jobs.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>xantium-greenhouse</t>
+          <t>worldquant-greenhouse</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -21926,17 +22109,13 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Xantium</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>xantium</t>
+          <t>worldquant</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -21951,14 +22130,14 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26 by source research against published firm lists (chrisaycock quant-firm gist, nuft headings, quant-bobby), probed under paths.USER_AGENT: 8 postings, 2 intern (Quantitative Developer Intern, NY/London, Summer 2027; penultimate year required).</t>
+          <t>WorldQuant. Verified 2026-09-11: 103 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>xtxmarkets-greenhouse</t>
+          <t>xantium-greenhouse</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -21968,13 +22147,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Xantium</t>
+        </is>
+      </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>xtxmarketstechnologies</t>
+          <t>xantium</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -21989,19 +22172,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The xtx-careers row's note claimed the firm was on no public ATS; it is not true. 10 postings, 1 early-career ('AI Research Internship - XTY Labs').</t>
+          <t>Verified 2026-09-26 by source research against published firm lists (chrisaycock quant-firm gist, nuft headings, quant-bobby), probed under paths.USER_AGENT: 8 postings, 2 intern (Quantitative Developer Intern, NY/London, Summer 2027; penultimate year required).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>belvederetrading-lever</t>
+          <t>xtxmarkets-greenhouse</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -22012,7 +22195,7 @@
       <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>belvederetrading</t>
+          <t>xtxmarketstechnologies</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -22027,19 +22210,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Belvedere Trading. Verified 2026-09-11: 14 postings, 3 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Added 2026-09-12 by the audit that followed a manual finding that watched careers pages were not the real job boards. The xtx-careers row's note claimed the firm was on no public ATS; it is not true. 10 postings, 1 early-career ('AI Research Internship - XTY Labs').</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>valkyrietrading-lever</t>
+          <t>smallco-greenhouse</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>greenhouse_bulk</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -22047,17 +22230,17 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr"/>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Small-company boards (Greenhouse)</t>
+        </is>
+      </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>valkyrietrading</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01T14:34:49+00:00</t>
-        </is>
-      </c>
+          <t>greenhouse.txt</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -22065,37 +22248,37 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Valkyrie Trading. Verified 2026-09-11: 6 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
+          <t>Added 2026-10-01. 167 Greenhouse boards listed in data/boards/greenhouse.txt, each kept because it carried an in-field US undergraduate internship when probed. A board that fails on a given run keeps its previous rows; HEALTH names it.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>citadel-students</t>
+          <t>belvederetrading-lever</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Citadel students</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>https://www.citadel.com/careers/students/</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr"/>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>belvederetrading</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01T14:34:49+00:00</t>
+        </is>
+      </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -22103,37 +22286,37 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>method=manual on purpose. Re-tested 2026-09-11: 403 Forbidden to state.USER_AGENT, HTTP 200 to a spoofed browser User-Agent. The block is deliberate and UA-based, so the only way to automate this page is to lie about who we are - declined. Surfaces as a monthly calendar reminder instead. An earlier note claiming 6,763 chars of text was measured with a browser-presenting fetcher, not with this tool's client.</t>
+          <t>Belvedere Trading. Verified 2026-09-11: 14 postings, 3 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>citadelsecurities-careers</t>
+          <t>valkyrietrading-lever</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Citadel Securities</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>https://www.citadelsecurities.com/careers</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr"/>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>valkyrietrading</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01T14:34:49+00:00</t>
+        </is>
+      </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -22141,19 +22324,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>method=manual on purpose. Sampled 10x on 2026-09-11: HTTP 200 in 5 of 10 fetches, 403 Cloudflare in the other 5, all with state.USER_AGENT. An earlier note here claimed the page was readable at 10,638 chars - that was a single lucky sample, the same error made on citadel.com the same day. An INTERMITTENT block is worse than a hard one: the source would report a failure on roughly half of all runs and escalate into ACT NOW after three, so it must not be automated. Re-sample repeatedly, never once, before moving any Citadel row off manual.</t>
+          <t>Valkyrie Trading. Verified 2026-09-11: 6 postings, 0 US student rows after the title/Employment-Type and US-location filters. program_names is deliberately empty: one board is not one tracked program.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>kaggle-competitions</t>
+          <t>smallco-lever</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>lever_bulk</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -22163,12 +22346,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Kaggle Competitions (all active)</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>https://www.kaggle.com/api/v1/competitions/list</t>
+          <t>Small-company boards (Lever)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>lever.txt</t>
         </i